--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -28409,7 +28409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3087"/>
+  <dimension ref="A1:C3088"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61951,10 +61951,10 @@
         <v>45808</v>
       </c>
       <c r="B3049" t="n">
-        <v>248000</v>
+        <v>246000</v>
       </c>
       <c r="C3049" t="n">
-        <v>248000</v>
+        <v>246000</v>
       </c>
     </row>
     <row r="3050">
@@ -61962,10 +61962,10 @@
         <v>45815</v>
       </c>
       <c r="B3050" t="n">
-        <v>250000</v>
+        <v>248000</v>
       </c>
       <c r="C3050" t="n">
-        <v>250000</v>
+        <v>248000</v>
       </c>
     </row>
     <row r="3051">
@@ -62369,10 +62369,21 @@
         <v>46074</v>
       </c>
       <c r="B3087" t="n">
-        <v>212000</v>
+        <v>213000</v>
       </c>
       <c r="C3087" t="n">
-        <v>212000</v>
+        <v>213000</v>
+      </c>
+    </row>
+    <row r="3088">
+      <c r="A3088" s="1" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B3088" t="n">
+        <v>213000</v>
+      </c>
+      <c r="C3088" t="n">
+        <v>213000</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -7046,7 +7046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C697"/>
+  <dimension ref="A1:C698"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14661,10 +14661,10 @@
         <v>45839</v>
       </c>
       <c r="B692" t="n">
-        <v>1310909.44</v>
+        <v>1310908.54</v>
       </c>
       <c r="C692" t="n">
-        <v>1310909.44</v>
+        <v>1310908.54</v>
       </c>
     </row>
     <row r="693">
@@ -14672,10 +14672,10 @@
         <v>45870</v>
       </c>
       <c r="B693" t="n">
-        <v>1306123.16</v>
+        <v>1306121.23</v>
       </c>
       <c r="C693" t="n">
-        <v>1306123.16</v>
+        <v>1306121.23</v>
       </c>
     </row>
     <row r="694">
@@ -14683,10 +14683,10 @@
         <v>45901</v>
       </c>
       <c r="B694" t="n">
-        <v>1310561.74</v>
+        <v>1310561.76</v>
       </c>
       <c r="C694" t="n">
-        <v>1310561.74</v>
+        <v>1310561.76</v>
       </c>
     </row>
     <row r="695">
@@ -14694,10 +14694,10 @@
         <v>45931</v>
       </c>
       <c r="B695" t="n">
-        <v>1316400.1</v>
+        <v>1315011.6</v>
       </c>
       <c r="C695" t="n">
-        <v>1316400.1</v>
+        <v>1315011.6</v>
       </c>
     </row>
     <row r="696">
@@ -14705,10 +14705,10 @@
         <v>45962</v>
       </c>
       <c r="B696" t="n">
-        <v>1314713.24</v>
+        <v>1311884.89</v>
       </c>
       <c r="C696" t="n">
-        <v>1314713.24</v>
+        <v>1311884.89</v>
       </c>
     </row>
     <row r="697">
@@ -14716,10 +14716,21 @@
         <v>45992</v>
       </c>
       <c r="B697" t="n">
-        <v>1328559.61</v>
+        <v>1324277.25</v>
       </c>
       <c r="C697" t="n">
-        <v>1328559.61</v>
+        <v>1324277.25</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B698" t="n">
+        <v>1328986.66</v>
+      </c>
+      <c r="C698" t="n">
+        <v>1328986.66</v>
       </c>
     </row>
   </sheetData>
@@ -18075,7 +18086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C938"/>
+  <dimension ref="A1:C939"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28396,6 +28407,17 @@
       </c>
       <c r="C938" t="n">
         <v>4.3</v>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B939" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="C939" t="n">
+        <v>4.4</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -28431,7 +28431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3088"/>
+  <dimension ref="A1:C3089"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62402,9 +62402,20 @@
         <v>46081</v>
       </c>
       <c r="B3088" t="n">
+        <v>214000</v>
+      </c>
+      <c r="C3088" t="n">
+        <v>214000</v>
+      </c>
+    </row>
+    <row r="3089">
+      <c r="A3089" s="1" t="n">
+        <v>46088</v>
+      </c>
+      <c r="B3089" t="n">
         <v>213000</v>
       </c>
-      <c r="C3088" t="n">
+      <c r="C3089" t="n">
         <v>213000</v>
       </c>
     </row>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -62430,7 +62430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C805"/>
+  <dimension ref="A1:C806"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71233,10 +71233,10 @@
         <v>45839</v>
       </c>
       <c r="B800" t="n">
-        <v>18009.5</v>
+        <v>18040.9</v>
       </c>
       <c r="C800" t="n">
-        <v>18009.5</v>
+        <v>18040.9</v>
       </c>
     </row>
     <row r="801">
@@ -71244,10 +71244,10 @@
         <v>45870</v>
       </c>
       <c r="B801" t="n">
-        <v>18027.6</v>
+        <v>18076.9</v>
       </c>
       <c r="C801" t="n">
-        <v>18027.6</v>
+        <v>18076.9</v>
       </c>
     </row>
     <row r="802">
@@ -71255,10 +71255,10 @@
         <v>45901</v>
       </c>
       <c r="B802" t="n">
-        <v>18037.9</v>
+        <v>18094.6</v>
       </c>
       <c r="C802" t="n">
-        <v>18037.9</v>
+        <v>18094.6</v>
       </c>
     </row>
     <row r="803">
@@ -71266,10 +71266,10 @@
         <v>45931</v>
       </c>
       <c r="B803" t="n">
-        <v>18014.8</v>
+        <v>18066.6</v>
       </c>
       <c r="C803" t="n">
-        <v>18014.8</v>
+        <v>18066.6</v>
       </c>
     </row>
     <row r="804">
@@ -71277,10 +71277,10 @@
         <v>45962</v>
       </c>
       <c r="B804" t="n">
-        <v>18037.3</v>
+        <v>18088</v>
       </c>
       <c r="C804" t="n">
-        <v>18037.3</v>
+        <v>18088</v>
       </c>
     </row>
     <row r="805">
@@ -71288,10 +71288,21 @@
         <v>45992</v>
       </c>
       <c r="B805" t="n">
-        <v>18032.2</v>
+        <v>18082.4</v>
       </c>
       <c r="C805" t="n">
-        <v>18032.2</v>
+        <v>18082.4</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B806" t="n">
+        <v>18203.2</v>
+      </c>
+      <c r="C806" t="n">
+        <v>18203.2</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -14744,7 +14744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C302"/>
+  <dimension ref="A1:C303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17420,10 +17420,10 @@
         <v>44197</v>
       </c>
       <c r="B243" t="n">
-        <v>7204</v>
+        <v>7162</v>
       </c>
       <c r="C243" t="n">
-        <v>7.204</v>
+        <v>7.162</v>
       </c>
     </row>
     <row r="244">
@@ -17431,10 +17431,10 @@
         <v>44228</v>
       </c>
       <c r="B244" t="n">
-        <v>7752</v>
+        <v>7827</v>
       </c>
       <c r="C244" t="n">
-        <v>7.752</v>
+        <v>7.827</v>
       </c>
     </row>
     <row r="245">
@@ -17442,10 +17442,10 @@
         <v>44256</v>
       </c>
       <c r="B245" t="n">
-        <v>8470</v>
+        <v>8499</v>
       </c>
       <c r="C245" t="n">
-        <v>8.470000000000001</v>
+        <v>8.499000000000001</v>
       </c>
     </row>
     <row r="246">
@@ -17453,10 +17453,10 @@
         <v>44287</v>
       </c>
       <c r="B246" t="n">
-        <v>9356</v>
+        <v>9346</v>
       </c>
       <c r="C246" t="n">
-        <v>9.356</v>
+        <v>9.346</v>
       </c>
     </row>
     <row r="247">
@@ -17464,10 +17464,10 @@
         <v>44317</v>
       </c>
       <c r="B247" t="n">
-        <v>9905</v>
+        <v>9954</v>
       </c>
       <c r="C247" t="n">
-        <v>9.904999999999999</v>
+        <v>9.954000000000001</v>
       </c>
     </row>
     <row r="248">
@@ -17475,10 +17475,10 @@
         <v>44348</v>
       </c>
       <c r="B248" t="n">
-        <v>10298</v>
+        <v>10319</v>
       </c>
       <c r="C248" t="n">
-        <v>10.298</v>
+        <v>10.319</v>
       </c>
     </row>
     <row r="249">
@@ -17486,10 +17486,10 @@
         <v>44378</v>
       </c>
       <c r="B249" t="n">
-        <v>11049</v>
+        <v>10983</v>
       </c>
       <c r="C249" t="n">
-        <v>11.049</v>
+        <v>10.983</v>
       </c>
     </row>
     <row r="250">
@@ -17497,10 +17497,10 @@
         <v>44409</v>
       </c>
       <c r="B250" t="n">
-        <v>10956</v>
+        <v>10872</v>
       </c>
       <c r="C250" t="n">
-        <v>10.956</v>
+        <v>10.872</v>
       </c>
     </row>
     <row r="251">
@@ -17508,10 +17508,10 @@
         <v>44440</v>
       </c>
       <c r="B251" t="n">
-        <v>10879</v>
+        <v>10834</v>
       </c>
       <c r="C251" t="n">
-        <v>10.879</v>
+        <v>10.834</v>
       </c>
     </row>
     <row r="252">
@@ -17519,10 +17519,10 @@
         <v>44470</v>
       </c>
       <c r="B252" t="n">
-        <v>11341</v>
+        <v>11238</v>
       </c>
       <c r="C252" t="n">
-        <v>11.341</v>
+        <v>11.238</v>
       </c>
     </row>
     <row r="253">
@@ -17530,10 +17530,10 @@
         <v>44501</v>
       </c>
       <c r="B253" t="n">
-        <v>11119</v>
+        <v>11199</v>
       </c>
       <c r="C253" t="n">
-        <v>11.119</v>
+        <v>11.199</v>
       </c>
     </row>
     <row r="254">
@@ -17541,10 +17541,10 @@
         <v>44531</v>
       </c>
       <c r="B254" t="n">
-        <v>11417</v>
+        <v>11520</v>
       </c>
       <c r="C254" t="n">
-        <v>11.417</v>
+        <v>11.52</v>
       </c>
     </row>
     <row r="255">
@@ -17552,10 +17552,10 @@
         <v>44562</v>
       </c>
       <c r="B255" t="n">
-        <v>11238</v>
+        <v>11210</v>
       </c>
       <c r="C255" t="n">
-        <v>11.238</v>
+        <v>11.21</v>
       </c>
     </row>
     <row r="256">
@@ -17563,10 +17563,10 @@
         <v>44593</v>
       </c>
       <c r="B256" t="n">
-        <v>11661</v>
+        <v>11698</v>
       </c>
       <c r="C256" t="n">
-        <v>11.661</v>
+        <v>11.698</v>
       </c>
     </row>
     <row r="257">
@@ -17574,10 +17574,10 @@
         <v>44621</v>
       </c>
       <c r="B257" t="n">
-        <v>12134</v>
+        <v>12301</v>
       </c>
       <c r="C257" t="n">
-        <v>12.134</v>
+        <v>12.301</v>
       </c>
     </row>
     <row r="258">
@@ -17585,10 +17585,10 @@
         <v>44652</v>
       </c>
       <c r="B258" t="n">
-        <v>11881</v>
+        <v>11861</v>
       </c>
       <c r="C258" t="n">
-        <v>11.881</v>
+        <v>11.861</v>
       </c>
     </row>
     <row r="259">
@@ -17596,10 +17596,10 @@
         <v>44682</v>
       </c>
       <c r="B259" t="n">
-        <v>11483</v>
+        <v>11535</v>
       </c>
       <c r="C259" t="n">
-        <v>11.483</v>
+        <v>11.535</v>
       </c>
     </row>
     <row r="260">
@@ -17607,10 +17607,10 @@
         <v>44713</v>
       </c>
       <c r="B260" t="n">
-        <v>11256</v>
+        <v>11283</v>
       </c>
       <c r="C260" t="n">
-        <v>11.256</v>
+        <v>11.283</v>
       </c>
     </row>
     <row r="261">
@@ -17618,10 +17618,10 @@
         <v>44743</v>
       </c>
       <c r="B261" t="n">
-        <v>11610</v>
+        <v>11576</v>
       </c>
       <c r="C261" t="n">
-        <v>11.61</v>
+        <v>11.576</v>
       </c>
     </row>
     <row r="262">
@@ -17629,10 +17629,10 @@
         <v>44774</v>
       </c>
       <c r="B262" t="n">
-        <v>10148</v>
+        <v>10092</v>
       </c>
       <c r="C262" t="n">
-        <v>10.148</v>
+        <v>10.092</v>
       </c>
     </row>
     <row r="263">
@@ -17640,10 +17640,10 @@
         <v>44805</v>
       </c>
       <c r="B263" t="n">
-        <v>10812</v>
+        <v>10800</v>
       </c>
       <c r="C263" t="n">
-        <v>10.812</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="264">
@@ -17651,10 +17651,10 @@
         <v>44835</v>
       </c>
       <c r="B264" t="n">
-        <v>10488</v>
+        <v>10447</v>
       </c>
       <c r="C264" t="n">
-        <v>10.488</v>
+        <v>10.447</v>
       </c>
     </row>
     <row r="265">
@@ -17662,10 +17662,10 @@
         <v>44866</v>
       </c>
       <c r="B265" t="n">
-        <v>10619</v>
+        <v>10632</v>
       </c>
       <c r="C265" t="n">
-        <v>10.619</v>
+        <v>10.632</v>
       </c>
     </row>
     <row r="266">
@@ -17673,10 +17673,10 @@
         <v>44896</v>
       </c>
       <c r="B266" t="n">
-        <v>10876</v>
+        <v>10902</v>
       </c>
       <c r="C266" t="n">
-        <v>10.876</v>
+        <v>10.902</v>
       </c>
     </row>
     <row r="267">
@@ -17684,10 +17684,10 @@
         <v>44927</v>
       </c>
       <c r="B267" t="n">
-        <v>10393</v>
+        <v>10318</v>
       </c>
       <c r="C267" t="n">
-        <v>10.393</v>
+        <v>10.318</v>
       </c>
     </row>
     <row r="268">
@@ -17695,10 +17695,10 @@
         <v>44958</v>
       </c>
       <c r="B268" t="n">
-        <v>9846</v>
+        <v>9857</v>
       </c>
       <c r="C268" t="n">
-        <v>9.846</v>
+        <v>9.856999999999999</v>
       </c>
     </row>
     <row r="269">
@@ -17706,10 +17706,10 @@
         <v>44986</v>
       </c>
       <c r="B269" t="n">
-        <v>9572</v>
+        <v>9655</v>
       </c>
       <c r="C269" t="n">
-        <v>9.571999999999999</v>
+        <v>9.654999999999999</v>
       </c>
     </row>
     <row r="270">
@@ -17717,10 +17717,10 @@
         <v>45017</v>
       </c>
       <c r="B270" t="n">
-        <v>9992</v>
+        <v>9966</v>
       </c>
       <c r="C270" t="n">
-        <v>9.992000000000001</v>
+        <v>9.965999999999999</v>
       </c>
     </row>
     <row r="271">
@@ -17728,10 +17728,10 @@
         <v>45047</v>
       </c>
       <c r="B271" t="n">
-        <v>9310</v>
+        <v>9368</v>
       </c>
       <c r="C271" t="n">
-        <v>9.31</v>
+        <v>9.368</v>
       </c>
     </row>
     <row r="272">
@@ -17739,10 +17739,10 @@
         <v>45078</v>
       </c>
       <c r="B272" t="n">
-        <v>9191</v>
+        <v>9180</v>
       </c>
       <c r="C272" t="n">
-        <v>9.191000000000001</v>
+        <v>9.18</v>
       </c>
     </row>
     <row r="273">
@@ -17750,10 +17750,10 @@
         <v>45108</v>
       </c>
       <c r="B273" t="n">
-        <v>8606</v>
+        <v>8657</v>
       </c>
       <c r="C273" t="n">
-        <v>8.606</v>
+        <v>8.657</v>
       </c>
     </row>
     <row r="274">
@@ -17761,10 +17761,10 @@
         <v>45139</v>
       </c>
       <c r="B274" t="n">
-        <v>9287</v>
+        <v>9254</v>
       </c>
       <c r="C274" t="n">
-        <v>9.287000000000001</v>
+        <v>9.254</v>
       </c>
     </row>
     <row r="275">
@@ -17772,10 +17772,10 @@
         <v>45170</v>
       </c>
       <c r="B275" t="n">
-        <v>9279</v>
+        <v>9259</v>
       </c>
       <c r="C275" t="n">
-        <v>9.279</v>
+        <v>9.259</v>
       </c>
     </row>
     <row r="276">
@@ -17783,10 +17783,10 @@
         <v>45200</v>
       </c>
       <c r="B276" t="n">
-        <v>8550</v>
+        <v>8580</v>
       </c>
       <c r="C276" t="n">
-        <v>8.550000000000001</v>
+        <v>8.58</v>
       </c>
     </row>
     <row r="277">
@@ -17794,10 +17794,10 @@
         <v>45231</v>
       </c>
       <c r="B277" t="n">
-        <v>8663</v>
+        <v>8602</v>
       </c>
       <c r="C277" t="n">
-        <v>8.663</v>
+        <v>8.602</v>
       </c>
     </row>
     <row r="278">
@@ -17805,10 +17805,10 @@
         <v>45261</v>
       </c>
       <c r="B278" t="n">
-        <v>8585</v>
+        <v>8520</v>
       </c>
       <c r="C278" t="n">
-        <v>8.585000000000001</v>
+        <v>8.52</v>
       </c>
     </row>
     <row r="279">
@@ -17816,10 +17816,10 @@
         <v>45292</v>
       </c>
       <c r="B279" t="n">
-        <v>8468</v>
+        <v>8378</v>
       </c>
       <c r="C279" t="n">
-        <v>8.468</v>
+        <v>8.378</v>
       </c>
     </row>
     <row r="280">
@@ -17827,10 +17827,10 @@
         <v>45323</v>
       </c>
       <c r="B280" t="n">
-        <v>8445</v>
+        <v>8440</v>
       </c>
       <c r="C280" t="n">
-        <v>8.445</v>
+        <v>8.44</v>
       </c>
     </row>
     <row r="281">
@@ -17838,10 +17838,10 @@
         <v>45352</v>
       </c>
       <c r="B281" t="n">
-        <v>8093</v>
+        <v>8206</v>
       </c>
       <c r="C281" t="n">
-        <v>8.093</v>
+        <v>8.206</v>
       </c>
     </row>
     <row r="282">
@@ -17849,10 +17849,10 @@
         <v>45383</v>
       </c>
       <c r="B282" t="n">
-        <v>7619</v>
+        <v>7529</v>
       </c>
       <c r="C282" t="n">
-        <v>7.619</v>
+        <v>7.529</v>
       </c>
     </row>
     <row r="283">
@@ -17860,10 +17860,10 @@
         <v>45413</v>
       </c>
       <c r="B283" t="n">
-        <v>7901</v>
+        <v>7782</v>
       </c>
       <c r="C283" t="n">
-        <v>7.901</v>
+        <v>7.782</v>
       </c>
     </row>
     <row r="284">
@@ -17871,10 +17871,10 @@
         <v>45444</v>
       </c>
       <c r="B284" t="n">
-        <v>7412</v>
+        <v>7416</v>
       </c>
       <c r="C284" t="n">
-        <v>7.412</v>
+        <v>7.416</v>
       </c>
     </row>
     <row r="285">
@@ -17882,10 +17882,10 @@
         <v>45474</v>
       </c>
       <c r="B285" t="n">
-        <v>7504</v>
+        <v>7426</v>
       </c>
       <c r="C285" t="n">
-        <v>7.504</v>
+        <v>7.426</v>
       </c>
     </row>
     <row r="286">
@@ -17893,10 +17893,10 @@
         <v>45505</v>
       </c>
       <c r="B286" t="n">
-        <v>7649</v>
+        <v>7520</v>
       </c>
       <c r="C286" t="n">
-        <v>7.649</v>
+        <v>7.52</v>
       </c>
     </row>
     <row r="287">
@@ -17904,10 +17904,10 @@
         <v>45536</v>
       </c>
       <c r="B287" t="n">
-        <v>7103</v>
+        <v>6943</v>
       </c>
       <c r="C287" t="n">
-        <v>7.103</v>
+        <v>6.943</v>
       </c>
     </row>
     <row r="288">
@@ -17915,10 +17915,10 @@
         <v>45566</v>
       </c>
       <c r="B288" t="n">
-        <v>7615</v>
+        <v>7379</v>
       </c>
       <c r="C288" t="n">
-        <v>7.615</v>
+        <v>7.379</v>
       </c>
     </row>
     <row r="289">
@@ -17926,10 +17926,10 @@
         <v>45597</v>
       </c>
       <c r="B289" t="n">
-        <v>8031</v>
+        <v>7566</v>
       </c>
       <c r="C289" t="n">
-        <v>8.031000000000001</v>
+        <v>7.566</v>
       </c>
     </row>
     <row r="290">
@@ -17937,10 +17937,10 @@
         <v>45627</v>
       </c>
       <c r="B290" t="n">
-        <v>7508</v>
+        <v>7295</v>
       </c>
       <c r="C290" t="n">
-        <v>7.508</v>
+        <v>7.295</v>
       </c>
     </row>
     <row r="291">
@@ -17948,10 +17948,10 @@
         <v>45658</v>
       </c>
       <c r="B291" t="n">
-        <v>7762</v>
+        <v>7431</v>
       </c>
       <c r="C291" t="n">
-        <v>7.762</v>
+        <v>7.431</v>
       </c>
     </row>
     <row r="292">
@@ -17959,10 +17959,10 @@
         <v>45689</v>
       </c>
       <c r="B292" t="n">
-        <v>7480</v>
+        <v>7242</v>
       </c>
       <c r="C292" t="n">
-        <v>7.48</v>
+        <v>7.242</v>
       </c>
     </row>
     <row r="293">
@@ -17970,10 +17970,10 @@
         <v>45717</v>
       </c>
       <c r="B293" t="n">
-        <v>7200</v>
+        <v>6952</v>
       </c>
       <c r="C293" t="n">
-        <v>7.2</v>
+        <v>6.952</v>
       </c>
     </row>
     <row r="294">
@@ -17981,10 +17981,10 @@
         <v>45748</v>
       </c>
       <c r="B294" t="n">
-        <v>7395</v>
+        <v>7098</v>
       </c>
       <c r="C294" t="n">
-        <v>7.395</v>
+        <v>7.098</v>
       </c>
     </row>
     <row r="295">
@@ -17992,10 +17992,10 @@
         <v>45778</v>
       </c>
       <c r="B295" t="n">
-        <v>7712</v>
+        <v>7310</v>
       </c>
       <c r="C295" t="n">
-        <v>7.712</v>
+        <v>7.31</v>
       </c>
     </row>
     <row r="296">
@@ -18003,10 +18003,10 @@
         <v>45809</v>
       </c>
       <c r="B296" t="n">
-        <v>7357</v>
+        <v>7204</v>
       </c>
       <c r="C296" t="n">
-        <v>7.357</v>
+        <v>7.204</v>
       </c>
     </row>
     <row r="297">
@@ -18014,10 +18014,10 @@
         <v>45839</v>
       </c>
       <c r="B297" t="n">
-        <v>7208</v>
+        <v>7089</v>
       </c>
       <c r="C297" t="n">
-        <v>7.208</v>
+        <v>7.089</v>
       </c>
     </row>
     <row r="298">
@@ -18025,10 +18025,10 @@
         <v>45870</v>
       </c>
       <c r="B298" t="n">
-        <v>7227</v>
+        <v>6919</v>
       </c>
       <c r="C298" t="n">
-        <v>7.227</v>
+        <v>6.919</v>
       </c>
     </row>
     <row r="299">
@@ -18036,10 +18036,10 @@
         <v>45901</v>
       </c>
       <c r="B299" t="n">
-        <v>7658</v>
+        <v>7169</v>
       </c>
       <c r="C299" t="n">
-        <v>7.658</v>
+        <v>7.169</v>
       </c>
     </row>
     <row r="300">
@@ -18047,10 +18047,10 @@
         <v>45931</v>
       </c>
       <c r="B300" t="n">
-        <v>7449</v>
+        <v>7170</v>
       </c>
       <c r="C300" t="n">
-        <v>7.449</v>
+        <v>7.17</v>
       </c>
     </row>
     <row r="301">
@@ -18058,10 +18058,10 @@
         <v>45962</v>
       </c>
       <c r="B301" t="n">
-        <v>6928</v>
+        <v>6846</v>
       </c>
       <c r="C301" t="n">
-        <v>6.928</v>
+        <v>6.846</v>
       </c>
     </row>
     <row r="302">
@@ -18069,10 +18069,21 @@
         <v>45992</v>
       </c>
       <c r="B302" t="n">
-        <v>6542</v>
+        <v>6550</v>
       </c>
       <c r="C302" t="n">
-        <v>6.542</v>
+        <v>6.55</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B303" t="n">
+        <v>6946</v>
+      </c>
+      <c r="C303" t="n">
+        <v>6.946</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -28442,7 +28442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3089"/>
+  <dimension ref="A1:C3090"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59729,10 +59729,10 @@
         <v>44373</v>
       </c>
       <c r="B2844" t="n">
-        <v>369000</v>
+        <v>368000</v>
       </c>
       <c r="C2844" t="n">
-        <v>369000</v>
+        <v>368000</v>
       </c>
     </row>
     <row r="2845">
@@ -59751,10 +59751,10 @@
         <v>44387</v>
       </c>
       <c r="B2846" t="n">
-        <v>332000</v>
+        <v>333000</v>
       </c>
       <c r="C2846" t="n">
-        <v>332000</v>
+        <v>333000</v>
       </c>
     </row>
     <row r="2847">
@@ -59784,10 +59784,10 @@
         <v>44408</v>
       </c>
       <c r="B2849" t="n">
-        <v>380000</v>
+        <v>379000</v>
       </c>
       <c r="C2849" t="n">
-        <v>380000</v>
+        <v>379000</v>
       </c>
     </row>
     <row r="2850">
@@ -59806,10 +59806,10 @@
         <v>44422</v>
       </c>
       <c r="B2851" t="n">
-        <v>368000</v>
+        <v>367000</v>
       </c>
       <c r="C2851" t="n">
-        <v>368000</v>
+        <v>367000</v>
       </c>
     </row>
     <row r="2852">
@@ -59839,10 +59839,10 @@
         <v>44443</v>
       </c>
       <c r="B2854" t="n">
-        <v>337000</v>
+        <v>335000</v>
       </c>
       <c r="C2854" t="n">
-        <v>337000</v>
+        <v>335000</v>
       </c>
     </row>
     <row r="2855">
@@ -59850,10 +59850,10 @@
         <v>44450</v>
       </c>
       <c r="B2855" t="n">
-        <v>344000</v>
+        <v>342000</v>
       </c>
       <c r="C2855" t="n">
-        <v>344000</v>
+        <v>342000</v>
       </c>
     </row>
     <row r="2856">
@@ -59872,10 +59872,10 @@
         <v>44464</v>
       </c>
       <c r="B2857" t="n">
-        <v>374000</v>
+        <v>375000</v>
       </c>
       <c r="C2857" t="n">
-        <v>374000</v>
+        <v>375000</v>
       </c>
     </row>
     <row r="2858">
@@ -59883,10 +59883,10 @@
         <v>44471</v>
       </c>
       <c r="B2858" t="n">
-        <v>314000</v>
+        <v>312000</v>
       </c>
       <c r="C2858" t="n">
-        <v>314000</v>
+        <v>312000</v>
       </c>
     </row>
     <row r="2859">
@@ -59894,10 +59894,10 @@
         <v>44478</v>
       </c>
       <c r="B2859" t="n">
-        <v>290000</v>
+        <v>291000</v>
       </c>
       <c r="C2859" t="n">
-        <v>290000</v>
+        <v>291000</v>
       </c>
     </row>
     <row r="2860">
@@ -59905,10 +59905,10 @@
         <v>44485</v>
       </c>
       <c r="B2860" t="n">
-        <v>290000</v>
+        <v>289000</v>
       </c>
       <c r="C2860" t="n">
-        <v>290000</v>
+        <v>289000</v>
       </c>
     </row>
     <row r="2861">
@@ -59916,10 +59916,10 @@
         <v>44492</v>
       </c>
       <c r="B2861" t="n">
-        <v>268000</v>
+        <v>269000</v>
       </c>
       <c r="C2861" t="n">
-        <v>268000</v>
+        <v>269000</v>
       </c>
     </row>
     <row r="2862">
@@ -59927,10 +59927,10 @@
         <v>44499</v>
       </c>
       <c r="B2862" t="n">
-        <v>262000</v>
+        <v>261000</v>
       </c>
       <c r="C2862" t="n">
-        <v>262000</v>
+        <v>261000</v>
       </c>
     </row>
     <row r="2863">
@@ -59960,10 +59960,10 @@
         <v>44520</v>
       </c>
       <c r="B2865" t="n">
-        <v>223000</v>
+        <v>224000</v>
       </c>
       <c r="C2865" t="n">
-        <v>223000</v>
+        <v>224000</v>
       </c>
     </row>
     <row r="2866">
@@ -59971,10 +59971,10 @@
         <v>44527</v>
       </c>
       <c r="B2866" t="n">
-        <v>222000</v>
+        <v>221000</v>
       </c>
       <c r="C2866" t="n">
-        <v>222000</v>
+        <v>221000</v>
       </c>
     </row>
     <row r="2867">
@@ -59982,10 +59982,10 @@
         <v>44534</v>
       </c>
       <c r="B2867" t="n">
-        <v>207000</v>
+        <v>206000</v>
       </c>
       <c r="C2867" t="n">
-        <v>207000</v>
+        <v>206000</v>
       </c>
     </row>
     <row r="2868">
@@ -60015,10 +60015,10 @@
         <v>44555</v>
       </c>
       <c r="B2870" t="n">
-        <v>216000</v>
+        <v>217000</v>
       </c>
       <c r="C2870" t="n">
-        <v>216000</v>
+        <v>217000</v>
       </c>
     </row>
     <row r="2871">
@@ -60026,10 +60026,10 @@
         <v>44562</v>
       </c>
       <c r="B2871" t="n">
-        <v>227000</v>
+        <v>229000</v>
       </c>
       <c r="C2871" t="n">
-        <v>227000</v>
+        <v>229000</v>
       </c>
     </row>
     <row r="2872">
@@ -60037,10 +60037,10 @@
         <v>44569</v>
       </c>
       <c r="B2872" t="n">
-        <v>247000</v>
+        <v>250000</v>
       </c>
       <c r="C2872" t="n">
-        <v>247000</v>
+        <v>250000</v>
       </c>
     </row>
     <row r="2873">
@@ -60048,10 +60048,10 @@
         <v>44576</v>
       </c>
       <c r="B2873" t="n">
-        <v>245000</v>
+        <v>246000</v>
       </c>
       <c r="C2873" t="n">
-        <v>245000</v>
+        <v>246000</v>
       </c>
     </row>
     <row r="2874">
@@ -60059,10 +60059,10 @@
         <v>44583</v>
       </c>
       <c r="B2874" t="n">
-        <v>238000</v>
+        <v>240000</v>
       </c>
       <c r="C2874" t="n">
-        <v>238000</v>
+        <v>240000</v>
       </c>
     </row>
     <row r="2875">
@@ -60103,10 +60103,10 @@
         <v>44611</v>
       </c>
       <c r="B2878" t="n">
-        <v>225000</v>
+        <v>224000</v>
       </c>
       <c r="C2878" t="n">
-        <v>225000</v>
+        <v>224000</v>
       </c>
     </row>
     <row r="2879">
@@ -60114,10 +60114,10 @@
         <v>44618</v>
       </c>
       <c r="B2879" t="n">
-        <v>209000</v>
+        <v>208000</v>
       </c>
       <c r="C2879" t="n">
-        <v>209000</v>
+        <v>208000</v>
       </c>
     </row>
     <row r="2880">
@@ -60169,10 +60169,10 @@
         <v>44653</v>
       </c>
       <c r="B2884" t="n">
-        <v>215000</v>
+        <v>214000</v>
       </c>
       <c r="C2884" t="n">
-        <v>215000</v>
+        <v>214000</v>
       </c>
     </row>
     <row r="2885">
@@ -60180,10 +60180,10 @@
         <v>44660</v>
       </c>
       <c r="B2885" t="n">
-        <v>213000</v>
+        <v>214000</v>
       </c>
       <c r="C2885" t="n">
-        <v>213000</v>
+        <v>214000</v>
       </c>
     </row>
     <row r="2886">
@@ -60191,10 +60191,10 @@
         <v>44667</v>
       </c>
       <c r="B2886" t="n">
-        <v>209000</v>
+        <v>210000</v>
       </c>
       <c r="C2886" t="n">
-        <v>209000</v>
+        <v>210000</v>
       </c>
     </row>
     <row r="2887">
@@ -60202,10 +60202,10 @@
         <v>44674</v>
       </c>
       <c r="B2887" t="n">
-        <v>210000</v>
+        <v>209000</v>
       </c>
       <c r="C2887" t="n">
-        <v>210000</v>
+        <v>209000</v>
       </c>
     </row>
     <row r="2888">
@@ -60213,10 +60213,10 @@
         <v>44681</v>
       </c>
       <c r="B2888" t="n">
-        <v>219000</v>
+        <v>218000</v>
       </c>
       <c r="C2888" t="n">
-        <v>219000</v>
+        <v>218000</v>
       </c>
     </row>
     <row r="2889">
@@ -60257,10 +60257,10 @@
         <v>44709</v>
       </c>
       <c r="B2892" t="n">
-        <v>200000</v>
+        <v>199000</v>
       </c>
       <c r="C2892" t="n">
-        <v>200000</v>
+        <v>199000</v>
       </c>
     </row>
     <row r="2893">
@@ -60268,10 +60268,10 @@
         <v>44716</v>
       </c>
       <c r="B2893" t="n">
-        <v>214000</v>
+        <v>213000</v>
       </c>
       <c r="C2893" t="n">
-        <v>214000</v>
+        <v>213000</v>
       </c>
     </row>
     <row r="2894">
@@ -60279,10 +60279,10 @@
         <v>44723</v>
       </c>
       <c r="B2894" t="n">
-        <v>213000</v>
+        <v>211000</v>
       </c>
       <c r="C2894" t="n">
-        <v>213000</v>
+        <v>211000</v>
       </c>
     </row>
     <row r="2895">
@@ -60290,10 +60290,10 @@
         <v>44730</v>
       </c>
       <c r="B2895" t="n">
-        <v>215000</v>
+        <v>214000</v>
       </c>
       <c r="C2895" t="n">
-        <v>215000</v>
+        <v>214000</v>
       </c>
     </row>
     <row r="2896">
@@ -60312,10 +60312,10 @@
         <v>44744</v>
       </c>
       <c r="B2897" t="n">
-        <v>215000</v>
+        <v>214000</v>
       </c>
       <c r="C2897" t="n">
-        <v>215000</v>
+        <v>214000</v>
       </c>
     </row>
     <row r="2898">
@@ -60345,10 +60345,10 @@
         <v>44765</v>
       </c>
       <c r="B2900" t="n">
-        <v>220000</v>
+        <v>221000</v>
       </c>
       <c r="C2900" t="n">
-        <v>220000</v>
+        <v>221000</v>
       </c>
     </row>
     <row r="2901">
@@ -60411,10 +60411,10 @@
         <v>44807</v>
       </c>
       <c r="B2906" t="n">
-        <v>204000</v>
+        <v>203000</v>
       </c>
       <c r="C2906" t="n">
-        <v>204000</v>
+        <v>203000</v>
       </c>
     </row>
     <row r="2907">
@@ -60422,10 +60422,10 @@
         <v>44814</v>
       </c>
       <c r="B2907" t="n">
-        <v>197000</v>
+        <v>195000</v>
       </c>
       <c r="C2907" t="n">
-        <v>197000</v>
+        <v>195000</v>
       </c>
     </row>
     <row r="2908">
@@ -60433,10 +60433,10 @@
         <v>44821</v>
       </c>
       <c r="B2908" t="n">
-        <v>201000</v>
+        <v>202000</v>
       </c>
       <c r="C2908" t="n">
-        <v>201000</v>
+        <v>202000</v>
       </c>
     </row>
     <row r="2909">
@@ -60444,10 +60444,10 @@
         <v>44828</v>
       </c>
       <c r="B2909" t="n">
-        <v>189000</v>
+        <v>190000</v>
       </c>
       <c r="C2909" t="n">
-        <v>189000</v>
+        <v>190000</v>
       </c>
     </row>
     <row r="2910">
@@ -60455,10 +60455,10 @@
         <v>44835</v>
       </c>
       <c r="B2910" t="n">
-        <v>204000</v>
+        <v>203000</v>
       </c>
       <c r="C2910" t="n">
-        <v>204000</v>
+        <v>203000</v>
       </c>
     </row>
     <row r="2911">
@@ -60466,10 +60466,10 @@
         <v>44842</v>
       </c>
       <c r="B2911" t="n">
-        <v>206000</v>
+        <v>207000</v>
       </c>
       <c r="C2911" t="n">
-        <v>206000</v>
+        <v>207000</v>
       </c>
     </row>
     <row r="2912">
@@ -60488,10 +60488,10 @@
         <v>44856</v>
       </c>
       <c r="B2913" t="n">
-        <v>201000</v>
+        <v>202000</v>
       </c>
       <c r="C2913" t="n">
-        <v>201000</v>
+        <v>202000</v>
       </c>
     </row>
     <row r="2914">
@@ -60565,10 +60565,10 @@
         <v>44905</v>
       </c>
       <c r="B2920" t="n">
-        <v>210000</v>
+        <v>209000</v>
       </c>
       <c r="C2920" t="n">
-        <v>210000</v>
+        <v>209000</v>
       </c>
     </row>
     <row r="2921">
@@ -60587,10 +60587,10 @@
         <v>44919</v>
       </c>
       <c r="B2922" t="n">
-        <v>204000</v>
+        <v>205000</v>
       </c>
       <c r="C2922" t="n">
-        <v>204000</v>
+        <v>205000</v>
       </c>
     </row>
     <row r="2923">
@@ -60598,10 +60598,10 @@
         <v>44926</v>
       </c>
       <c r="B2923" t="n">
-        <v>204000</v>
+        <v>205000</v>
       </c>
       <c r="C2923" t="n">
-        <v>204000</v>
+        <v>205000</v>
       </c>
     </row>
     <row r="2924">
@@ -60609,10 +60609,10 @@
         <v>44933</v>
       </c>
       <c r="B2924" t="n">
-        <v>208000</v>
+        <v>210000</v>
       </c>
       <c r="C2924" t="n">
-        <v>208000</v>
+        <v>210000</v>
       </c>
     </row>
     <row r="2925">
@@ -60620,10 +60620,10 @@
         <v>44940</v>
       </c>
       <c r="B2925" t="n">
-        <v>203000</v>
+        <v>204000</v>
       </c>
       <c r="C2925" t="n">
-        <v>203000</v>
+        <v>204000</v>
       </c>
     </row>
     <row r="2926">
@@ -60631,10 +60631,10 @@
         <v>44947</v>
       </c>
       <c r="B2926" t="n">
-        <v>203000</v>
+        <v>204000</v>
       </c>
       <c r="C2926" t="n">
-        <v>203000</v>
+        <v>204000</v>
       </c>
     </row>
     <row r="2927">
@@ -60664,10 +60664,10 @@
         <v>44968</v>
       </c>
       <c r="B2929" t="n">
-        <v>219000</v>
+        <v>220000</v>
       </c>
       <c r="C2929" t="n">
-        <v>219000</v>
+        <v>220000</v>
       </c>
     </row>
     <row r="2930">
@@ -60686,10 +60686,10 @@
         <v>44982</v>
       </c>
       <c r="B2931" t="n">
-        <v>209000</v>
+        <v>207000</v>
       </c>
       <c r="C2931" t="n">
-        <v>209000</v>
+        <v>207000</v>
       </c>
     </row>
     <row r="2932">
@@ -60697,10 +60697,10 @@
         <v>44989</v>
       </c>
       <c r="B2932" t="n">
-        <v>229000</v>
+        <v>230000</v>
       </c>
       <c r="C2932" t="n">
-        <v>229000</v>
+        <v>230000</v>
       </c>
     </row>
     <row r="2933">
@@ -60752,10 +60752,10 @@
         <v>45024</v>
       </c>
       <c r="B2937" t="n">
-        <v>219000</v>
+        <v>220000</v>
       </c>
       <c r="C2937" t="n">
-        <v>219000</v>
+        <v>220000</v>
       </c>
     </row>
     <row r="2938">
@@ -60774,10 +60774,10 @@
         <v>45038</v>
       </c>
       <c r="B2939" t="n">
-        <v>210000</v>
+        <v>209000</v>
       </c>
       <c r="C2939" t="n">
-        <v>210000</v>
+        <v>209000</v>
       </c>
     </row>
     <row r="2940">
@@ -60785,10 +60785,10 @@
         <v>45045</v>
       </c>
       <c r="B2940" t="n">
-        <v>214000</v>
+        <v>213000</v>
       </c>
       <c r="C2940" t="n">
-        <v>214000</v>
+        <v>213000</v>
       </c>
     </row>
     <row r="2941">
@@ -60829,10 +60829,10 @@
         <v>45073</v>
       </c>
       <c r="B2944" t="n">
-        <v>230000</v>
+        <v>229000</v>
       </c>
       <c r="C2944" t="n">
-        <v>230000</v>
+        <v>229000</v>
       </c>
     </row>
     <row r="2945">
@@ -60840,10 +60840,10 @@
         <v>45080</v>
       </c>
       <c r="B2945" t="n">
-        <v>253000</v>
+        <v>252000</v>
       </c>
       <c r="C2945" t="n">
-        <v>253000</v>
+        <v>252000</v>
       </c>
     </row>
     <row r="2946">
@@ -60851,10 +60851,10 @@
         <v>45087</v>
       </c>
       <c r="B2946" t="n">
-        <v>258000</v>
+        <v>256000</v>
       </c>
       <c r="C2946" t="n">
-        <v>258000</v>
+        <v>256000</v>
       </c>
     </row>
     <row r="2947">
@@ -60862,10 +60862,10 @@
         <v>45094</v>
       </c>
       <c r="B2947" t="n">
-        <v>260000</v>
+        <v>259000</v>
       </c>
       <c r="C2947" t="n">
-        <v>260000</v>
+        <v>259000</v>
       </c>
     </row>
     <row r="2948">
@@ -60895,10 +60895,10 @@
         <v>45115</v>
       </c>
       <c r="B2950" t="n">
-        <v>229000</v>
+        <v>230000</v>
       </c>
       <c r="C2950" t="n">
-        <v>229000</v>
+        <v>230000</v>
       </c>
     </row>
     <row r="2951">
@@ -60906,10 +60906,10 @@
         <v>45122</v>
       </c>
       <c r="B2951" t="n">
-        <v>228000</v>
+        <v>229000</v>
       </c>
       <c r="C2951" t="n">
-        <v>228000</v>
+        <v>229000</v>
       </c>
     </row>
     <row r="2952">
@@ -60983,10 +60983,10 @@
         <v>45171</v>
       </c>
       <c r="B2958" t="n">
-        <v>227000</v>
+        <v>225000</v>
       </c>
       <c r="C2958" t="n">
-        <v>227000</v>
+        <v>225000</v>
       </c>
     </row>
     <row r="2959">
@@ -60994,10 +60994,10 @@
         <v>45178</v>
       </c>
       <c r="B2959" t="n">
-        <v>227000</v>
+        <v>225000</v>
       </c>
       <c r="C2959" t="n">
-        <v>227000</v>
+        <v>225000</v>
       </c>
     </row>
     <row r="2960">
@@ -61005,10 +61005,10 @@
         <v>45185</v>
       </c>
       <c r="B2960" t="n">
-        <v>210000</v>
+        <v>211000</v>
       </c>
       <c r="C2960" t="n">
-        <v>210000</v>
+        <v>211000</v>
       </c>
     </row>
     <row r="2961">
@@ -61016,10 +61016,10 @@
         <v>45192</v>
       </c>
       <c r="B2961" t="n">
-        <v>215000</v>
+        <v>216000</v>
       </c>
       <c r="C2961" t="n">
-        <v>215000</v>
+        <v>216000</v>
       </c>
     </row>
     <row r="2962">
@@ -61093,10 +61093,10 @@
         <v>45241</v>
       </c>
       <c r="B2968" t="n">
-        <v>229000</v>
+        <v>230000</v>
       </c>
       <c r="C2968" t="n">
-        <v>229000</v>
+        <v>230000</v>
       </c>
     </row>
     <row r="2969">
@@ -61115,10 +61115,10 @@
         <v>45255</v>
       </c>
       <c r="B2970" t="n">
-        <v>214000</v>
+        <v>213000</v>
       </c>
       <c r="C2970" t="n">
-        <v>214000</v>
+        <v>213000</v>
       </c>
     </row>
     <row r="2971">
@@ -61126,10 +61126,10 @@
         <v>45262</v>
       </c>
       <c r="B2971" t="n">
-        <v>216000</v>
+        <v>215000</v>
       </c>
       <c r="C2971" t="n">
-        <v>216000</v>
+        <v>215000</v>
       </c>
     </row>
     <row r="2972">
@@ -61137,10 +61137,10 @@
         <v>45269</v>
       </c>
       <c r="B2972" t="n">
-        <v>204000</v>
+        <v>203000</v>
       </c>
       <c r="C2972" t="n">
-        <v>204000</v>
+        <v>203000</v>
       </c>
     </row>
     <row r="2973">
@@ -61159,10 +61159,10 @@
         <v>45283</v>
       </c>
       <c r="B2974" t="n">
-        <v>210000</v>
+        <v>212000</v>
       </c>
       <c r="C2974" t="n">
-        <v>210000</v>
+        <v>212000</v>
       </c>
     </row>
     <row r="2975">
@@ -61170,10 +61170,10 @@
         <v>45290</v>
       </c>
       <c r="B2975" t="n">
-        <v>198000</v>
+        <v>200000</v>
       </c>
       <c r="C2975" t="n">
-        <v>198000</v>
+        <v>200000</v>
       </c>
     </row>
     <row r="2976">
@@ -61181,10 +61181,10 @@
         <v>45297</v>
       </c>
       <c r="B2976" t="n">
-        <v>199000</v>
+        <v>201000</v>
       </c>
       <c r="C2976" t="n">
-        <v>199000</v>
+        <v>201000</v>
       </c>
     </row>
     <row r="2977">
@@ -61192,10 +61192,10 @@
         <v>45304</v>
       </c>
       <c r="B2977" t="n">
-        <v>193000</v>
+        <v>195000</v>
       </c>
       <c r="C2977" t="n">
-        <v>193000</v>
+        <v>195000</v>
       </c>
     </row>
     <row r="2978">
@@ -61203,10 +61203,10 @@
         <v>45311</v>
       </c>
       <c r="B2978" t="n">
-        <v>223000</v>
+        <v>224000</v>
       </c>
       <c r="C2978" t="n">
-        <v>223000</v>
+        <v>224000</v>
       </c>
     </row>
     <row r="2979">
@@ -61214,10 +61214,10 @@
         <v>45318</v>
       </c>
       <c r="B2979" t="n">
-        <v>225000</v>
+        <v>226000</v>
       </c>
       <c r="C2979" t="n">
-        <v>225000</v>
+        <v>226000</v>
       </c>
     </row>
     <row r="2980">
@@ -61225,10 +61225,10 @@
         <v>45325</v>
       </c>
       <c r="B2980" t="n">
-        <v>214000</v>
+        <v>213000</v>
       </c>
       <c r="C2980" t="n">
-        <v>214000</v>
+        <v>213000</v>
       </c>
     </row>
     <row r="2981">
@@ -61236,10 +61236,10 @@
         <v>45332</v>
       </c>
       <c r="B2981" t="n">
-        <v>212000</v>
+        <v>213000</v>
       </c>
       <c r="C2981" t="n">
-        <v>212000</v>
+        <v>213000</v>
       </c>
     </row>
     <row r="2982">
@@ -61247,10 +61247,10 @@
         <v>45339</v>
       </c>
       <c r="B2982" t="n">
-        <v>203000</v>
+        <v>202000</v>
       </c>
       <c r="C2982" t="n">
-        <v>203000</v>
+        <v>202000</v>
       </c>
     </row>
     <row r="2983">
@@ -61258,10 +61258,10 @@
         <v>45346</v>
       </c>
       <c r="B2983" t="n">
-        <v>214000</v>
+        <v>212000</v>
       </c>
       <c r="C2983" t="n">
-        <v>214000</v>
+        <v>212000</v>
       </c>
     </row>
     <row r="2984">
@@ -61269,10 +61269,10 @@
         <v>45353</v>
       </c>
       <c r="B2984" t="n">
-        <v>212000</v>
+        <v>213000</v>
       </c>
       <c r="C2984" t="n">
-        <v>212000</v>
+        <v>213000</v>
       </c>
     </row>
     <row r="2985">
@@ -61324,10 +61324,10 @@
         <v>45388</v>
       </c>
       <c r="B2989" t="n">
-        <v>212000</v>
+        <v>213000</v>
       </c>
       <c r="C2989" t="n">
-        <v>212000</v>
+        <v>213000</v>
       </c>
     </row>
     <row r="2990">
@@ -61335,10 +61335,10 @@
         <v>45395</v>
       </c>
       <c r="B2990" t="n">
-        <v>211000</v>
+        <v>212000</v>
       </c>
       <c r="C2990" t="n">
-        <v>211000</v>
+        <v>212000</v>
       </c>
     </row>
     <row r="2991">
@@ -61357,10 +61357,10 @@
         <v>45409</v>
       </c>
       <c r="B2992" t="n">
-        <v>209000</v>
+        <v>207000</v>
       </c>
       <c r="C2992" t="n">
-        <v>209000</v>
+        <v>207000</v>
       </c>
     </row>
     <row r="2993">
@@ -61368,10 +61368,10 @@
         <v>45416</v>
       </c>
       <c r="B2993" t="n">
-        <v>229000</v>
+        <v>230000</v>
       </c>
       <c r="C2993" t="n">
-        <v>229000</v>
+        <v>230000</v>
       </c>
     </row>
     <row r="2994">
@@ -61401,10 +61401,10 @@
         <v>45437</v>
       </c>
       <c r="B2996" t="n">
-        <v>221000</v>
+        <v>220000</v>
       </c>
       <c r="C2996" t="n">
-        <v>221000</v>
+        <v>220000</v>
       </c>
     </row>
     <row r="2997">
@@ -61412,10 +61412,10 @@
         <v>45444</v>
       </c>
       <c r="B2997" t="n">
-        <v>229000</v>
+        <v>227000</v>
       </c>
       <c r="C2997" t="n">
-        <v>229000</v>
+        <v>227000</v>
       </c>
     </row>
     <row r="2998">
@@ -61423,10 +61423,10 @@
         <v>45451</v>
       </c>
       <c r="B2998" t="n">
-        <v>241000</v>
+        <v>240000</v>
       </c>
       <c r="C2998" t="n">
-        <v>241000</v>
+        <v>240000</v>
       </c>
     </row>
     <row r="2999">
@@ -61434,10 +61434,10 @@
         <v>45458</v>
       </c>
       <c r="B2999" t="n">
-        <v>237000</v>
+        <v>236000</v>
       </c>
       <c r="C2999" t="n">
-        <v>237000</v>
+        <v>236000</v>
       </c>
     </row>
     <row r="3000">
@@ -61467,10 +61467,10 @@
         <v>45479</v>
       </c>
       <c r="B3002" t="n">
-        <v>222000</v>
+        <v>223000</v>
       </c>
       <c r="C3002" t="n">
-        <v>222000</v>
+        <v>223000</v>
       </c>
     </row>
     <row r="3003">
@@ -61478,10 +61478,10 @@
         <v>45486</v>
       </c>
       <c r="B3003" t="n">
-        <v>240000</v>
+        <v>241000</v>
       </c>
       <c r="C3003" t="n">
-        <v>240000</v>
+        <v>241000</v>
       </c>
     </row>
     <row r="3004">
@@ -61489,10 +61489,10 @@
         <v>45493</v>
       </c>
       <c r="B3004" t="n">
-        <v>236000</v>
+        <v>237000</v>
       </c>
       <c r="C3004" t="n">
-        <v>236000</v>
+        <v>237000</v>
       </c>
     </row>
     <row r="3005">
@@ -61555,10 +61555,10 @@
         <v>45535</v>
       </c>
       <c r="B3010" t="n">
-        <v>228000</v>
+        <v>227000</v>
       </c>
       <c r="C3010" t="n">
-        <v>228000</v>
+        <v>227000</v>
       </c>
     </row>
     <row r="3011">
@@ -61566,10 +61566,10 @@
         <v>45542</v>
       </c>
       <c r="B3011" t="n">
-        <v>230000</v>
+        <v>227000</v>
       </c>
       <c r="C3011" t="n">
-        <v>230000</v>
+        <v>227000</v>
       </c>
     </row>
     <row r="3012">
@@ -61577,10 +61577,10 @@
         <v>45549</v>
       </c>
       <c r="B3012" t="n">
-        <v>222000</v>
+        <v>223000</v>
       </c>
       <c r="C3012" t="n">
-        <v>222000</v>
+        <v>223000</v>
       </c>
     </row>
     <row r="3013">
@@ -61610,10 +61610,10 @@
         <v>45570</v>
       </c>
       <c r="B3015" t="n">
-        <v>259000</v>
+        <v>258000</v>
       </c>
       <c r="C3015" t="n">
-        <v>259000</v>
+        <v>258000</v>
       </c>
     </row>
     <row r="3016">
@@ -61621,10 +61621,10 @@
         <v>45577</v>
       </c>
       <c r="B3016" t="n">
-        <v>240000</v>
+        <v>241000</v>
       </c>
       <c r="C3016" t="n">
-        <v>240000</v>
+        <v>241000</v>
       </c>
     </row>
     <row r="3017">
@@ -61632,10 +61632,10 @@
         <v>45584</v>
       </c>
       <c r="B3017" t="n">
-        <v>228000</v>
+        <v>227000</v>
       </c>
       <c r="C3017" t="n">
-        <v>228000</v>
+        <v>227000</v>
       </c>
     </row>
     <row r="3018">
@@ -61643,10 +61643,10 @@
         <v>45591</v>
       </c>
       <c r="B3018" t="n">
-        <v>218000</v>
+        <v>219000</v>
       </c>
       <c r="C3018" t="n">
-        <v>218000</v>
+        <v>219000</v>
       </c>
     </row>
     <row r="3019">
@@ -61665,10 +61665,10 @@
         <v>45605</v>
       </c>
       <c r="B3020" t="n">
-        <v>219000</v>
+        <v>218000</v>
       </c>
       <c r="C3020" t="n">
-        <v>219000</v>
+        <v>218000</v>
       </c>
     </row>
     <row r="3021">
@@ -61687,10 +61687,10 @@
         <v>45619</v>
       </c>
       <c r="B3022" t="n">
-        <v>216000</v>
+        <v>219000</v>
       </c>
       <c r="C3022" t="n">
-        <v>216000</v>
+        <v>219000</v>
       </c>
     </row>
     <row r="3023">
@@ -61698,10 +61698,10 @@
         <v>45626</v>
       </c>
       <c r="B3023" t="n">
-        <v>225000</v>
+        <v>222000</v>
       </c>
       <c r="C3023" t="n">
-        <v>225000</v>
+        <v>222000</v>
       </c>
     </row>
     <row r="3024">
@@ -61709,10 +61709,10 @@
         <v>45633</v>
       </c>
       <c r="B3024" t="n">
-        <v>239000</v>
+        <v>238000</v>
       </c>
       <c r="C3024" t="n">
-        <v>239000</v>
+        <v>238000</v>
       </c>
     </row>
     <row r="3025">
@@ -61742,10 +61742,10 @@
         <v>45654</v>
       </c>
       <c r="B3027" t="n">
-        <v>209000</v>
+        <v>212000</v>
       </c>
       <c r="C3027" t="n">
-        <v>209000</v>
+        <v>212000</v>
       </c>
     </row>
     <row r="3028">
@@ -61753,10 +61753,10 @@
         <v>45661</v>
       </c>
       <c r="B3028" t="n">
-        <v>205000</v>
+        <v>206000</v>
       </c>
       <c r="C3028" t="n">
-        <v>205000</v>
+        <v>206000</v>
       </c>
     </row>
     <row r="3029">
@@ -61764,10 +61764,10 @@
         <v>45668</v>
       </c>
       <c r="B3029" t="n">
-        <v>217000</v>
+        <v>219000</v>
       </c>
       <c r="C3029" t="n">
-        <v>217000</v>
+        <v>219000</v>
       </c>
     </row>
     <row r="3030">
@@ -61775,10 +61775,10 @@
         <v>45675</v>
       </c>
       <c r="B3030" t="n">
-        <v>222000</v>
+        <v>223000</v>
       </c>
       <c r="C3030" t="n">
-        <v>222000</v>
+        <v>223000</v>
       </c>
     </row>
     <row r="3031">
@@ -61786,10 +61786,10 @@
         <v>45682</v>
       </c>
       <c r="B3031" t="n">
-        <v>210000</v>
+        <v>212000</v>
       </c>
       <c r="C3031" t="n">
-        <v>210000</v>
+        <v>212000</v>
       </c>
     </row>
     <row r="3032">
@@ -61797,10 +61797,10 @@
         <v>45689</v>
       </c>
       <c r="B3032" t="n">
-        <v>222000</v>
+        <v>220000</v>
       </c>
       <c r="C3032" t="n">
-        <v>222000</v>
+        <v>220000</v>
       </c>
     </row>
     <row r="3033">
@@ -61808,10 +61808,10 @@
         <v>45696</v>
       </c>
       <c r="B3033" t="n">
-        <v>215000</v>
+        <v>216000</v>
       </c>
       <c r="C3033" t="n">
-        <v>215000</v>
+        <v>216000</v>
       </c>
     </row>
     <row r="3034">
@@ -61819,10 +61819,10 @@
         <v>45703</v>
       </c>
       <c r="B3034" t="n">
-        <v>224000</v>
+        <v>223000</v>
       </c>
       <c r="C3034" t="n">
-        <v>224000</v>
+        <v>223000</v>
       </c>
     </row>
     <row r="3035">
@@ -61830,10 +61830,10 @@
         <v>45710</v>
       </c>
       <c r="B3035" t="n">
-        <v>243000</v>
+        <v>241000</v>
       </c>
       <c r="C3035" t="n">
-        <v>243000</v>
+        <v>241000</v>
       </c>
     </row>
     <row r="3036">
@@ -61852,10 +61852,10 @@
         <v>45724</v>
       </c>
       <c r="B3037" t="n">
-        <v>223000</v>
+        <v>222000</v>
       </c>
       <c r="C3037" t="n">
-        <v>223000</v>
+        <v>222000</v>
       </c>
     </row>
     <row r="3038">
@@ -61874,10 +61874,10 @@
         <v>45738</v>
       </c>
       <c r="B3039" t="n">
-        <v>225000</v>
+        <v>224000</v>
       </c>
       <c r="C3039" t="n">
-        <v>225000</v>
+        <v>224000</v>
       </c>
     </row>
     <row r="3040">
@@ -61885,10 +61885,10 @@
         <v>45745</v>
       </c>
       <c r="B3040" t="n">
-        <v>219000</v>
+        <v>220000</v>
       </c>
       <c r="C3040" t="n">
-        <v>219000</v>
+        <v>220000</v>
       </c>
     </row>
     <row r="3041">
@@ -61896,10 +61896,10 @@
         <v>45752</v>
       </c>
       <c r="B3041" t="n">
-        <v>224000</v>
+        <v>223000</v>
       </c>
       <c r="C3041" t="n">
-        <v>224000</v>
+        <v>223000</v>
       </c>
     </row>
     <row r="3042">
@@ -61907,10 +61907,10 @@
         <v>45759</v>
       </c>
       <c r="B3042" t="n">
-        <v>216000</v>
+        <v>217000</v>
       </c>
       <c r="C3042" t="n">
-        <v>216000</v>
+        <v>217000</v>
       </c>
     </row>
     <row r="3043">
@@ -61918,10 +61918,10 @@
         <v>45766</v>
       </c>
       <c r="B3043" t="n">
-        <v>223000</v>
+        <v>224000</v>
       </c>
       <c r="C3043" t="n">
-        <v>223000</v>
+        <v>224000</v>
       </c>
     </row>
     <row r="3044">
@@ -61929,10 +61929,10 @@
         <v>45773</v>
       </c>
       <c r="B3044" t="n">
-        <v>241000</v>
+        <v>239000</v>
       </c>
       <c r="C3044" t="n">
-        <v>241000</v>
+        <v>239000</v>
       </c>
     </row>
     <row r="3045">
@@ -61940,10 +61940,10 @@
         <v>45780</v>
       </c>
       <c r="B3045" t="n">
-        <v>229000</v>
+        <v>228000</v>
       </c>
       <c r="C3045" t="n">
-        <v>229000</v>
+        <v>228000</v>
       </c>
     </row>
     <row r="3046">
@@ -61951,10 +61951,10 @@
         <v>45787</v>
       </c>
       <c r="B3046" t="n">
-        <v>228000</v>
+        <v>226000</v>
       </c>
       <c r="C3046" t="n">
-        <v>228000</v>
+        <v>226000</v>
       </c>
     </row>
     <row r="3047">
@@ -61962,10 +61962,10 @@
         <v>45794</v>
       </c>
       <c r="B3047" t="n">
-        <v>226000</v>
+        <v>225000</v>
       </c>
       <c r="C3047" t="n">
-        <v>226000</v>
+        <v>225000</v>
       </c>
     </row>
     <row r="3048">
@@ -61973,10 +61973,10 @@
         <v>45801</v>
       </c>
       <c r="B3048" t="n">
-        <v>239000</v>
+        <v>236000</v>
       </c>
       <c r="C3048" t="n">
-        <v>239000</v>
+        <v>236000</v>
       </c>
     </row>
     <row r="3049">
@@ -61984,10 +61984,10 @@
         <v>45808</v>
       </c>
       <c r="B3049" t="n">
-        <v>246000</v>
+        <v>244000</v>
       </c>
       <c r="C3049" t="n">
-        <v>246000</v>
+        <v>244000</v>
       </c>
     </row>
     <row r="3050">
@@ -61995,10 +61995,10 @@
         <v>45815</v>
       </c>
       <c r="B3050" t="n">
-        <v>248000</v>
+        <v>246000</v>
       </c>
       <c r="C3050" t="n">
-        <v>248000</v>
+        <v>246000</v>
       </c>
     </row>
     <row r="3051">
@@ -62006,10 +62006,10 @@
         <v>45822</v>
       </c>
       <c r="B3051" t="n">
-        <v>246000</v>
+        <v>243000</v>
       </c>
       <c r="C3051" t="n">
-        <v>246000</v>
+        <v>243000</v>
       </c>
     </row>
     <row r="3052">
@@ -62017,10 +62017,10 @@
         <v>45829</v>
       </c>
       <c r="B3052" t="n">
-        <v>237000</v>
+        <v>236000</v>
       </c>
       <c r="C3052" t="n">
-        <v>237000</v>
+        <v>236000</v>
       </c>
     </row>
     <row r="3053">
@@ -62028,10 +62028,10 @@
         <v>45836</v>
       </c>
       <c r="B3053" t="n">
-        <v>232000</v>
+        <v>231000</v>
       </c>
       <c r="C3053" t="n">
-        <v>232000</v>
+        <v>231000</v>
       </c>
     </row>
     <row r="3054">
@@ -62061,10 +62061,10 @@
         <v>45857</v>
       </c>
       <c r="B3056" t="n">
-        <v>217000</v>
+        <v>218000</v>
       </c>
       <c r="C3056" t="n">
-        <v>217000</v>
+        <v>218000</v>
       </c>
     </row>
     <row r="3057">
@@ -62083,10 +62083,10 @@
         <v>45871</v>
       </c>
       <c r="B3058" t="n">
-        <v>227000</v>
+        <v>226000</v>
       </c>
       <c r="C3058" t="n">
-        <v>227000</v>
+        <v>226000</v>
       </c>
     </row>
     <row r="3059">
@@ -62105,10 +62105,10 @@
         <v>45885</v>
       </c>
       <c r="B3060" t="n">
-        <v>234000</v>
+        <v>233000</v>
       </c>
       <c r="C3060" t="n">
-        <v>234000</v>
+        <v>233000</v>
       </c>
     </row>
     <row r="3061">
@@ -62138,10 +62138,10 @@
         <v>45906</v>
       </c>
       <c r="B3063" t="n">
-        <v>264000</v>
+        <v>259000</v>
       </c>
       <c r="C3063" t="n">
-        <v>264000</v>
+        <v>259000</v>
       </c>
     </row>
     <row r="3064">
@@ -62149,10 +62149,10 @@
         <v>45913</v>
       </c>
       <c r="B3064" t="n">
-        <v>232000</v>
+        <v>233000</v>
       </c>
       <c r="C3064" t="n">
-        <v>232000</v>
+        <v>233000</v>
       </c>
     </row>
     <row r="3065">
@@ -62171,10 +62171,10 @@
         <v>45927</v>
       </c>
       <c r="B3066" t="n">
-        <v>224000</v>
+        <v>225000</v>
       </c>
       <c r="C3066" t="n">
-        <v>224000</v>
+        <v>225000</v>
       </c>
     </row>
     <row r="3067">
@@ -62182,10 +62182,10 @@
         <v>45934</v>
       </c>
       <c r="B3067" t="n">
-        <v>235000</v>
+        <v>233000</v>
       </c>
       <c r="C3067" t="n">
-        <v>235000</v>
+        <v>233000</v>
       </c>
     </row>
     <row r="3068">
@@ -62193,10 +62193,10 @@
         <v>45941</v>
       </c>
       <c r="B3068" t="n">
-        <v>220000</v>
+        <v>222000</v>
       </c>
       <c r="C3068" t="n">
-        <v>220000</v>
+        <v>222000</v>
       </c>
     </row>
     <row r="3069">
@@ -62204,10 +62204,10 @@
         <v>45948</v>
       </c>
       <c r="B3069" t="n">
-        <v>232000</v>
+        <v>231000</v>
       </c>
       <c r="C3069" t="n">
-        <v>232000</v>
+        <v>231000</v>
       </c>
     </row>
     <row r="3070">
@@ -62215,10 +62215,10 @@
         <v>45955</v>
       </c>
       <c r="B3070" t="n">
-        <v>220000</v>
+        <v>221000</v>
       </c>
       <c r="C3070" t="n">
-        <v>220000</v>
+        <v>221000</v>
       </c>
     </row>
     <row r="3071">
@@ -62226,10 +62226,10 @@
         <v>45962</v>
       </c>
       <c r="B3071" t="n">
-        <v>229000</v>
+        <v>228000</v>
       </c>
       <c r="C3071" t="n">
-        <v>229000</v>
+        <v>228000</v>
       </c>
     </row>
     <row r="3072">
@@ -62259,10 +62259,10 @@
         <v>45983</v>
       </c>
       <c r="B3074" t="n">
-        <v>217000</v>
+        <v>218000</v>
       </c>
       <c r="C3074" t="n">
-        <v>217000</v>
+        <v>218000</v>
       </c>
     </row>
     <row r="3075">
@@ -62270,10 +62270,10 @@
         <v>45990</v>
       </c>
       <c r="B3075" t="n">
-        <v>192000</v>
+        <v>216000</v>
       </c>
       <c r="C3075" t="n">
-        <v>192000</v>
+        <v>216000</v>
       </c>
     </row>
     <row r="3076">
@@ -62281,10 +62281,10 @@
         <v>45997</v>
       </c>
       <c r="B3076" t="n">
-        <v>237000</v>
+        <v>235000</v>
       </c>
       <c r="C3076" t="n">
-        <v>237000</v>
+        <v>235000</v>
       </c>
     </row>
     <row r="3077">
@@ -62314,10 +62314,10 @@
         <v>46018</v>
       </c>
       <c r="B3079" t="n">
-        <v>200000</v>
+        <v>203000</v>
       </c>
       <c r="C3079" t="n">
-        <v>200000</v>
+        <v>203000</v>
       </c>
     </row>
     <row r="3080">
@@ -62336,10 +62336,10 @@
         <v>46032</v>
       </c>
       <c r="B3081" t="n">
-        <v>199000</v>
+        <v>201000</v>
       </c>
       <c r="C3081" t="n">
-        <v>199000</v>
+        <v>201000</v>
       </c>
     </row>
     <row r="3082">
@@ -62358,10 +62358,10 @@
         <v>46046</v>
       </c>
       <c r="B3083" t="n">
-        <v>209000</v>
+        <v>211000</v>
       </c>
       <c r="C3083" t="n">
-        <v>209000</v>
+        <v>211000</v>
       </c>
     </row>
     <row r="3084">
@@ -62369,10 +62369,10 @@
         <v>46053</v>
       </c>
       <c r="B3084" t="n">
-        <v>232000</v>
+        <v>230000</v>
       </c>
       <c r="C3084" t="n">
-        <v>232000</v>
+        <v>230000</v>
       </c>
     </row>
     <row r="3085">
@@ -62380,10 +62380,10 @@
         <v>46060</v>
       </c>
       <c r="B3085" t="n">
-        <v>229000</v>
+        <v>230000</v>
       </c>
       <c r="C3085" t="n">
-        <v>229000</v>
+        <v>230000</v>
       </c>
     </row>
     <row r="3086">
@@ -62402,10 +62402,10 @@
         <v>46074</v>
       </c>
       <c r="B3087" t="n">
-        <v>213000</v>
+        <v>211000</v>
       </c>
       <c r="C3087" t="n">
-        <v>213000</v>
+        <v>211000</v>
       </c>
     </row>
     <row r="3088">
@@ -62428,6 +62428,17 @@
       </c>
       <c r="C3089" t="n">
         <v>213000</v>
+      </c>
+    </row>
+    <row r="3090">
+      <c r="A3090" s="1" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B3090" t="n">
+        <v>205000</v>
+      </c>
+      <c r="C3090" t="n">
+        <v>205000</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -3831,7 +3831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C184"/>
+  <dimension ref="A1:C185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4952,10 +4952,10 @@
         <v>41640</v>
       </c>
       <c r="B138" t="n">
-        <v>11.883752</v>
+        <v>11.883755</v>
       </c>
       <c r="C138" t="n">
-        <v>11.883752</v>
+        <v>11.883755</v>
       </c>
     </row>
     <row r="139">
@@ -4963,10 +4963,10 @@
         <v>41730</v>
       </c>
       <c r="B139" t="n">
-        <v>11.62113</v>
+        <v>11.621135</v>
       </c>
       <c r="C139" t="n">
-        <v>11.62113</v>
+        <v>11.621135</v>
       </c>
     </row>
     <row r="140">
@@ -4974,10 +4974,10 @@
         <v>41821</v>
       </c>
       <c r="B140" t="n">
-        <v>11.646935</v>
+        <v>11.646939</v>
       </c>
       <c r="C140" t="n">
-        <v>11.646935</v>
+        <v>11.646939</v>
       </c>
     </row>
     <row r="141">
@@ -4985,10 +4985,10 @@
         <v>41913</v>
       </c>
       <c r="B141" t="n">
-        <v>11.631979</v>
+        <v>11.631985</v>
       </c>
       <c r="C141" t="n">
-        <v>11.631979</v>
+        <v>11.631985</v>
       </c>
     </row>
     <row r="142">
@@ -4996,10 +4996,10 @@
         <v>42005</v>
       </c>
       <c r="B142" t="n">
-        <v>11.556607</v>
+        <v>11.556623</v>
       </c>
       <c r="C142" t="n">
-        <v>11.556607</v>
+        <v>11.556623</v>
       </c>
     </row>
     <row r="143">
@@ -5007,10 +5007,10 @@
         <v>42095</v>
       </c>
       <c r="B143" t="n">
-        <v>11.485107</v>
+        <v>11.485132</v>
       </c>
       <c r="C143" t="n">
-        <v>11.485107</v>
+        <v>11.485132</v>
       </c>
     </row>
     <row r="144">
@@ -5018,10 +5018,10 @@
         <v>42186</v>
       </c>
       <c r="B144" t="n">
-        <v>11.606456</v>
+        <v>11.606478</v>
       </c>
       <c r="C144" t="n">
-        <v>11.606456</v>
+        <v>11.606478</v>
       </c>
     </row>
     <row r="145">
@@ -5029,10 +5029,10 @@
         <v>42278</v>
       </c>
       <c r="B145" t="n">
-        <v>11.738949</v>
+        <v>11.738968</v>
       </c>
       <c r="C145" t="n">
-        <v>11.738949</v>
+        <v>11.738968</v>
       </c>
     </row>
     <row r="146">
@@ -5040,10 +5040,10 @@
         <v>42370</v>
       </c>
       <c r="B146" t="n">
-        <v>11.763221</v>
+        <v>11.763236</v>
       </c>
       <c r="C146" t="n">
-        <v>11.763221</v>
+        <v>11.763236</v>
       </c>
     </row>
     <row r="147">
@@ -5051,10 +5051,10 @@
         <v>42461</v>
       </c>
       <c r="B147" t="n">
-        <v>11.766084</v>
+        <v>11.766097</v>
       </c>
       <c r="C147" t="n">
-        <v>11.766084</v>
+        <v>11.766097</v>
       </c>
     </row>
     <row r="148">
@@ -5062,10 +5062,10 @@
         <v>42552</v>
       </c>
       <c r="B148" t="n">
-        <v>11.769828</v>
+        <v>11.769843</v>
       </c>
       <c r="C148" t="n">
-        <v>11.769828</v>
+        <v>11.769843</v>
       </c>
     </row>
     <row r="149">
@@ -5073,10 +5073,10 @@
         <v>42644</v>
       </c>
       <c r="B149" t="n">
-        <v>11.865791</v>
+        <v>11.865809</v>
       </c>
       <c r="C149" t="n">
-        <v>11.865791</v>
+        <v>11.865809</v>
       </c>
     </row>
     <row r="150">
@@ -5084,10 +5084,10 @@
         <v>42736</v>
       </c>
       <c r="B150" t="n">
-        <v>11.723736</v>
+        <v>11.723754</v>
       </c>
       <c r="C150" t="n">
-        <v>11.723736</v>
+        <v>11.723754</v>
       </c>
     </row>
     <row r="151">
@@ -5095,10 +5095,10 @@
         <v>42826</v>
       </c>
       <c r="B151" t="n">
-        <v>11.756954</v>
+        <v>11.756978</v>
       </c>
       <c r="C151" t="n">
-        <v>11.756954</v>
+        <v>11.756978</v>
       </c>
     </row>
     <row r="152">
@@ -5106,10 +5106,10 @@
         <v>42917</v>
       </c>
       <c r="B152" t="n">
-        <v>11.818405</v>
+        <v>11.818432</v>
       </c>
       <c r="C152" t="n">
-        <v>11.818405</v>
+        <v>11.818432</v>
       </c>
     </row>
     <row r="153">
@@ -5117,10 +5117,10 @@
         <v>43009</v>
       </c>
       <c r="B153" t="n">
-        <v>11.816674</v>
+        <v>11.816692</v>
       </c>
       <c r="C153" t="n">
-        <v>11.816674</v>
+        <v>11.816692</v>
       </c>
     </row>
     <row r="154">
@@ -5128,10 +5128,10 @@
         <v>43101</v>
       </c>
       <c r="B154" t="n">
-        <v>11.644543</v>
+        <v>11.644577</v>
       </c>
       <c r="C154" t="n">
-        <v>11.644543</v>
+        <v>11.644577</v>
       </c>
     </row>
     <row r="155">
@@ -5139,10 +5139,10 @@
         <v>43191</v>
       </c>
       <c r="B155" t="n">
-        <v>11.598347</v>
+        <v>11.598376</v>
       </c>
       <c r="C155" t="n">
-        <v>11.598347</v>
+        <v>11.598376</v>
       </c>
     </row>
     <row r="156">
@@ -5150,10 +5150,10 @@
         <v>43282</v>
       </c>
       <c r="B156" t="n">
-        <v>11.619544</v>
+        <v>11.619565</v>
       </c>
       <c r="C156" t="n">
-        <v>11.619544</v>
+        <v>11.619565</v>
       </c>
     </row>
     <row r="157">
@@ -5161,10 +5161,10 @@
         <v>43374</v>
       </c>
       <c r="B157" t="n">
-        <v>11.666352</v>
+        <v>11.666399</v>
       </c>
       <c r="C157" t="n">
-        <v>11.666352</v>
+        <v>11.666399</v>
       </c>
     </row>
     <row r="158">
@@ -5172,10 +5172,10 @@
         <v>43466</v>
       </c>
       <c r="B158" t="n">
-        <v>11.499875</v>
+        <v>11.499899</v>
       </c>
       <c r="C158" t="n">
-        <v>11.499875</v>
+        <v>11.499899</v>
       </c>
     </row>
     <row r="159">
@@ -5183,10 +5183,10 @@
         <v>43556</v>
       </c>
       <c r="B159" t="n">
-        <v>11.626957</v>
+        <v>11.626984</v>
       </c>
       <c r="C159" t="n">
-        <v>11.626957</v>
+        <v>11.626984</v>
       </c>
     </row>
     <row r="160">
@@ -5194,10 +5194,10 @@
         <v>43647</v>
       </c>
       <c r="B160" t="n">
-        <v>11.646529</v>
+        <v>11.646573</v>
       </c>
       <c r="C160" t="n">
-        <v>11.646529</v>
+        <v>11.646573</v>
       </c>
     </row>
     <row r="161">
@@ -5205,10 +5205,10 @@
         <v>43739</v>
       </c>
       <c r="B161" t="n">
-        <v>11.727541</v>
+        <v>11.727611</v>
       </c>
       <c r="C161" t="n">
-        <v>11.727541</v>
+        <v>11.727611</v>
       </c>
     </row>
     <row r="162">
@@ -5216,10 +5216,10 @@
         <v>43831</v>
       </c>
       <c r="B162" t="n">
-        <v>11.591065</v>
+        <v>11.591122</v>
       </c>
       <c r="C162" t="n">
-        <v>11.591065</v>
+        <v>11.591122</v>
       </c>
     </row>
     <row r="163">
@@ -5227,10 +5227,10 @@
         <v>43922</v>
       </c>
       <c r="B163" t="n">
-        <v>9.739786</v>
+        <v>9.739837</v>
       </c>
       <c r="C163" t="n">
-        <v>9.739786</v>
+        <v>9.739837</v>
       </c>
     </row>
     <row r="164">
@@ -5238,10 +5238,10 @@
         <v>44013</v>
       </c>
       <c r="B164" t="n">
-        <v>10.058434</v>
+        <v>10.058475</v>
       </c>
       <c r="C164" t="n">
-        <v>10.058434</v>
+        <v>10.058475</v>
       </c>
     </row>
     <row r="165">
@@ -5249,10 +5249,10 @@
         <v>44105</v>
       </c>
       <c r="B165" t="n">
-        <v>10.389279</v>
+        <v>10.389341</v>
       </c>
       <c r="C165" t="n">
-        <v>10.389279</v>
+        <v>10.389341</v>
       </c>
     </row>
     <row r="166">
@@ -5260,10 +5260,10 @@
         <v>44197</v>
       </c>
       <c r="B166" t="n">
-        <v>9.051398000000001</v>
+        <v>9.051425999999999</v>
       </c>
       <c r="C166" t="n">
-        <v>9.051398000000001</v>
+        <v>9.051425999999999</v>
       </c>
     </row>
     <row r="167">
@@ -5271,10 +5271,10 @@
         <v>44287</v>
       </c>
       <c r="B167" t="n">
-        <v>9.840935999999999</v>
+        <v>9.840987999999999</v>
       </c>
       <c r="C167" t="n">
-        <v>9.840935999999999</v>
+        <v>9.840987999999999</v>
       </c>
     </row>
     <row r="168">
@@ -5282,10 +5282,10 @@
         <v>44378</v>
       </c>
       <c r="B168" t="n">
-        <v>10.009535</v>
+        <v>10.009574</v>
       </c>
       <c r="C168" t="n">
-        <v>10.009535</v>
+        <v>10.009574</v>
       </c>
     </row>
     <row r="169">
@@ -5293,10 +5293,10 @@
         <v>44470</v>
       </c>
       <c r="B169" t="n">
-        <v>10.228733</v>
+        <v>10.228773</v>
       </c>
       <c r="C169" t="n">
-        <v>10.228733</v>
+        <v>10.228773</v>
       </c>
     </row>
     <row r="170">
@@ -5304,10 +5304,10 @@
         <v>44562</v>
       </c>
       <c r="B170" t="n">
-        <v>10.47232</v>
+        <v>10.472376</v>
       </c>
       <c r="C170" t="n">
-        <v>10.47232</v>
+        <v>10.472376</v>
       </c>
     </row>
     <row r="171">
@@ -5315,10 +5315,10 @@
         <v>44652</v>
       </c>
       <c r="B171" t="n">
-        <v>10.684637</v>
+        <v>10.684715</v>
       </c>
       <c r="C171" t="n">
-        <v>10.684637</v>
+        <v>10.684715</v>
       </c>
     </row>
     <row r="172">
@@ -5326,10 +5326,10 @@
         <v>44743</v>
       </c>
       <c r="B172" t="n">
-        <v>10.567735</v>
+        <v>10.567813</v>
       </c>
       <c r="C172" t="n">
-        <v>10.567735</v>
+        <v>10.567813</v>
       </c>
     </row>
     <row r="173">
@@ -5337,10 +5337,10 @@
         <v>44835</v>
       </c>
       <c r="B173" t="n">
-        <v>10.736833</v>
+        <v>10.736908</v>
       </c>
       <c r="C173" t="n">
-        <v>10.736833</v>
+        <v>10.736908</v>
       </c>
     </row>
     <row r="174">
@@ -5348,10 +5348,10 @@
         <v>44927</v>
       </c>
       <c r="B174" t="n">
-        <v>10.56399</v>
+        <v>10.564065</v>
       </c>
       <c r="C174" t="n">
-        <v>10.56399</v>
+        <v>10.564065</v>
       </c>
     </row>
     <row r="175">
@@ -5359,10 +5359,10 @@
         <v>45017</v>
       </c>
       <c r="B175" t="n">
-        <v>10.576866</v>
+        <v>10.576964</v>
       </c>
       <c r="C175" t="n">
-        <v>10.576866</v>
+        <v>10.576964</v>
       </c>
     </row>
     <row r="176">
@@ -5370,10 +5370,10 @@
         <v>45108</v>
       </c>
       <c r="B176" t="n">
-        <v>10.747704</v>
+        <v>10.747803</v>
       </c>
       <c r="C176" t="n">
-        <v>10.747704</v>
+        <v>10.747803</v>
       </c>
     </row>
     <row r="177">
@@ -5381,10 +5381,10 @@
         <v>45200</v>
       </c>
       <c r="B177" t="n">
-        <v>11.095984</v>
+        <v>11.096103</v>
       </c>
       <c r="C177" t="n">
-        <v>11.095984</v>
+        <v>11.096103</v>
       </c>
     </row>
     <row r="178">
@@ -5392,10 +5392,10 @@
         <v>45292</v>
       </c>
       <c r="B178" t="n">
-        <v>11.058721</v>
+        <v>11.058844</v>
       </c>
       <c r="C178" t="n">
-        <v>11.058721</v>
+        <v>11.058844</v>
       </c>
     </row>
     <row r="179">
@@ -5403,10 +5403,10 @@
         <v>45383</v>
       </c>
       <c r="B179" t="n">
-        <v>11.019084</v>
+        <v>11.0193</v>
       </c>
       <c r="C179" t="n">
-        <v>11.019084</v>
+        <v>11.0193</v>
       </c>
     </row>
     <row r="180">
@@ -5414,10 +5414,10 @@
         <v>45474</v>
       </c>
       <c r="B180" t="n">
-        <v>11.138535</v>
+        <v>11.138746</v>
       </c>
       <c r="C180" t="n">
-        <v>11.138535</v>
+        <v>11.138746</v>
       </c>
     </row>
     <row r="181">
@@ -5425,10 +5425,10 @@
         <v>45566</v>
       </c>
       <c r="B181" t="n">
-        <v>11.12225</v>
+        <v>11.122474</v>
       </c>
       <c r="C181" t="n">
-        <v>11.12225</v>
+        <v>11.122474</v>
       </c>
     </row>
     <row r="182">
@@ -5436,10 +5436,10 @@
         <v>45658</v>
       </c>
       <c r="B182" t="n">
-        <v>11.10531</v>
+        <v>11.105374</v>
       </c>
       <c r="C182" t="n">
-        <v>11.10531</v>
+        <v>11.105374</v>
       </c>
     </row>
     <row r="183">
@@ -5447,10 +5447,10 @@
         <v>45748</v>
       </c>
       <c r="B183" t="n">
-        <v>11.123837</v>
+        <v>11.124175</v>
       </c>
       <c r="C183" t="n">
-        <v>11.123837</v>
+        <v>11.124175</v>
       </c>
     </row>
     <row r="184">
@@ -5458,10 +5458,21 @@
         <v>45839</v>
       </c>
       <c r="B184" t="n">
-        <v>11.256338</v>
+        <v>11.257951</v>
       </c>
       <c r="C184" t="n">
-        <v>11.256338</v>
+        <v>11.257951</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B185" t="n">
+        <v>11.323096</v>
+      </c>
+      <c r="C185" t="n">
+        <v>11.323096</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -28453,7 +28453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3090"/>
+  <dimension ref="A1:C3091"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62450,6 +62450,17 @@
       </c>
       <c r="C3090" t="n">
         <v>205000</v>
+      </c>
+    </row>
+    <row r="3091">
+      <c r="A3091" s="1" t="n">
+        <v>46102</v>
+      </c>
+      <c r="B3091" t="n">
+        <v>210000</v>
+      </c>
+      <c r="C3091" t="n">
+        <v>210000</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -14755,7 +14755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C303"/>
+  <dimension ref="A1:C304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18091,10 +18091,21 @@
         <v>46023</v>
       </c>
       <c r="B303" t="n">
-        <v>6946</v>
+        <v>7240</v>
       </c>
       <c r="C303" t="n">
-        <v>6.946</v>
+        <v>7.24</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B304" t="n">
+        <v>6882</v>
+      </c>
+      <c r="C304" t="n">
+        <v>6.882</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -18119,7 +18119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C939"/>
+  <dimension ref="A1:C940"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28451,6 +28451,17 @@
       </c>
       <c r="C939" t="n">
         <v>4.4</v>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B940" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C940" t="n">
+        <v>4.3</v>
       </c>
     </row>
   </sheetData>
@@ -28464,7 +28475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3091"/>
+  <dimension ref="A1:C3092"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62468,10 +62479,21 @@
         <v>46102</v>
       </c>
       <c r="B3091" t="n">
-        <v>210000</v>
+        <v>211000</v>
       </c>
       <c r="C3091" t="n">
-        <v>210000</v>
+        <v>211000</v>
+      </c>
+    </row>
+    <row r="3092">
+      <c r="A3092" s="1" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B3092" t="n">
+        <v>202000</v>
+      </c>
+      <c r="C3092" t="n">
+        <v>202000</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -7057,7 +7057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C698"/>
+  <dimension ref="A1:C699"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13418,10 +13418,10 @@
         <v>42370</v>
       </c>
       <c r="B578" t="n">
-        <v>903594.77</v>
+        <v>903391.27</v>
       </c>
       <c r="C578" t="n">
-        <v>903594.77</v>
+        <v>903391.27</v>
       </c>
     </row>
     <row r="579">
@@ -13429,10 +13429,10 @@
         <v>42401</v>
       </c>
       <c r="B579" t="n">
-        <v>907604.1800000001</v>
+        <v>907247.9399999999</v>
       </c>
       <c r="C579" t="n">
-        <v>907604.1800000001</v>
+        <v>907247.9399999999</v>
       </c>
     </row>
     <row r="580">
@@ -13440,10 +13440,10 @@
         <v>42430</v>
       </c>
       <c r="B580" t="n">
-        <v>919221.85</v>
+        <v>920927.83</v>
       </c>
       <c r="C580" t="n">
-        <v>919221.85</v>
+        <v>920927.83</v>
       </c>
     </row>
     <row r="581">
@@ -13451,10 +13451,10 @@
         <v>42461</v>
       </c>
       <c r="B581" t="n">
-        <v>924099.12</v>
+        <v>926777.5699999999</v>
       </c>
       <c r="C581" t="n">
-        <v>924099.12</v>
+        <v>926777.5699999999</v>
       </c>
     </row>
     <row r="582">
@@ -13462,10 +13462,10 @@
         <v>42491</v>
       </c>
       <c r="B582" t="n">
-        <v>926988.16</v>
+        <v>926207.9300000001</v>
       </c>
       <c r="C582" t="n">
-        <v>926988.16</v>
+        <v>926207.9300000001</v>
       </c>
     </row>
     <row r="583">
@@ -13473,10 +13473,10 @@
         <v>42522</v>
       </c>
       <c r="B583" t="n">
-        <v>934770.98</v>
+        <v>934914.74</v>
       </c>
       <c r="C583" t="n">
-        <v>934770.98</v>
+        <v>934914.74</v>
       </c>
     </row>
     <row r="584">
@@ -13484,10 +13484,10 @@
         <v>42552</v>
       </c>
       <c r="B584" t="n">
-        <v>940192.76</v>
+        <v>940893.83</v>
       </c>
       <c r="C584" t="n">
-        <v>940192.76</v>
+        <v>940893.83</v>
       </c>
     </row>
     <row r="585">
@@ -13495,10 +13495,10 @@
         <v>42583</v>
       </c>
       <c r="B585" t="n">
-        <v>945126.03</v>
+        <v>945450.2</v>
       </c>
       <c r="C585" t="n">
-        <v>945126.03</v>
+        <v>945450.2</v>
       </c>
     </row>
     <row r="586">
@@ -13506,10 +13506,10 @@
         <v>42614</v>
       </c>
       <c r="B586" t="n">
-        <v>949069.8</v>
+        <v>950383.25</v>
       </c>
       <c r="C586" t="n">
-        <v>949069.8</v>
+        <v>950383.25</v>
       </c>
     </row>
     <row r="587">
@@ -13517,10 +13517,10 @@
         <v>42644</v>
       </c>
       <c r="B587" t="n">
-        <v>949948.1800000001</v>
+        <v>949019.77</v>
       </c>
       <c r="C587" t="n">
-        <v>949948.1800000001</v>
+        <v>949019.77</v>
       </c>
     </row>
     <row r="588">
@@ -13528,10 +13528,10 @@
         <v>42675</v>
       </c>
       <c r="B588" t="n">
-        <v>954415.47</v>
+        <v>953427.45</v>
       </c>
       <c r="C588" t="n">
-        <v>954415.47</v>
+        <v>953427.45</v>
       </c>
     </row>
     <row r="589">
@@ -13550,10 +13550,10 @@
         <v>42736</v>
       </c>
       <c r="B590" t="n">
-        <v>963467.38</v>
+        <v>963412.14</v>
       </c>
       <c r="C590" t="n">
-        <v>963467.38</v>
+        <v>963412.14</v>
       </c>
     </row>
     <row r="591">
@@ -13561,10 +13561,10 @@
         <v>42767</v>
       </c>
       <c r="B591" t="n">
-        <v>969320.8199999999</v>
+        <v>969194.1899999999</v>
       </c>
       <c r="C591" t="n">
-        <v>969320.8199999999</v>
+        <v>969194.1899999999</v>
       </c>
     </row>
     <row r="592">
@@ -13572,10 +13572,10 @@
         <v>42795</v>
       </c>
       <c r="B592" t="n">
-        <v>973860.13</v>
+        <v>974868.85</v>
       </c>
       <c r="C592" t="n">
-        <v>973860.13</v>
+        <v>974868.85</v>
       </c>
     </row>
     <row r="593">
@@ -13583,10 +13583,10 @@
         <v>42826</v>
       </c>
       <c r="B593" t="n">
-        <v>976395.9300000001</v>
+        <v>978104.15</v>
       </c>
       <c r="C593" t="n">
-        <v>976395.9300000001</v>
+        <v>978104.15</v>
       </c>
     </row>
     <row r="594">
@@ -13594,10 +13594,10 @@
         <v>42856</v>
       </c>
       <c r="B594" t="n">
-        <v>980809.9</v>
+        <v>980279.99</v>
       </c>
       <c r="C594" t="n">
-        <v>980809.9</v>
+        <v>980279.99</v>
       </c>
     </row>
     <row r="595">
@@ -13605,10 +13605,10 @@
         <v>42887</v>
       </c>
       <c r="B595" t="n">
-        <v>984955.36</v>
+        <v>985028.53</v>
       </c>
       <c r="C595" t="n">
-        <v>984955.36</v>
+        <v>985028.53</v>
       </c>
     </row>
     <row r="596">
@@ -13616,10 +13616,10 @@
         <v>42917</v>
       </c>
       <c r="B596" t="n">
-        <v>987546.5699999999</v>
+        <v>988170.45</v>
       </c>
       <c r="C596" t="n">
-        <v>987546.5699999999</v>
+        <v>988170.45</v>
       </c>
     </row>
     <row r="597">
@@ -13627,10 +13627,10 @@
         <v>42948</v>
       </c>
       <c r="B597" t="n">
-        <v>992084.83</v>
+        <v>992523.1</v>
       </c>
       <c r="C597" t="n">
-        <v>992084.83</v>
+        <v>992523.1</v>
       </c>
     </row>
     <row r="598">
@@ -13638,10 +13638,10 @@
         <v>42979</v>
       </c>
       <c r="B598" t="n">
-        <v>997799.58</v>
+        <v>998846.97</v>
       </c>
       <c r="C598" t="n">
-        <v>997799.58</v>
+        <v>998846.97</v>
       </c>
     </row>
     <row r="599">
@@ -13649,10 +13649,10 @@
         <v>43009</v>
       </c>
       <c r="B599" t="n">
-        <v>1006228.68</v>
+        <v>1005844.63</v>
       </c>
       <c r="C599" t="n">
-        <v>1006228.68</v>
+        <v>1005844.63</v>
       </c>
     </row>
     <row r="600">
@@ -13660,10 +13660,10 @@
         <v>43040</v>
       </c>
       <c r="B600" t="n">
-        <v>1012316.89</v>
+        <v>1011810.7</v>
       </c>
       <c r="C600" t="n">
-        <v>1012316.89</v>
+        <v>1011810.7</v>
       </c>
     </row>
     <row r="601">
@@ -13682,10 +13682,10 @@
         <v>43101</v>
       </c>
       <c r="B602" t="n">
-        <v>1022731</v>
+        <v>1022645.86</v>
       </c>
       <c r="C602" t="n">
-        <v>1022731</v>
+        <v>1022645.86</v>
       </c>
     </row>
     <row r="603">
@@ -13693,10 +13693,10 @@
         <v>43132</v>
       </c>
       <c r="B603" t="n">
-        <v>1024980.99</v>
+        <v>1024831.9</v>
       </c>
       <c r="C603" t="n">
-        <v>1024980.99</v>
+        <v>1024831.9</v>
       </c>
     </row>
     <row r="604">
@@ -13704,10 +13704,10 @@
         <v>43160</v>
       </c>
       <c r="B604" t="n">
-        <v>1028817.4</v>
+        <v>1028766.03</v>
       </c>
       <c r="C604" t="n">
-        <v>1028817.4</v>
+        <v>1028766.03</v>
       </c>
     </row>
     <row r="605">
@@ -13715,10 +13715,10 @@
         <v>43191</v>
       </c>
       <c r="B605" t="n">
-        <v>1024656.62</v>
+        <v>1025126.26</v>
       </c>
       <c r="C605" t="n">
-        <v>1024656.62</v>
+        <v>1025126.26</v>
       </c>
     </row>
     <row r="606">
@@ -13726,10 +13726,10 @@
         <v>43221</v>
       </c>
       <c r="B606" t="n">
-        <v>1027724.28</v>
+        <v>1027283.18</v>
       </c>
       <c r="C606" t="n">
-        <v>1027724.28</v>
+        <v>1027283.18</v>
       </c>
     </row>
     <row r="607">
@@ -13737,10 +13737,10 @@
         <v>43252</v>
       </c>
       <c r="B607" t="n">
-        <v>1025345.59</v>
+        <v>1025346.97</v>
       </c>
       <c r="C607" t="n">
-        <v>1025345.59</v>
+        <v>1025346.97</v>
       </c>
     </row>
     <row r="608">
@@ -13748,10 +13748,10 @@
         <v>43282</v>
       </c>
       <c r="B608" t="n">
-        <v>1035337.56</v>
+        <v>1035824.78</v>
       </c>
       <c r="C608" t="n">
-        <v>1035337.56</v>
+        <v>1035824.78</v>
       </c>
     </row>
     <row r="609">
@@ -13759,10 +13759,10 @@
         <v>43313</v>
       </c>
       <c r="B609" t="n">
-        <v>1042014.05</v>
+        <v>1042274.79</v>
       </c>
       <c r="C609" t="n">
-        <v>1042014.05</v>
+        <v>1042274.79</v>
       </c>
     </row>
     <row r="610">
@@ -13770,10 +13770,10 @@
         <v>43344</v>
       </c>
       <c r="B610" t="n">
-        <v>1043901.27</v>
+        <v>1044435.9</v>
       </c>
       <c r="C610" t="n">
-        <v>1043901.27</v>
+        <v>1044435.9</v>
       </c>
     </row>
     <row r="611">
@@ -13781,10 +13781,10 @@
         <v>43374</v>
       </c>
       <c r="B611" t="n">
-        <v>1050366.36</v>
+        <v>1050200.23</v>
       </c>
       <c r="C611" t="n">
-        <v>1050366.36</v>
+        <v>1050200.23</v>
       </c>
     </row>
     <row r="612">
@@ -13792,10 +13792,10 @@
         <v>43405</v>
       </c>
       <c r="B612" t="n">
-        <v>1052545.16</v>
+        <v>1052273.29</v>
       </c>
       <c r="C612" t="n">
-        <v>1052545.16</v>
+        <v>1052273.29</v>
       </c>
     </row>
     <row r="613">
@@ -13814,10 +13814,10 @@
         <v>43466</v>
       </c>
       <c r="B614" t="n">
-        <v>1061026.63</v>
+        <v>1060871.35</v>
       </c>
       <c r="C614" t="n">
-        <v>1061026.63</v>
+        <v>1060871.35</v>
       </c>
     </row>
     <row r="615">
@@ -13825,10 +13825,10 @@
         <v>43497</v>
       </c>
       <c r="B615" t="n">
-        <v>1063376.27</v>
+        <v>1063152.34</v>
       </c>
       <c r="C615" t="n">
-        <v>1063376.27</v>
+        <v>1063152.34</v>
       </c>
     </row>
     <row r="616">
@@ -13836,10 +13836,10 @@
         <v>43525</v>
       </c>
       <c r="B616" t="n">
-        <v>1064354.25</v>
+        <v>1063183.99</v>
       </c>
       <c r="C616" t="n">
-        <v>1064354.25</v>
+        <v>1063183.99</v>
       </c>
     </row>
     <row r="617">
@@ -13847,10 +13847,10 @@
         <v>43556</v>
       </c>
       <c r="B617" t="n">
-        <v>1070714.69</v>
+        <v>1069911.76</v>
       </c>
       <c r="C617" t="n">
-        <v>1070714.69</v>
+        <v>1069911.76</v>
       </c>
     </row>
     <row r="618">
@@ -13858,10 +13858,10 @@
         <v>43586</v>
       </c>
       <c r="B618" t="n">
-        <v>1073802.25</v>
+        <v>1073219.5</v>
       </c>
       <c r="C618" t="n">
-        <v>1073802.25</v>
+        <v>1073219.5</v>
       </c>
     </row>
     <row r="619">
@@ -13869,10 +13869,10 @@
         <v>43617</v>
       </c>
       <c r="B619" t="n">
-        <v>1071552.07</v>
+        <v>1071356.44</v>
       </c>
       <c r="C619" t="n">
-        <v>1071552.07</v>
+        <v>1071356.44</v>
       </c>
     </row>
     <row r="620">
@@ -13880,10 +13880,10 @@
         <v>43647</v>
       </c>
       <c r="B620" t="n">
-        <v>1082456.83</v>
+        <v>1082725.64</v>
       </c>
       <c r="C620" t="n">
-        <v>1082456.83</v>
+        <v>1082725.64</v>
       </c>
     </row>
     <row r="621">
@@ -13891,10 +13891,10 @@
         <v>43678</v>
       </c>
       <c r="B621" t="n">
-        <v>1084000.01</v>
+        <v>1084058.65</v>
       </c>
       <c r="C621" t="n">
-        <v>1084000.01</v>
+        <v>1084058.65</v>
       </c>
     </row>
     <row r="622">
@@ -13902,10 +13902,10 @@
         <v>43709</v>
       </c>
       <c r="B622" t="n">
-        <v>1084190</v>
+        <v>1084272.68</v>
       </c>
       <c r="C622" t="n">
-        <v>1084190</v>
+        <v>1084272.68</v>
       </c>
     </row>
     <row r="623">
@@ -13913,10 +13913,10 @@
         <v>43739</v>
       </c>
       <c r="B623" t="n">
-        <v>1087314.72</v>
+        <v>1087260.79</v>
       </c>
       <c r="C623" t="n">
-        <v>1087314.72</v>
+        <v>1087260.79</v>
       </c>
     </row>
     <row r="624">
@@ -13924,10 +13924,10 @@
         <v>43770</v>
       </c>
       <c r="B624" t="n">
-        <v>1077376.27</v>
+        <v>1077235.11</v>
       </c>
       <c r="C624" t="n">
-        <v>1077376.27</v>
+        <v>1077235.11</v>
       </c>
     </row>
     <row r="625">
@@ -13946,10 +13946,10 @@
         <v>43831</v>
       </c>
       <c r="B626" t="n">
-        <v>1076357.79</v>
+        <v>1076066.6</v>
       </c>
       <c r="C626" t="n">
-        <v>1076357.79</v>
+        <v>1076066.6</v>
       </c>
     </row>
     <row r="627">
@@ -13957,10 +13957,10 @@
         <v>43862</v>
       </c>
       <c r="B627" t="n">
-        <v>1081958.19</v>
+        <v>1081538.96</v>
       </c>
       <c r="C627" t="n">
-        <v>1081958.19</v>
+        <v>1081538.96</v>
       </c>
     </row>
     <row r="628">
@@ -13968,10 +13968,10 @@
         <v>43891</v>
       </c>
       <c r="B628" t="n">
-        <v>1064082.5</v>
+        <v>1062207.46</v>
       </c>
       <c r="C628" t="n">
-        <v>1064082.5</v>
+        <v>1062207.46</v>
       </c>
     </row>
     <row r="629">
@@ -13979,10 +13979,10 @@
         <v>43922</v>
       </c>
       <c r="B629" t="n">
-        <v>1006627.91</v>
+        <v>1005102.9</v>
       </c>
       <c r="C629" t="n">
-        <v>1006627.91</v>
+        <v>1005102.9</v>
       </c>
     </row>
     <row r="630">
@@ -13990,10 +13990,10 @@
         <v>43952</v>
       </c>
       <c r="B630" t="n">
-        <v>981248.2</v>
+        <v>980419.13</v>
       </c>
       <c r="C630" t="n">
-        <v>981248.2</v>
+        <v>980419.13</v>
       </c>
     </row>
     <row r="631">
@@ -14001,10 +14001,10 @@
         <v>43983</v>
       </c>
       <c r="B631" t="n">
-        <v>973899.96</v>
+        <v>973452.87</v>
       </c>
       <c r="C631" t="n">
-        <v>973899.96</v>
+        <v>973452.87</v>
       </c>
     </row>
     <row r="632">
@@ -14012,10 +14012,10 @@
         <v>44013</v>
       </c>
       <c r="B632" t="n">
-        <v>971278.7</v>
+        <v>971303.2</v>
       </c>
       <c r="C632" t="n">
-        <v>971278.7</v>
+        <v>971303.2</v>
       </c>
     </row>
     <row r="633">
@@ -14023,10 +14023,10 @@
         <v>44044</v>
       </c>
       <c r="B633" t="n">
-        <v>961509.24</v>
+        <v>961387.23</v>
       </c>
       <c r="C633" t="n">
-        <v>961509.24</v>
+        <v>961387.23</v>
       </c>
     </row>
     <row r="634">
@@ -14034,10 +14034,10 @@
         <v>44075</v>
       </c>
       <c r="B634" t="n">
-        <v>964464.42</v>
+        <v>964357.67</v>
       </c>
       <c r="C634" t="n">
-        <v>964464.42</v>
+        <v>964357.67</v>
       </c>
     </row>
     <row r="635">
@@ -14045,10 +14045,10 @@
         <v>44105</v>
       </c>
       <c r="B635" t="n">
-        <v>961074.1800000001</v>
+        <v>961050.49</v>
       </c>
       <c r="C635" t="n">
-        <v>961074.1800000001</v>
+        <v>961050.49</v>
       </c>
     </row>
     <row r="636">
@@ -14056,10 +14056,10 @@
         <v>44136</v>
       </c>
       <c r="B636" t="n">
-        <v>953306.86</v>
+        <v>953267.65</v>
       </c>
       <c r="C636" t="n">
-        <v>953306.86</v>
+        <v>953267.65</v>
       </c>
     </row>
     <row r="637">
@@ -14078,10 +14078,10 @@
         <v>44197</v>
       </c>
       <c r="B638" t="n">
-        <v>951790.91</v>
+        <v>951410.1</v>
       </c>
       <c r="C638" t="n">
-        <v>951790.91</v>
+        <v>951410.1</v>
       </c>
     </row>
     <row r="639">
@@ -14089,10 +14089,10 @@
         <v>44228</v>
       </c>
       <c r="B639" t="n">
-        <v>955872.65</v>
+        <v>955382.3100000001</v>
       </c>
       <c r="C639" t="n">
-        <v>955872.65</v>
+        <v>955382.3100000001</v>
       </c>
     </row>
     <row r="640">
@@ -14100,10 +14100,10 @@
         <v>44256</v>
       </c>
       <c r="B640" t="n">
-        <v>954267.4</v>
+        <v>952080.8</v>
       </c>
       <c r="C640" t="n">
-        <v>954267.4</v>
+        <v>952080.8</v>
       </c>
     </row>
     <row r="641">
@@ -14111,10 +14111,10 @@
         <v>44287</v>
       </c>
       <c r="B641" t="n">
-        <v>953948.77</v>
+        <v>952144.46</v>
       </c>
       <c r="C641" t="n">
-        <v>953948.77</v>
+        <v>952144.46</v>
       </c>
     </row>
     <row r="642">
@@ -14122,10 +14122,10 @@
         <v>44317</v>
       </c>
       <c r="B642" t="n">
-        <v>961471.41</v>
+        <v>960451.8</v>
       </c>
       <c r="C642" t="n">
-        <v>961471.41</v>
+        <v>960451.8</v>
       </c>
     </row>
     <row r="643">
@@ -14133,10 +14133,10 @@
         <v>44348</v>
       </c>
       <c r="B643" t="n">
-        <v>986122.27</v>
+        <v>985552.64</v>
       </c>
       <c r="C643" t="n">
-        <v>986122.27</v>
+        <v>985552.64</v>
       </c>
     </row>
     <row r="644">
@@ -14144,10 +14144,10 @@
         <v>44378</v>
       </c>
       <c r="B644" t="n">
-        <v>990643.76</v>
+        <v>990634.8199999999</v>
       </c>
       <c r="C644" t="n">
-        <v>990643.76</v>
+        <v>990634.8199999999</v>
       </c>
     </row>
     <row r="645">
@@ -14155,10 +14155,10 @@
         <v>44409</v>
       </c>
       <c r="B645" t="n">
-        <v>994001.28</v>
+        <v>994035.02</v>
       </c>
       <c r="C645" t="n">
-        <v>994001.28</v>
+        <v>994035.02</v>
       </c>
     </row>
     <row r="646">
@@ -14166,10 +14166,10 @@
         <v>44440</v>
       </c>
       <c r="B646" t="n">
-        <v>1005332.86</v>
+        <v>1005471.37</v>
       </c>
       <c r="C646" t="n">
-        <v>1005332.86</v>
+        <v>1005471.37</v>
       </c>
     </row>
     <row r="647">
@@ -14177,10 +14177,10 @@
         <v>44470</v>
       </c>
       <c r="B647" t="n">
-        <v>1013373.01</v>
+        <v>1013717.84</v>
       </c>
       <c r="C647" t="n">
-        <v>1013373.01</v>
+        <v>1013717.84</v>
       </c>
     </row>
     <row r="648">
@@ -14188,10 +14188,10 @@
         <v>44501</v>
       </c>
       <c r="B648" t="n">
-        <v>1025886.27</v>
+        <v>1026365.94</v>
       </c>
       <c r="C648" t="n">
-        <v>1025886.27</v>
+        <v>1026365.94</v>
       </c>
     </row>
     <row r="649">
@@ -14210,10 +14210,10 @@
         <v>44562</v>
       </c>
       <c r="B650" t="n">
-        <v>1043732.38</v>
+        <v>1043043</v>
       </c>
       <c r="C650" t="n">
-        <v>1043732.38</v>
+        <v>1043043</v>
       </c>
     </row>
     <row r="651">
@@ -14221,10 +14221,10 @@
         <v>44593</v>
       </c>
       <c r="B651" t="n">
-        <v>1055211.13</v>
+        <v>1054708.34</v>
       </c>
       <c r="C651" t="n">
-        <v>1055211.13</v>
+        <v>1054708.34</v>
       </c>
     </row>
     <row r="652">
@@ -14232,10 +14232,10 @@
         <v>44621</v>
       </c>
       <c r="B652" t="n">
-        <v>1079329.43</v>
+        <v>1077503.17</v>
       </c>
       <c r="C652" t="n">
-        <v>1079329.43</v>
+        <v>1077503.17</v>
       </c>
     </row>
     <row r="653">
@@ -14243,10 +14243,10 @@
         <v>44652</v>
       </c>
       <c r="B653" t="n">
-        <v>1092969.86</v>
+        <v>1091128.82</v>
       </c>
       <c r="C653" t="n">
-        <v>1092969.86</v>
+        <v>1091128.82</v>
       </c>
     </row>
     <row r="654">
@@ -14254,10 +14254,10 @@
         <v>44682</v>
       </c>
       <c r="B654" t="n">
-        <v>1101405.35</v>
+        <v>1100547.3</v>
       </c>
       <c r="C654" t="n">
-        <v>1101405.35</v>
+        <v>1100547.3</v>
       </c>
     </row>
     <row r="655">
@@ -14265,10 +14265,10 @@
         <v>44713</v>
       </c>
       <c r="B655" t="n">
-        <v>1120580.97</v>
+        <v>1120168.09</v>
       </c>
       <c r="C655" t="n">
-        <v>1120580.97</v>
+        <v>1120168.09</v>
       </c>
     </row>
     <row r="656">
@@ -14276,10 +14276,10 @@
         <v>44743</v>
       </c>
       <c r="B656" t="n">
-        <v>1130232.51</v>
+        <v>1129894.02</v>
       </c>
       <c r="C656" t="n">
-        <v>1130232.51</v>
+        <v>1129894.02</v>
       </c>
     </row>
     <row r="657">
@@ -14287,10 +14287,10 @@
         <v>44774</v>
       </c>
       <c r="B657" t="n">
-        <v>1144559.98</v>
+        <v>1144930.67</v>
       </c>
       <c r="C657" t="n">
-        <v>1144559.98</v>
+        <v>1144930.67</v>
       </c>
     </row>
     <row r="658">
@@ -14298,10 +14298,10 @@
         <v>44805</v>
       </c>
       <c r="B658" t="n">
-        <v>1154880.21</v>
+        <v>1155439.56</v>
       </c>
       <c r="C658" t="n">
-        <v>1154880.21</v>
+        <v>1155439.56</v>
       </c>
     </row>
     <row r="659">
@@ -14309,10 +14309,10 @@
         <v>44835</v>
       </c>
       <c r="B659" t="n">
-        <v>1166450.88</v>
+        <v>1167445</v>
       </c>
       <c r="C659" t="n">
-        <v>1166450.88</v>
+        <v>1167445</v>
       </c>
     </row>
     <row r="660">
@@ -14320,10 +14320,10 @@
         <v>44866</v>
       </c>
       <c r="B660" t="n">
-        <v>1182559.74</v>
+        <v>1183888.99</v>
       </c>
       <c r="C660" t="n">
-        <v>1182559.74</v>
+        <v>1183888.99</v>
       </c>
     </row>
     <row r="661">
@@ -14342,10 +14342,10 @@
         <v>44927</v>
       </c>
       <c r="B662" t="n">
-        <v>1200987.99</v>
+        <v>1199848.64</v>
       </c>
       <c r="C662" t="n">
-        <v>1200987.99</v>
+        <v>1199848.64</v>
       </c>
     </row>
     <row r="663">
@@ -14353,10 +14353,10 @@
         <v>44958</v>
       </c>
       <c r="B663" t="n">
-        <v>1205245.27</v>
+        <v>1204657.9</v>
       </c>
       <c r="C663" t="n">
-        <v>1205245.27</v>
+        <v>1204657.9</v>
       </c>
     </row>
     <row r="664">
@@ -14364,10 +14364,10 @@
         <v>44986</v>
       </c>
       <c r="B664" t="n">
-        <v>1222516.82</v>
+        <v>1220942.04</v>
       </c>
       <c r="C664" t="n">
-        <v>1222516.82</v>
+        <v>1220942.04</v>
       </c>
     </row>
     <row r="665">
@@ -14375,10 +14375,10 @@
         <v>45017</v>
       </c>
       <c r="B665" t="n">
-        <v>1234456.94</v>
+        <v>1232543.71</v>
       </c>
       <c r="C665" t="n">
-        <v>1234456.94</v>
+        <v>1232543.71</v>
       </c>
     </row>
     <row r="666">
@@ -14386,10 +14386,10 @@
         <v>45047</v>
       </c>
       <c r="B666" t="n">
-        <v>1241882.33</v>
+        <v>1241274.52</v>
       </c>
       <c r="C666" t="n">
-        <v>1241882.33</v>
+        <v>1241274.52</v>
       </c>
     </row>
     <row r="667">
@@ -14397,10 +14397,10 @@
         <v>45078</v>
       </c>
       <c r="B667" t="n">
-        <v>1247752.95</v>
+        <v>1247629.97</v>
       </c>
       <c r="C667" t="n">
-        <v>1247752.95</v>
+        <v>1247629.97</v>
       </c>
     </row>
     <row r="668">
@@ -14408,10 +14408,10 @@
         <v>45108</v>
       </c>
       <c r="B668" t="n">
-        <v>1256258.08</v>
+        <v>1255755.94</v>
       </c>
       <c r="C668" t="n">
-        <v>1256258.08</v>
+        <v>1255755.94</v>
       </c>
     </row>
     <row r="669">
@@ -14419,10 +14419,10 @@
         <v>45139</v>
       </c>
       <c r="B669" t="n">
-        <v>1270866.74</v>
+        <v>1271810.03</v>
       </c>
       <c r="C669" t="n">
-        <v>1270866.74</v>
+        <v>1271810.03</v>
       </c>
     </row>
     <row r="670">
@@ -14430,10 +14430,10 @@
         <v>45170</v>
       </c>
       <c r="B670" t="n">
-        <v>1276945.06</v>
+        <v>1277927.44</v>
       </c>
       <c r="C670" t="n">
-        <v>1276945.06</v>
+        <v>1277927.44</v>
       </c>
     </row>
     <row r="671">
@@ -14441,10 +14441,10 @@
         <v>45200</v>
       </c>
       <c r="B671" t="n">
-        <v>1280720.18</v>
+        <v>1282359.38</v>
       </c>
       <c r="C671" t="n">
-        <v>1280720.18</v>
+        <v>1282359.38</v>
       </c>
     </row>
     <row r="672">
@@ -14452,10 +14452,10 @@
         <v>45231</v>
       </c>
       <c r="B672" t="n">
-        <v>1299364.41</v>
+        <v>1301585.93</v>
       </c>
       <c r="C672" t="n">
-        <v>1299364.41</v>
+        <v>1301585.93</v>
       </c>
     </row>
     <row r="673">
@@ -14474,10 +14474,10 @@
         <v>45292</v>
       </c>
       <c r="B674" t="n">
-        <v>1310033.54</v>
+        <v>1308351.47</v>
       </c>
       <c r="C674" t="n">
-        <v>1310033.54</v>
+        <v>1308351.47</v>
       </c>
     </row>
     <row r="675">
@@ -14485,10 +14485,10 @@
         <v>45323</v>
       </c>
       <c r="B675" t="n">
-        <v>1320172.41</v>
+        <v>1319462.37</v>
       </c>
       <c r="C675" t="n">
-        <v>1320172.41</v>
+        <v>1319462.37</v>
       </c>
     </row>
     <row r="676">
@@ -14496,10 +14496,10 @@
         <v>45352</v>
       </c>
       <c r="B676" t="n">
-        <v>1322156.8</v>
+        <v>1320920.6</v>
       </c>
       <c r="C676" t="n">
-        <v>1322156.8</v>
+        <v>1320920.6</v>
       </c>
     </row>
     <row r="677">
@@ -14507,10 +14507,10 @@
         <v>45383</v>
       </c>
       <c r="B677" t="n">
-        <v>1324876.54</v>
+        <v>1322883.53</v>
       </c>
       <c r="C677" t="n">
-        <v>1324876.54</v>
+        <v>1322883.53</v>
       </c>
     </row>
     <row r="678">
@@ -14518,10 +14518,10 @@
         <v>45413</v>
       </c>
       <c r="B678" t="n">
-        <v>1331664.15</v>
+        <v>1331284.5</v>
       </c>
       <c r="C678" t="n">
-        <v>1331664.15</v>
+        <v>1331284.5</v>
       </c>
     </row>
     <row r="679">
@@ -14529,10 +14529,10 @@
         <v>45444</v>
       </c>
       <c r="B679" t="n">
-        <v>1330645.54</v>
+        <v>1330878.94</v>
       </c>
       <c r="C679" t="n">
-        <v>1330645.54</v>
+        <v>1330878.94</v>
       </c>
     </row>
     <row r="680">
@@ -14540,10 +14540,10 @@
         <v>45474</v>
       </c>
       <c r="B680" t="n">
-        <v>1338289.48</v>
+        <v>1337484.66</v>
       </c>
       <c r="C680" t="n">
-        <v>1338289.48</v>
+        <v>1337484.66</v>
       </c>
     </row>
     <row r="681">
@@ -14551,10 +14551,10 @@
         <v>45505</v>
       </c>
       <c r="B681" t="n">
-        <v>1338717.06</v>
+        <v>1340184.49</v>
       </c>
       <c r="C681" t="n">
-        <v>1338717.06</v>
+        <v>1340184.49</v>
       </c>
     </row>
     <row r="682">
@@ -14562,10 +14562,10 @@
         <v>45536</v>
       </c>
       <c r="B682" t="n">
-        <v>1341182.07</v>
+        <v>1342480.89</v>
       </c>
       <c r="C682" t="n">
-        <v>1341182.07</v>
+        <v>1342480.89</v>
       </c>
     </row>
     <row r="683">
@@ -14573,10 +14573,10 @@
         <v>45566</v>
       </c>
       <c r="B683" t="n">
-        <v>1350299.02</v>
+        <v>1352433.61</v>
       </c>
       <c r="C683" t="n">
-        <v>1350299.02</v>
+        <v>1352433.61</v>
       </c>
     </row>
     <row r="684">
@@ -14584,10 +14584,10 @@
         <v>45597</v>
       </c>
       <c r="B684" t="n">
-        <v>1339075</v>
+        <v>1342090.49</v>
       </c>
       <c r="C684" t="n">
-        <v>1339075</v>
+        <v>1342090.49</v>
       </c>
     </row>
     <row r="685">
@@ -14595,10 +14595,10 @@
         <v>45627</v>
       </c>
       <c r="B685" t="n">
-        <v>1296965.56</v>
+        <v>1296965.62</v>
       </c>
       <c r="C685" t="n">
-        <v>1296965.56</v>
+        <v>1296965.62</v>
       </c>
     </row>
     <row r="686">
@@ -14606,10 +14606,10 @@
         <v>45658</v>
       </c>
       <c r="B686" t="n">
-        <v>1304262.54</v>
+        <v>1301982.23</v>
       </c>
       <c r="C686" t="n">
-        <v>1304262.54</v>
+        <v>1301982.23</v>
       </c>
     </row>
     <row r="687">
@@ -14617,10 +14617,10 @@
         <v>45689</v>
       </c>
       <c r="B687" t="n">
-        <v>1305504.87</v>
+        <v>1304274.47</v>
       </c>
       <c r="C687" t="n">
-        <v>1305504.87</v>
+        <v>1304274.47</v>
       </c>
     </row>
     <row r="688">
@@ -14628,10 +14628,10 @@
         <v>45717</v>
       </c>
       <c r="B688" t="n">
-        <v>1294474.35</v>
+        <v>1292802.55</v>
       </c>
       <c r="C688" t="n">
-        <v>1294474.35</v>
+        <v>1292802.55</v>
       </c>
     </row>
     <row r="689">
@@ -14639,10 +14639,10 @@
         <v>45748</v>
       </c>
       <c r="B689" t="n">
-        <v>1301496.38</v>
+        <v>1299129.25</v>
       </c>
       <c r="C689" t="n">
-        <v>1301496.38</v>
+        <v>1299129.25</v>
       </c>
     </row>
     <row r="690">
@@ -14650,10 +14650,10 @@
         <v>45778</v>
       </c>
       <c r="B690" t="n">
-        <v>1300226.33</v>
+        <v>1299722.4</v>
       </c>
       <c r="C690" t="n">
-        <v>1300226.33</v>
+        <v>1299722.4</v>
       </c>
     </row>
     <row r="691">
@@ -14661,10 +14661,10 @@
         <v>45809</v>
       </c>
       <c r="B691" t="n">
-        <v>1300318</v>
+        <v>1301742.19</v>
       </c>
       <c r="C691" t="n">
-        <v>1300318</v>
+        <v>1301742.19</v>
       </c>
     </row>
     <row r="692">
@@ -14672,10 +14672,10 @@
         <v>45839</v>
       </c>
       <c r="B692" t="n">
-        <v>1310908.54</v>
+        <v>1310351.97</v>
       </c>
       <c r="C692" t="n">
-        <v>1310908.54</v>
+        <v>1310351.97</v>
       </c>
     </row>
     <row r="693">
@@ -14683,10 +14683,10 @@
         <v>45870</v>
       </c>
       <c r="B693" t="n">
-        <v>1306121.23</v>
+        <v>1308162.07</v>
       </c>
       <c r="C693" t="n">
-        <v>1306121.23</v>
+        <v>1308162.07</v>
       </c>
     </row>
     <row r="694">
@@ -14694,10 +14694,10 @@
         <v>45901</v>
       </c>
       <c r="B694" t="n">
-        <v>1310561.76</v>
+        <v>1312713.48</v>
       </c>
       <c r="C694" t="n">
-        <v>1310561.76</v>
+        <v>1312713.48</v>
       </c>
     </row>
     <row r="695">
@@ -14705,10 +14705,10 @@
         <v>45931</v>
       </c>
       <c r="B695" t="n">
-        <v>1315011.6</v>
+        <v>1317148.12</v>
       </c>
       <c r="C695" t="n">
-        <v>1315011.6</v>
+        <v>1317148.12</v>
       </c>
     </row>
     <row r="696">
@@ -14716,10 +14716,10 @@
         <v>45962</v>
       </c>
       <c r="B696" t="n">
-        <v>1311884.89</v>
+        <v>1316163.23</v>
       </c>
       <c r="C696" t="n">
-        <v>1311884.89</v>
+        <v>1316163.23</v>
       </c>
     </row>
     <row r="697">
@@ -14727,10 +14727,10 @@
         <v>45992</v>
       </c>
       <c r="B697" t="n">
-        <v>1324277.25</v>
+        <v>1324321.59</v>
       </c>
       <c r="C697" t="n">
-        <v>1324277.25</v>
+        <v>1324321.59</v>
       </c>
     </row>
     <row r="698">
@@ -14738,10 +14738,21 @@
         <v>46023</v>
       </c>
       <c r="B698" t="n">
-        <v>1328986.66</v>
+        <v>1326887.25</v>
       </c>
       <c r="C698" t="n">
-        <v>1328986.66</v>
+        <v>1326887.25</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B699" t="n">
+        <v>1327596.44</v>
+      </c>
+      <c r="C699" t="n">
+        <v>1327596.44</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -28486,7 +28486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3092"/>
+  <dimension ref="A1:C3093"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62501,10 +62501,21 @@
         <v>46109</v>
       </c>
       <c r="B3092" t="n">
-        <v>202000</v>
+        <v>203000</v>
       </c>
       <c r="C3092" t="n">
-        <v>202000</v>
+        <v>203000</v>
+      </c>
+    </row>
+    <row r="3093">
+      <c r="A3093" s="1" t="n">
+        <v>46116</v>
+      </c>
+      <c r="B3093" t="n">
+        <v>219000</v>
+      </c>
+      <c r="C3093" t="n">
+        <v>219000</v>
       </c>
     </row>
   </sheetData>
@@ -62518,7 +62529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C806"/>
+  <dimension ref="A1:C807"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71354,10 +71365,10 @@
         <v>45931</v>
       </c>
       <c r="B803" t="n">
-        <v>18066.6</v>
+        <v>18063.1</v>
       </c>
       <c r="C803" t="n">
-        <v>18066.6</v>
+        <v>18063.1</v>
       </c>
     </row>
     <row r="804">
@@ -71365,10 +71376,10 @@
         <v>45962</v>
       </c>
       <c r="B804" t="n">
-        <v>18088</v>
+        <v>18078.6</v>
       </c>
       <c r="C804" t="n">
-        <v>18088</v>
+        <v>18078.6</v>
       </c>
     </row>
     <row r="805">
@@ -71376,10 +71387,10 @@
         <v>45992</v>
       </c>
       <c r="B805" t="n">
-        <v>18082.4</v>
+        <v>18070.6</v>
       </c>
       <c r="C805" t="n">
-        <v>18082.4</v>
+        <v>18070.6</v>
       </c>
     </row>
     <row r="806">
@@ -71387,10 +71398,21 @@
         <v>46023</v>
       </c>
       <c r="B806" t="n">
-        <v>18203.2</v>
+        <v>18183.1</v>
       </c>
       <c r="C806" t="n">
-        <v>18203.2</v>
+        <v>18183.1</v>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B807" t="n">
+        <v>18100.8</v>
+      </c>
+      <c r="C807" t="n">
+        <v>18100.8</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -28486,7 +28486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3093"/>
+  <dimension ref="A1:C3094"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62512,10 +62512,21 @@
         <v>46116</v>
       </c>
       <c r="B3093" t="n">
-        <v>219000</v>
+        <v>218000</v>
       </c>
       <c r="C3093" t="n">
-        <v>219000</v>
+        <v>218000</v>
+      </c>
+    </row>
+    <row r="3094">
+      <c r="A3094" s="1" t="n">
+        <v>46123</v>
+      </c>
+      <c r="B3094" t="n">
+        <v>207000</v>
+      </c>
+      <c r="C3094" t="n">
+        <v>207000</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -28486,7 +28486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3094"/>
+  <dimension ref="A1:C3095"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62523,10 +62523,21 @@
         <v>46123</v>
       </c>
       <c r="B3094" t="n">
-        <v>207000</v>
+        <v>208000</v>
       </c>
       <c r="C3094" t="n">
-        <v>207000</v>
+        <v>208000</v>
+      </c>
+    </row>
+    <row r="3095">
+      <c r="A3095" s="1" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B3095" t="n">
+        <v>214000</v>
+      </c>
+      <c r="C3095" t="n">
+        <v>214000</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -28486,7 +28486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3095"/>
+  <dimension ref="A1:C3096"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62534,10 +62534,21 @@
         <v>46130</v>
       </c>
       <c r="B3095" t="n">
-        <v>214000</v>
+        <v>215000</v>
       </c>
       <c r="C3095" t="n">
-        <v>214000</v>
+        <v>215000</v>
+      </c>
+    </row>
+    <row r="3096">
+      <c r="A3096" s="1" t="n">
+        <v>46137</v>
+      </c>
+      <c r="B3096" t="n">
+        <v>189000</v>
+      </c>
+      <c r="C3096" t="n">
+        <v>189000</v>
       </c>
     </row>
   </sheetData>
@@ -62551,7 +62562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C807"/>
+  <dimension ref="A1:C808"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71420,10 +71431,10 @@
         <v>46023</v>
       </c>
       <c r="B806" t="n">
-        <v>18183.1</v>
+        <v>18187</v>
       </c>
       <c r="C806" t="n">
-        <v>18183.1</v>
+        <v>18187</v>
       </c>
     </row>
     <row r="807">
@@ -71431,10 +71442,21 @@
         <v>46054</v>
       </c>
       <c r="B807" t="n">
-        <v>18100.8</v>
+        <v>18118.9</v>
       </c>
       <c r="C807" t="n">
-        <v>18100.8</v>
+        <v>18118.9</v>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B808" t="n">
+        <v>18108.7</v>
+      </c>
+      <c r="C808" t="n">
+        <v>18108.7</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -14766,7 +14766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C304"/>
+  <dimension ref="A1:C305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18113,10 +18113,21 @@
         <v>46054</v>
       </c>
       <c r="B304" t="n">
-        <v>6882</v>
+        <v>6922</v>
       </c>
       <c r="C304" t="n">
-        <v>6.882</v>
+        <v>6.922</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B305" t="n">
+        <v>6866</v>
+      </c>
+      <c r="C305" t="n">
+        <v>6.866</v>
       </c>
     </row>
   </sheetData>
@@ -28486,7 +28497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3096"/>
+  <dimension ref="A1:C3097"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62545,10 +62556,21 @@
         <v>46137</v>
       </c>
       <c r="B3096" t="n">
-        <v>189000</v>
+        <v>190000</v>
       </c>
       <c r="C3096" t="n">
-        <v>189000</v>
+        <v>190000</v>
+      </c>
+    </row>
+    <row r="3097">
+      <c r="A3097" s="1" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B3097" t="n">
+        <v>200000</v>
+      </c>
+      <c r="C3097" t="n">
+        <v>200000</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -7057,7 +7057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C699"/>
+  <dimension ref="A1:C700"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14705,10 +14705,10 @@
         <v>45931</v>
       </c>
       <c r="B695" t="n">
-        <v>1317148.12</v>
+        <v>1317148.1</v>
       </c>
       <c r="C695" t="n">
-        <v>1317148.12</v>
+        <v>1317148.1</v>
       </c>
     </row>
     <row r="696">
@@ -14716,10 +14716,10 @@
         <v>45962</v>
       </c>
       <c r="B696" t="n">
-        <v>1316163.23</v>
+        <v>1316163.19</v>
       </c>
       <c r="C696" t="n">
-        <v>1316163.23</v>
+        <v>1316163.19</v>
       </c>
     </row>
     <row r="697">
@@ -14727,10 +14727,10 @@
         <v>45992</v>
       </c>
       <c r="B697" t="n">
-        <v>1324321.59</v>
+        <v>1324321.51</v>
       </c>
       <c r="C697" t="n">
-        <v>1324321.59</v>
+        <v>1324321.51</v>
       </c>
     </row>
     <row r="698">
@@ -14738,10 +14738,10 @@
         <v>46023</v>
       </c>
       <c r="B698" t="n">
-        <v>1326887.25</v>
+        <v>1326575.31</v>
       </c>
       <c r="C698" t="n">
-        <v>1326887.25</v>
+        <v>1326575.31</v>
       </c>
     </row>
     <row r="699">
@@ -14749,10 +14749,21 @@
         <v>46054</v>
       </c>
       <c r="B699" t="n">
-        <v>1327596.44</v>
+        <v>1326953.92</v>
       </c>
       <c r="C699" t="n">
-        <v>1327596.44</v>
+        <v>1326953.92</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B700" t="n">
+        <v>1336987.42</v>
+      </c>
+      <c r="C700" t="n">
+        <v>1336987.42</v>
       </c>
     </row>
   </sheetData>
@@ -18141,7 +18152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C940"/>
+  <dimension ref="A1:C941"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28483,6 +28494,17 @@
         <v>4.3</v>
       </c>
       <c r="C940" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B941" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C941" t="n">
         <v>4.3</v>
       </c>
     </row>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -28519,7 +28519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3097"/>
+  <dimension ref="A1:C3098"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62589,10 +62589,21 @@
         <v>46144</v>
       </c>
       <c r="B3097" t="n">
-        <v>200000</v>
+        <v>199000</v>
       </c>
       <c r="C3097" t="n">
-        <v>200000</v>
+        <v>199000</v>
+      </c>
+    </row>
+    <row r="3098">
+      <c r="A3098" s="1" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B3098" t="n">
+        <v>211000</v>
+      </c>
+      <c r="C3098" t="n">
+        <v>211000</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C141"/>
+  <dimension ref="A1:C142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1983,6 +1983,17 @@
       </c>
       <c r="C141" t="n">
         <v>2.94</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B142" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="C142" t="n">
+        <v>2.92</v>
       </c>
     </row>
   </sheetData>
@@ -1996,7 +2007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C165"/>
+  <dimension ref="A1:C166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2571,10 +2582,10 @@
         <v>35612</v>
       </c>
       <c r="B52" t="n">
-        <v>5.5</v>
+        <v>5.49</v>
       </c>
       <c r="C52" t="n">
-        <v>5.5</v>
+        <v>5.49</v>
       </c>
     </row>
     <row r="53">
@@ -2593,10 +2604,10 @@
         <v>35796</v>
       </c>
       <c r="B54" t="n">
-        <v>5.24</v>
+        <v>5.25</v>
       </c>
       <c r="C54" t="n">
-        <v>5.24</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="55">
@@ -2604,10 +2615,10 @@
         <v>35886</v>
       </c>
       <c r="B55" t="n">
-        <v>5.2</v>
+        <v>5.21</v>
       </c>
       <c r="C55" t="n">
-        <v>5.2</v>
+        <v>5.21</v>
       </c>
     </row>
     <row r="56">
@@ -2615,10 +2626,10 @@
         <v>35977</v>
       </c>
       <c r="B56" t="n">
-        <v>5.28</v>
+        <v>5.27</v>
       </c>
       <c r="C56" t="n">
-        <v>5.28</v>
+        <v>5.27</v>
       </c>
     </row>
     <row r="57">
@@ -2626,10 +2637,10 @@
         <v>36069</v>
       </c>
       <c r="B57" t="n">
-        <v>5.08</v>
+        <v>5.06</v>
       </c>
       <c r="C57" t="n">
-        <v>5.08</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="58">
@@ -2637,10 +2648,10 @@
         <v>36161</v>
       </c>
       <c r="B58" t="n">
-        <v>4.89</v>
+        <v>4.92</v>
       </c>
       <c r="C58" t="n">
-        <v>4.89</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="59">
@@ -2648,10 +2659,10 @@
         <v>36251</v>
       </c>
       <c r="B59" t="n">
-        <v>4.32</v>
+        <v>4.33</v>
       </c>
       <c r="C59" t="n">
-        <v>4.32</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="60">
@@ -2659,10 +2670,10 @@
         <v>36342</v>
       </c>
       <c r="B60" t="n">
-        <v>4.5</v>
+        <v>4.48</v>
       </c>
       <c r="C60" t="n">
-        <v>4.5</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="61">
@@ -2670,10 +2681,10 @@
         <v>36434</v>
       </c>
       <c r="B61" t="n">
-        <v>4.49</v>
+        <v>4.46</v>
       </c>
       <c r="C61" t="n">
-        <v>4.49</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="62">
@@ -2681,10 +2692,10 @@
         <v>36526</v>
       </c>
       <c r="B62" t="n">
-        <v>4.49</v>
+        <v>4.53</v>
       </c>
       <c r="C62" t="n">
-        <v>4.49</v>
+        <v>4.53</v>
       </c>
     </row>
     <row r="63">
@@ -2692,10 +2703,10 @@
         <v>36617</v>
       </c>
       <c r="B63" t="n">
-        <v>4.09</v>
+        <v>4.1</v>
       </c>
       <c r="C63" t="n">
-        <v>4.09</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="64">
@@ -2703,10 +2714,10 @@
         <v>36708</v>
       </c>
       <c r="B64" t="n">
-        <v>4.25</v>
+        <v>4.23</v>
       </c>
       <c r="C64" t="n">
-        <v>4.25</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="65">
@@ -2714,10 +2725,10 @@
         <v>36800</v>
       </c>
       <c r="B65" t="n">
-        <v>4.39</v>
+        <v>4.34</v>
       </c>
       <c r="C65" t="n">
-        <v>4.39</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="66">
@@ -2725,10 +2736,10 @@
         <v>36892</v>
       </c>
       <c r="B66" t="n">
-        <v>4.57</v>
+        <v>4.65</v>
       </c>
       <c r="C66" t="n">
-        <v>4.57</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="67">
@@ -2736,10 +2747,10 @@
         <v>36982</v>
       </c>
       <c r="B67" t="n">
-        <v>5.22</v>
+        <v>5.21</v>
       </c>
       <c r="C67" t="n">
-        <v>5.22</v>
+        <v>5.21</v>
       </c>
     </row>
     <row r="68">
@@ -2747,10 +2758,10 @@
         <v>37073</v>
       </c>
       <c r="B68" t="n">
-        <v>5.55</v>
+        <v>5.52</v>
       </c>
       <c r="C68" t="n">
-        <v>5.55</v>
+        <v>5.52</v>
       </c>
     </row>
     <row r="69">
@@ -2758,10 +2769,10 @@
         <v>37165</v>
       </c>
       <c r="B69" t="n">
-        <v>6.35</v>
+        <v>6.28</v>
       </c>
       <c r="C69" t="n">
-        <v>6.35</v>
+        <v>6.28</v>
       </c>
     </row>
     <row r="70">
@@ -2769,10 +2780,10 @@
         <v>37257</v>
       </c>
       <c r="B70" t="n">
-        <v>7.65</v>
+        <v>7.78</v>
       </c>
       <c r="C70" t="n">
-        <v>7.65</v>
+        <v>7.78</v>
       </c>
     </row>
     <row r="71">
@@ -2791,10 +2802,10 @@
         <v>37438</v>
       </c>
       <c r="B72" t="n">
-        <v>6.22</v>
+        <v>6.18</v>
       </c>
       <c r="C72" t="n">
-        <v>6.22</v>
+        <v>6.18</v>
       </c>
     </row>
     <row r="73">
@@ -2802,10 +2813,10 @@
         <v>37530</v>
       </c>
       <c r="B73" t="n">
-        <v>5.54</v>
+        <v>5.48</v>
       </c>
       <c r="C73" t="n">
-        <v>5.54</v>
+        <v>5.48</v>
       </c>
     </row>
     <row r="74">
@@ -2813,10 +2824,10 @@
         <v>37622</v>
       </c>
       <c r="B74" t="n">
-        <v>5.73</v>
+        <v>5.83</v>
       </c>
       <c r="C74" t="n">
-        <v>5.73</v>
+        <v>5.83</v>
       </c>
     </row>
     <row r="75">
@@ -2835,10 +2846,10 @@
         <v>37803</v>
       </c>
       <c r="B76" t="n">
-        <v>5.6</v>
+        <v>5.57</v>
       </c>
       <c r="C76" t="n">
-        <v>5.6</v>
+        <v>5.57</v>
       </c>
     </row>
     <row r="77">
@@ -2846,10 +2857,10 @@
         <v>37895</v>
       </c>
       <c r="B77" t="n">
-        <v>6</v>
+        <v>5.95</v>
       </c>
       <c r="C77" t="n">
-        <v>6</v>
+        <v>5.95</v>
       </c>
     </row>
     <row r="78">
@@ -2857,10 +2868,10 @@
         <v>37987</v>
       </c>
       <c r="B78" t="n">
-        <v>5.4</v>
+        <v>5.47</v>
       </c>
       <c r="C78" t="n">
-        <v>5.4</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="79">
@@ -2879,10 +2890,10 @@
         <v>38169</v>
       </c>
       <c r="B80" t="n">
-        <v>4.49</v>
+        <v>4.47</v>
       </c>
       <c r="C80" t="n">
-        <v>4.49</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="81">
@@ -2890,10 +2901,10 @@
         <v>38261</v>
       </c>
       <c r="B81" t="n">
-        <v>4.67</v>
+        <v>4.65</v>
       </c>
       <c r="C81" t="n">
-        <v>4.67</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="82">
@@ -2901,10 +2912,10 @@
         <v>38353</v>
       </c>
       <c r="B82" t="n">
-        <v>4.66</v>
+        <v>4.7</v>
       </c>
       <c r="C82" t="n">
-        <v>4.66</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="83">
@@ -2923,10 +2934,10 @@
         <v>38534</v>
       </c>
       <c r="B84" t="n">
-        <v>4.35</v>
+        <v>4.34</v>
       </c>
       <c r="C84" t="n">
-        <v>4.35</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="85">
@@ -2934,10 +2945,10 @@
         <v>38626</v>
       </c>
       <c r="B85" t="n">
-        <v>6.09</v>
+        <v>6.07</v>
       </c>
       <c r="C85" t="n">
-        <v>6.09</v>
+        <v>6.07</v>
       </c>
     </row>
     <row r="86">
@@ -2945,10 +2956,10 @@
         <v>38718</v>
       </c>
       <c r="B86" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="C86" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="87">
@@ -2956,10 +2967,10 @@
         <v>38808</v>
       </c>
       <c r="B87" t="n">
-        <v>3.43</v>
+        <v>3.44</v>
       </c>
       <c r="C87" t="n">
-        <v>3.43</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="88">
@@ -2967,10 +2978,10 @@
         <v>38899</v>
       </c>
       <c r="B88" t="n">
-        <v>3.84</v>
+        <v>3.83</v>
       </c>
       <c r="C88" t="n">
-        <v>3.84</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="89">
@@ -2989,10 +3000,10 @@
         <v>39083</v>
       </c>
       <c r="B90" t="n">
-        <v>4.01</v>
+        <v>4.02</v>
       </c>
       <c r="C90" t="n">
-        <v>4.01</v>
+        <v>4.02</v>
       </c>
     </row>
     <row r="91">
@@ -3011,10 +3022,10 @@
         <v>39264</v>
       </c>
       <c r="B92" t="n">
-        <v>3.91</v>
+        <v>3.9</v>
       </c>
       <c r="C92" t="n">
-        <v>3.91</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="93">
@@ -3066,10 +3077,10 @@
         <v>39722</v>
       </c>
       <c r="B97" t="n">
-        <v>6.53</v>
+        <v>6.52</v>
       </c>
       <c r="C97" t="n">
-        <v>6.53</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="98">
@@ -3143,10 +3154,10 @@
         <v>40360</v>
       </c>
       <c r="B104" t="n">
-        <v>8.779999999999999</v>
+        <v>8.77</v>
       </c>
       <c r="C104" t="n">
-        <v>8.779999999999999</v>
+        <v>8.77</v>
       </c>
     </row>
     <row r="105">
@@ -3352,10 +3363,10 @@
         <v>42095</v>
       </c>
       <c r="B123" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="C123" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="124">
@@ -3363,10 +3374,10 @@
         <v>42186</v>
       </c>
       <c r="B124" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="C124" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="125">
@@ -3407,10 +3418,10 @@
         <v>42552</v>
       </c>
       <c r="B128" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="C128" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="129">
@@ -3429,10 +3440,10 @@
         <v>42736</v>
       </c>
       <c r="B130" t="n">
-        <v>3.45</v>
+        <v>3.46</v>
       </c>
       <c r="C130" t="n">
-        <v>3.45</v>
+        <v>3.46</v>
       </c>
     </row>
     <row r="131">
@@ -3451,10 +3462,10 @@
         <v>42917</v>
       </c>
       <c r="B132" t="n">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
       <c r="C132" t="n">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
     </row>
     <row r="133">
@@ -3462,10 +3473,10 @@
         <v>43009</v>
       </c>
       <c r="B133" t="n">
-        <v>3.7</v>
+        <v>3.69</v>
       </c>
       <c r="C133" t="n">
-        <v>3.7</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="134">
@@ -3473,10 +3484,10 @@
         <v>43101</v>
       </c>
       <c r="B134" t="n">
-        <v>3.65</v>
+        <v>3.66</v>
       </c>
       <c r="C134" t="n">
-        <v>3.65</v>
+        <v>3.66</v>
       </c>
     </row>
     <row r="135">
@@ -3484,10 +3495,10 @@
         <v>43191</v>
       </c>
       <c r="B135" t="n">
-        <v>3.58</v>
+        <v>3.61</v>
       </c>
       <c r="C135" t="n">
-        <v>3.58</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="136">
@@ -3495,10 +3506,10 @@
         <v>43282</v>
       </c>
       <c r="B136" t="n">
-        <v>3.69</v>
+        <v>3.65</v>
       </c>
       <c r="C136" t="n">
-        <v>3.69</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="137">
@@ -3506,10 +3517,10 @@
         <v>43374</v>
       </c>
       <c r="B137" t="n">
-        <v>3.67</v>
+        <v>3.66</v>
       </c>
       <c r="C137" t="n">
-        <v>3.67</v>
+        <v>3.66</v>
       </c>
     </row>
     <row r="138">
@@ -3517,10 +3528,10 @@
         <v>43466</v>
       </c>
       <c r="B138" t="n">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="C138" t="n">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="139">
@@ -3528,10 +3539,10 @@
         <v>43556</v>
       </c>
       <c r="B139" t="n">
-        <v>3.64</v>
+        <v>3.67</v>
       </c>
       <c r="C139" t="n">
-        <v>3.64</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="140">
@@ -3539,10 +3550,10 @@
         <v>43647</v>
       </c>
       <c r="B140" t="n">
-        <v>3.74</v>
+        <v>3.68</v>
       </c>
       <c r="C140" t="n">
-        <v>3.74</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="141">
@@ -3550,10 +3561,10 @@
         <v>43739</v>
       </c>
       <c r="B141" t="n">
-        <v>3.78</v>
+        <v>3.77</v>
       </c>
       <c r="C141" t="n">
-        <v>3.78</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="142">
@@ -3561,10 +3572,10 @@
         <v>43831</v>
       </c>
       <c r="B142" t="n">
-        <v>3.72</v>
+        <v>3.75</v>
       </c>
       <c r="C142" t="n">
-        <v>3.72</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="143">
@@ -3572,10 +3583,10 @@
         <v>43922</v>
       </c>
       <c r="B143" t="n">
-        <v>3.78</v>
+        <v>3.84</v>
       </c>
       <c r="C143" t="n">
-        <v>3.78</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="144">
@@ -3583,10 +3594,10 @@
         <v>44013</v>
       </c>
       <c r="B144" t="n">
-        <v>3.6</v>
+        <v>3.51</v>
       </c>
       <c r="C144" t="n">
-        <v>3.6</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="145">
@@ -3605,10 +3616,10 @@
         <v>44197</v>
       </c>
       <c r="B146" t="n">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
       <c r="C146" t="n">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="147">
@@ -3616,10 +3627,10 @@
         <v>44287</v>
       </c>
       <c r="B147" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="C147" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="148">
@@ -3627,10 +3638,10 @@
         <v>44378</v>
       </c>
       <c r="B148" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="C148" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="149">
@@ -3649,10 +3660,10 @@
         <v>44562</v>
       </c>
       <c r="B150" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="C150" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="151">
@@ -3660,10 +3671,10 @@
         <v>44652</v>
       </c>
       <c r="B151" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="C151" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="152">
@@ -3671,10 +3682,10 @@
         <v>44743</v>
       </c>
       <c r="B152" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="C152" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="153">
@@ -3682,10 +3693,10 @@
         <v>44835</v>
       </c>
       <c r="B153" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="C153" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="154">
@@ -3693,10 +3704,10 @@
         <v>44927</v>
       </c>
       <c r="B154" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="C154" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="155">
@@ -3704,10 +3715,10 @@
         <v>45017</v>
       </c>
       <c r="B155" t="n">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
       <c r="C155" t="n">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="156">
@@ -3715,10 +3726,10 @@
         <v>45108</v>
       </c>
       <c r="B156" t="n">
-        <v>3.76</v>
+        <v>3.7</v>
       </c>
       <c r="C156" t="n">
-        <v>3.76</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="157">
@@ -3726,10 +3737,10 @@
         <v>45200</v>
       </c>
       <c r="B157" t="n">
-        <v>4.19</v>
+        <v>4.17</v>
       </c>
       <c r="C157" t="n">
-        <v>4.19</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="158">
@@ -3737,10 +3748,10 @@
         <v>45292</v>
       </c>
       <c r="B158" t="n">
-        <v>4.4</v>
+        <v>4.43</v>
       </c>
       <c r="C158" t="n">
-        <v>4.4</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="159">
@@ -3748,10 +3759,10 @@
         <v>45383</v>
       </c>
       <c r="B159" t="n">
-        <v>4.56</v>
+        <v>4.59</v>
       </c>
       <c r="C159" t="n">
-        <v>4.56</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="160">
@@ -3759,10 +3770,10 @@
         <v>45474</v>
       </c>
       <c r="B160" t="n">
-        <v>4.69</v>
+        <v>4.64</v>
       </c>
       <c r="C160" t="n">
-        <v>4.69</v>
+        <v>4.64</v>
       </c>
     </row>
     <row r="161">
@@ -3770,10 +3781,10 @@
         <v>45566</v>
       </c>
       <c r="B161" t="n">
-        <v>4.58</v>
+        <v>4.56</v>
       </c>
       <c r="C161" t="n">
-        <v>4.58</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="162">
@@ -3781,10 +3792,10 @@
         <v>45658</v>
       </c>
       <c r="B162" t="n">
-        <v>4.43</v>
+        <v>4.46</v>
       </c>
       <c r="C162" t="n">
-        <v>4.43</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="163">
@@ -3792,10 +3803,10 @@
         <v>45748</v>
       </c>
       <c r="B163" t="n">
-        <v>4.18</v>
+        <v>4.21</v>
       </c>
       <c r="C163" t="n">
-        <v>4.18</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="164">
@@ -3803,10 +3814,10 @@
         <v>45839</v>
       </c>
       <c r="B164" t="n">
-        <v>4.18</v>
+        <v>4.15</v>
       </c>
       <c r="C164" t="n">
-        <v>4.18</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="165">
@@ -3814,10 +3825,21 @@
         <v>45931</v>
       </c>
       <c r="B165" t="n">
-        <v>4.11</v>
+        <v>4.07</v>
       </c>
       <c r="C165" t="n">
-        <v>4.11</v>
+        <v>4.07</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B166" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="C166" t="n">
+        <v>3.84</v>
       </c>
     </row>
   </sheetData>
@@ -5486,7 +5508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C141"/>
+  <dimension ref="A1:C142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5522,10 +5544,10 @@
         <v>33329</v>
       </c>
       <c r="B3" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="C3" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="4">
@@ -5533,10 +5555,10 @@
         <v>33420</v>
       </c>
       <c r="B4" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="C4" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="5">
@@ -5577,10 +5599,10 @@
         <v>33786</v>
       </c>
       <c r="B8" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="C8" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="9">
@@ -5797,10 +5819,10 @@
         <v>35612</v>
       </c>
       <c r="B28" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="C28" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="29">
@@ -5808,10 +5830,10 @@
         <v>35704</v>
       </c>
       <c r="B29" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="C29" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="30">
@@ -5841,10 +5863,10 @@
         <v>35977</v>
       </c>
       <c r="B32" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="C32" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="33">
@@ -6028,10 +6050,10 @@
         <v>37530</v>
       </c>
       <c r="B49" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="50">
@@ -6039,10 +6061,10 @@
         <v>37622</v>
       </c>
       <c r="B50" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="C50" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="51">
@@ -6072,10 +6094,10 @@
         <v>37895</v>
       </c>
       <c r="B53" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="C53" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="54">
@@ -6083,10 +6105,10 @@
         <v>37987</v>
       </c>
       <c r="B54" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="C54" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="55">
@@ -6237,10 +6259,10 @@
         <v>39264</v>
       </c>
       <c r="B68" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="C68" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="69">
@@ -6259,10 +6281,10 @@
         <v>39448</v>
       </c>
       <c r="B70" t="n">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="C70" t="n">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="71">
@@ -6281,10 +6303,10 @@
         <v>39630</v>
       </c>
       <c r="B72" t="n">
-        <v>5.28</v>
+        <v>5.27</v>
       </c>
       <c r="C72" t="n">
-        <v>5.28</v>
+        <v>5.27</v>
       </c>
     </row>
     <row r="73">
@@ -6292,10 +6314,10 @@
         <v>39722</v>
       </c>
       <c r="B73" t="n">
-        <v>6.58</v>
+        <v>6.59</v>
       </c>
       <c r="C73" t="n">
-        <v>6.58</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="74">
@@ -6303,10 +6325,10 @@
         <v>39814</v>
       </c>
       <c r="B74" t="n">
-        <v>8.01</v>
+        <v>8</v>
       </c>
       <c r="C74" t="n">
-        <v>8.01</v>
+        <v>8</v>
       </c>
     </row>
     <row r="75">
@@ -6314,10 +6336,10 @@
         <v>39904</v>
       </c>
       <c r="B75" t="n">
-        <v>8.57</v>
+        <v>8.58</v>
       </c>
       <c r="C75" t="n">
-        <v>8.57</v>
+        <v>8.58</v>
       </c>
     </row>
     <row r="76">
@@ -6325,10 +6347,10 @@
         <v>39995</v>
       </c>
       <c r="B76" t="n">
-        <v>9.470000000000001</v>
+        <v>9.49</v>
       </c>
       <c r="C76" t="n">
-        <v>9.470000000000001</v>
+        <v>9.49</v>
       </c>
     </row>
     <row r="77">
@@ -6336,10 +6358,10 @@
         <v>40087</v>
       </c>
       <c r="B77" t="n">
-        <v>10.4</v>
+        <v>10.41</v>
       </c>
       <c r="C77" t="n">
-        <v>10.4</v>
+        <v>10.41</v>
       </c>
     </row>
     <row r="78">
@@ -6347,10 +6369,10 @@
         <v>40179</v>
       </c>
       <c r="B78" t="n">
-        <v>11.49</v>
+        <v>11.48</v>
       </c>
       <c r="C78" t="n">
-        <v>11.49</v>
+        <v>11.48</v>
       </c>
     </row>
     <row r="79">
@@ -6369,10 +6391,10 @@
         <v>40360</v>
       </c>
       <c r="B80" t="n">
-        <v>10.65</v>
+        <v>10.66</v>
       </c>
       <c r="C80" t="n">
-        <v>10.65</v>
+        <v>10.66</v>
       </c>
     </row>
     <row r="81">
@@ -6380,10 +6402,10 @@
         <v>40452</v>
       </c>
       <c r="B81" t="n">
-        <v>10.32</v>
+        <v>10.33</v>
       </c>
       <c r="C81" t="n">
-        <v>10.32</v>
+        <v>10.33</v>
       </c>
     </row>
     <row r="82">
@@ -6457,10 +6479,10 @@
         <v>41091</v>
       </c>
       <c r="B88" t="n">
-        <v>10.48</v>
+        <v>10.47</v>
       </c>
       <c r="C88" t="n">
-        <v>10.48</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="89">
@@ -6490,10 +6512,10 @@
         <v>41365</v>
       </c>
       <c r="B91" t="n">
-        <v>9.32</v>
+        <v>9.31</v>
       </c>
       <c r="C91" t="n">
-        <v>9.32</v>
+        <v>9.31</v>
       </c>
     </row>
     <row r="92">
@@ -6523,10 +6545,10 @@
         <v>41640</v>
       </c>
       <c r="B94" t="n">
-        <v>7.77</v>
+        <v>7.78</v>
       </c>
       <c r="C94" t="n">
-        <v>7.77</v>
+        <v>7.78</v>
       </c>
     </row>
     <row r="95">
@@ -6545,10 +6567,10 @@
         <v>41821</v>
       </c>
       <c r="B96" t="n">
-        <v>7.06</v>
+        <v>7.05</v>
       </c>
       <c r="C96" t="n">
-        <v>7.06</v>
+        <v>7.05</v>
       </c>
     </row>
     <row r="97">
@@ -6556,10 +6578,10 @@
         <v>41913</v>
       </c>
       <c r="B97" t="n">
-        <v>6.5</v>
+        <v>6.52</v>
       </c>
       <c r="C97" t="n">
-        <v>6.5</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="98">
@@ -6567,10 +6589,10 @@
         <v>42005</v>
       </c>
       <c r="B98" t="n">
-        <v>6.24</v>
+        <v>6.23</v>
       </c>
       <c r="C98" t="n">
-        <v>6.24</v>
+        <v>6.23</v>
       </c>
     </row>
     <row r="99">
@@ -6578,10 +6600,10 @@
         <v>42095</v>
       </c>
       <c r="B99" t="n">
-        <v>5.82</v>
+        <v>5.81</v>
       </c>
       <c r="C99" t="n">
-        <v>5.82</v>
+        <v>5.81</v>
       </c>
     </row>
     <row r="100">
@@ -6589,10 +6611,10 @@
         <v>42186</v>
       </c>
       <c r="B100" t="n">
-        <v>5.39</v>
+        <v>5.4</v>
       </c>
       <c r="C100" t="n">
-        <v>5.39</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="101">
@@ -6600,10 +6622,10 @@
         <v>42278</v>
       </c>
       <c r="B101" t="n">
-        <v>5.11</v>
+        <v>5.12</v>
       </c>
       <c r="C101" t="n">
-        <v>5.11</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="102">
@@ -6611,10 +6633,10 @@
         <v>42370</v>
       </c>
       <c r="B102" t="n">
-        <v>4.79</v>
+        <v>4.78</v>
       </c>
       <c r="C102" t="n">
-        <v>4.79</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="103">
@@ -6842,10 +6864,10 @@
         <v>44287</v>
       </c>
       <c r="B123" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="C123" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="124">
@@ -6886,10 +6908,10 @@
         <v>44652</v>
       </c>
       <c r="B127" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="C127" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="128">
@@ -6996,10 +7018,10 @@
         <v>45566</v>
       </c>
       <c r="B137" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="C137" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="138">
@@ -7007,10 +7029,10 @@
         <v>45658</v>
       </c>
       <c r="B138" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="C138" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="139">
@@ -7018,10 +7040,10 @@
         <v>45748</v>
       </c>
       <c r="B139" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="C139" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="140">
@@ -7040,10 +7062,21 @@
         <v>45931</v>
       </c>
       <c r="B141" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="C141" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B142" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.89</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -28552,7 +28552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3098"/>
+  <dimension ref="A1:C3099"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62633,10 +62633,21 @@
         <v>46151</v>
       </c>
       <c r="B3098" t="n">
-        <v>211000</v>
+        <v>212000</v>
       </c>
       <c r="C3098" t="n">
-        <v>211000</v>
+        <v>212000</v>
+      </c>
+    </row>
+    <row r="3099">
+      <c r="A3099" s="1" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B3099" t="n">
+        <v>209000</v>
+      </c>
+      <c r="C3099" t="n">
+        <v>209000</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -28552,7 +28552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3099"/>
+  <dimension ref="A1:C3100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62644,10 +62644,21 @@
         <v>46158</v>
       </c>
       <c r="B3099" t="n">
-        <v>209000</v>
+        <v>210000</v>
       </c>
       <c r="C3099" t="n">
-        <v>209000</v>
+        <v>210000</v>
+      </c>
+    </row>
+    <row r="3100">
+      <c r="A3100" s="1" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B3100" t="n">
+        <v>215000</v>
+      </c>
+      <c r="C3100" t="n">
+        <v>215000</v>
       </c>
     </row>
   </sheetData>
@@ -62661,7 +62672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C808"/>
+  <dimension ref="A1:C809"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71497,10 +71508,10 @@
         <v>45931</v>
       </c>
       <c r="B803" t="n">
-        <v>18063.1</v>
+        <v>18037.3</v>
       </c>
       <c r="C803" t="n">
-        <v>18063.1</v>
+        <v>18037.3</v>
       </c>
     </row>
     <row r="804">
@@ -71508,10 +71519,10 @@
         <v>45962</v>
       </c>
       <c r="B804" t="n">
-        <v>18078.6</v>
+        <v>18035.1</v>
       </c>
       <c r="C804" t="n">
-        <v>18078.6</v>
+        <v>18035.1</v>
       </c>
     </row>
     <row r="805">
@@ -71519,10 +71530,10 @@
         <v>45992</v>
       </c>
       <c r="B805" t="n">
-        <v>18070.6</v>
+        <v>18018.5</v>
       </c>
       <c r="C805" t="n">
-        <v>18070.6</v>
+        <v>18018.5</v>
       </c>
     </row>
     <row r="806">
@@ -71530,10 +71541,10 @@
         <v>46023</v>
       </c>
       <c r="B806" t="n">
-        <v>18187</v>
+        <v>18132.2</v>
       </c>
       <c r="C806" t="n">
-        <v>18187</v>
+        <v>18132.2</v>
       </c>
     </row>
     <row r="807">
@@ -71541,10 +71552,10 @@
         <v>46054</v>
       </c>
       <c r="B807" t="n">
-        <v>18118.9</v>
+        <v>18048.5</v>
       </c>
       <c r="C807" t="n">
-        <v>18118.9</v>
+        <v>18048.5</v>
       </c>
     </row>
     <row r="808">
@@ -71552,10 +71563,21 @@
         <v>46082</v>
       </c>
       <c r="B808" t="n">
-        <v>18108.7</v>
+        <v>18019.6</v>
       </c>
       <c r="C808" t="n">
-        <v>18108.7</v>
+        <v>18019.6</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B809" t="n">
+        <v>17932.6</v>
+      </c>
+      <c r="C809" t="n">
+        <v>17932.6</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -14810,7 +14810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C305"/>
+  <dimension ref="A1:C306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18168,10 +18168,21 @@
         <v>46082</v>
       </c>
       <c r="B305" t="n">
-        <v>6866</v>
+        <v>6887</v>
       </c>
       <c r="C305" t="n">
-        <v>6.866</v>
+        <v>6.887</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B306" t="n">
+        <v>7618</v>
+      </c>
+      <c r="C306" t="n">
+        <v>7.618</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -28563,7 +28563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3100"/>
+  <dimension ref="A1:C3101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62666,10 +62666,21 @@
         <v>46165</v>
       </c>
       <c r="B3100" t="n">
-        <v>215000</v>
+        <v>212000</v>
       </c>
       <c r="C3100" t="n">
-        <v>215000</v>
+        <v>212000</v>
+      </c>
+    </row>
+    <row r="3101">
+      <c r="A3101" s="1" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B3101" t="n">
+        <v>225000</v>
+      </c>
+      <c r="C3101" t="n">
+        <v>225000</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -18196,7 +18196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C941"/>
+  <dimension ref="A1:C942"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28549,6 +28549,17 @@
         <v>4.3</v>
       </c>
       <c r="C941" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B942" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C942" t="n">
         <v>4.3</v>
       </c>
     </row>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -7090,7 +7090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C700"/>
+  <dimension ref="A1:C701"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14738,10 +14738,10 @@
         <v>45931</v>
       </c>
       <c r="B695" t="n">
-        <v>1317148.1</v>
+        <v>1317360.61</v>
       </c>
       <c r="C695" t="n">
-        <v>1317148.1</v>
+        <v>1317360.61</v>
       </c>
     </row>
     <row r="696">
@@ -14749,10 +14749,10 @@
         <v>45962</v>
       </c>
       <c r="B696" t="n">
-        <v>1316163.19</v>
+        <v>1316595.89</v>
       </c>
       <c r="C696" t="n">
-        <v>1316163.19</v>
+        <v>1316595.89</v>
       </c>
     </row>
     <row r="697">
@@ -14760,10 +14760,10 @@
         <v>45992</v>
       </c>
       <c r="B697" t="n">
-        <v>1324321.51</v>
+        <v>1324322.54</v>
       </c>
       <c r="C697" t="n">
-        <v>1324321.51</v>
+        <v>1324322.54</v>
       </c>
     </row>
     <row r="698">
@@ -14771,10 +14771,10 @@
         <v>46023</v>
       </c>
       <c r="B698" t="n">
-        <v>1326575.31</v>
+        <v>1325847.84</v>
       </c>
       <c r="C698" t="n">
-        <v>1326575.31</v>
+        <v>1325847.84</v>
       </c>
     </row>
     <row r="699">
@@ -14782,10 +14782,10 @@
         <v>46054</v>
       </c>
       <c r="B699" t="n">
-        <v>1326953.92</v>
+        <v>1326709.14</v>
       </c>
       <c r="C699" t="n">
-        <v>1326953.92</v>
+        <v>1326709.14</v>
       </c>
     </row>
     <row r="700">
@@ -14793,10 +14793,21 @@
         <v>46082</v>
       </c>
       <c r="B700" t="n">
-        <v>1336987.42</v>
+        <v>1337051.75</v>
       </c>
       <c r="C700" t="n">
-        <v>1336987.42</v>
+        <v>1337051.75</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B701" t="n">
+        <v>1348688.3</v>
+      </c>
+      <c r="C701" t="n">
+        <v>1348688.3</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -28585,7 +28585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3101"/>
+  <dimension ref="A1:C3102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62703,6 +62703,17 @@
       </c>
       <c r="C3101" t="n">
         <v>225000</v>
+      </c>
+    </row>
+    <row r="3102">
+      <c r="A3102" s="1" t="n">
+        <v>46179</v>
+      </c>
+      <c r="B3102" t="n">
+        <v>229000</v>
+      </c>
+      <c r="C3102" t="n">
+        <v>229000</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -28585,7 +28585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3102"/>
+  <dimension ref="A1:C3103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62710,10 +62710,21 @@
         <v>46179</v>
       </c>
       <c r="B3102" t="n">
-        <v>229000</v>
+        <v>230000</v>
       </c>
       <c r="C3102" t="n">
-        <v>229000</v>
+        <v>230000</v>
+      </c>
+    </row>
+    <row r="3103">
+      <c r="A3103" s="1" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B3103" t="n">
+        <v>226000</v>
+      </c>
+      <c r="C3103" t="n">
+        <v>226000</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -3853,7 +3853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C185"/>
+  <dimension ref="A1:C186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4974,10 +4974,10 @@
         <v>41640</v>
       </c>
       <c r="B138" t="n">
-        <v>11.883755</v>
+        <v>11.883758</v>
       </c>
       <c r="C138" t="n">
-        <v>11.883755</v>
+        <v>11.883758</v>
       </c>
     </row>
     <row r="139">
@@ -4985,10 +4985,10 @@
         <v>41730</v>
       </c>
       <c r="B139" t="n">
-        <v>11.621135</v>
+        <v>11.62114</v>
       </c>
       <c r="C139" t="n">
-        <v>11.621135</v>
+        <v>11.62114</v>
       </c>
     </row>
     <row r="140">
@@ -4996,10 +4996,10 @@
         <v>41821</v>
       </c>
       <c r="B140" t="n">
-        <v>11.646939</v>
+        <v>11.646947</v>
       </c>
       <c r="C140" t="n">
-        <v>11.646939</v>
+        <v>11.646947</v>
       </c>
     </row>
     <row r="141">
@@ -5007,10 +5007,10 @@
         <v>41913</v>
       </c>
       <c r="B141" t="n">
-        <v>11.631985</v>
+        <v>11.631993</v>
       </c>
       <c r="C141" t="n">
-        <v>11.631985</v>
+        <v>11.631993</v>
       </c>
     </row>
     <row r="142">
@@ -5018,10 +5018,10 @@
         <v>42005</v>
       </c>
       <c r="B142" t="n">
-        <v>11.556623</v>
+        <v>11.556634</v>
       </c>
       <c r="C142" t="n">
-        <v>11.556623</v>
+        <v>11.556634</v>
       </c>
     </row>
     <row r="143">
@@ -5029,10 +5029,10 @@
         <v>42095</v>
       </c>
       <c r="B143" t="n">
-        <v>11.485132</v>
+        <v>11.485147</v>
       </c>
       <c r="C143" t="n">
-        <v>11.485132</v>
+        <v>11.485147</v>
       </c>
     </row>
     <row r="144">
@@ -5040,10 +5040,10 @@
         <v>42186</v>
       </c>
       <c r="B144" t="n">
-        <v>11.606478</v>
+        <v>11.606488</v>
       </c>
       <c r="C144" t="n">
-        <v>11.606478</v>
+        <v>11.606488</v>
       </c>
     </row>
     <row r="145">
@@ -5051,10 +5051,10 @@
         <v>42278</v>
       </c>
       <c r="B145" t="n">
-        <v>11.738968</v>
+        <v>11.738976</v>
       </c>
       <c r="C145" t="n">
-        <v>11.738968</v>
+        <v>11.738976</v>
       </c>
     </row>
     <row r="146">
@@ -5062,10 +5062,10 @@
         <v>42370</v>
       </c>
       <c r="B146" t="n">
-        <v>11.763236</v>
+        <v>11.763247</v>
       </c>
       <c r="C146" t="n">
-        <v>11.763236</v>
+        <v>11.763247</v>
       </c>
     </row>
     <row r="147">
@@ -5073,10 +5073,10 @@
         <v>42461</v>
       </c>
       <c r="B147" t="n">
-        <v>11.766097</v>
+        <v>11.766109</v>
       </c>
       <c r="C147" t="n">
-        <v>11.766097</v>
+        <v>11.766109</v>
       </c>
     </row>
     <row r="148">
@@ -5084,10 +5084,10 @@
         <v>42552</v>
       </c>
       <c r="B148" t="n">
-        <v>11.769843</v>
+        <v>11.769855</v>
       </c>
       <c r="C148" t="n">
-        <v>11.769843</v>
+        <v>11.769855</v>
       </c>
     </row>
     <row r="149">
@@ -5095,10 +5095,10 @@
         <v>42644</v>
       </c>
       <c r="B149" t="n">
-        <v>11.865809</v>
+        <v>11.865818</v>
       </c>
       <c r="C149" t="n">
-        <v>11.865809</v>
+        <v>11.865818</v>
       </c>
     </row>
     <row r="150">
@@ -5106,10 +5106,10 @@
         <v>42736</v>
       </c>
       <c r="B150" t="n">
-        <v>11.723754</v>
+        <v>11.723758</v>
       </c>
       <c r="C150" t="n">
-        <v>11.723754</v>
+        <v>11.723758</v>
       </c>
     </row>
     <row r="151">
@@ -5117,10 +5117,10 @@
         <v>42826</v>
       </c>
       <c r="B151" t="n">
-        <v>11.756978</v>
+        <v>11.756991</v>
       </c>
       <c r="C151" t="n">
-        <v>11.756978</v>
+        <v>11.756991</v>
       </c>
     </row>
     <row r="152">
@@ -5128,10 +5128,10 @@
         <v>42917</v>
       </c>
       <c r="B152" t="n">
-        <v>11.818432</v>
+        <v>11.818444</v>
       </c>
       <c r="C152" t="n">
-        <v>11.818432</v>
+        <v>11.818444</v>
       </c>
     </row>
     <row r="153">
@@ -5139,10 +5139,10 @@
         <v>43009</v>
       </c>
       <c r="B153" t="n">
-        <v>11.816692</v>
+        <v>11.816704</v>
       </c>
       <c r="C153" t="n">
-        <v>11.816692</v>
+        <v>11.816704</v>
       </c>
     </row>
     <row r="154">
@@ -5150,10 +5150,10 @@
         <v>43101</v>
       </c>
       <c r="B154" t="n">
-        <v>11.644577</v>
+        <v>11.644589</v>
       </c>
       <c r="C154" t="n">
-        <v>11.644577</v>
+        <v>11.644589</v>
       </c>
     </row>
     <row r="155">
@@ -5161,10 +5161,10 @@
         <v>43191</v>
       </c>
       <c r="B155" t="n">
-        <v>11.598376</v>
+        <v>11.598389</v>
       </c>
       <c r="C155" t="n">
-        <v>11.598376</v>
+        <v>11.598389</v>
       </c>
     </row>
     <row r="156">
@@ -5172,10 +5172,10 @@
         <v>43282</v>
       </c>
       <c r="B156" t="n">
-        <v>11.619565</v>
+        <v>11.619573</v>
       </c>
       <c r="C156" t="n">
-        <v>11.619565</v>
+        <v>11.619573</v>
       </c>
     </row>
     <row r="157">
@@ -5183,10 +5183,10 @@
         <v>43374</v>
       </c>
       <c r="B157" t="n">
-        <v>11.666399</v>
+        <v>11.66641</v>
       </c>
       <c r="C157" t="n">
-        <v>11.666399</v>
+        <v>11.66641</v>
       </c>
     </row>
     <row r="158">
@@ -5194,10 +5194,10 @@
         <v>43466</v>
       </c>
       <c r="B158" t="n">
-        <v>11.499899</v>
+        <v>11.49991</v>
       </c>
       <c r="C158" t="n">
-        <v>11.499899</v>
+        <v>11.49991</v>
       </c>
     </row>
     <row r="159">
@@ -5205,10 +5205,10 @@
         <v>43556</v>
       </c>
       <c r="B159" t="n">
-        <v>11.626984</v>
+        <v>11.626991</v>
       </c>
       <c r="C159" t="n">
-        <v>11.626984</v>
+        <v>11.626991</v>
       </c>
     </row>
     <row r="160">
@@ -5216,10 +5216,10 @@
         <v>43647</v>
       </c>
       <c r="B160" t="n">
-        <v>11.646573</v>
+        <v>11.646611</v>
       </c>
       <c r="C160" t="n">
-        <v>11.646573</v>
+        <v>11.646611</v>
       </c>
     </row>
     <row r="161">
@@ -5227,10 +5227,10 @@
         <v>43739</v>
       </c>
       <c r="B161" t="n">
-        <v>11.727611</v>
+        <v>11.727653</v>
       </c>
       <c r="C161" t="n">
-        <v>11.727611</v>
+        <v>11.727653</v>
       </c>
     </row>
     <row r="162">
@@ -5238,10 +5238,10 @@
         <v>43831</v>
       </c>
       <c r="B162" t="n">
-        <v>11.591122</v>
+        <v>11.591159</v>
       </c>
       <c r="C162" t="n">
-        <v>11.591122</v>
+        <v>11.591159</v>
       </c>
     </row>
     <row r="163">
@@ -5249,10 +5249,10 @@
         <v>43922</v>
       </c>
       <c r="B163" t="n">
-        <v>9.739837</v>
+        <v>9.739844</v>
       </c>
       <c r="C163" t="n">
-        <v>9.739837</v>
+        <v>9.739844</v>
       </c>
     </row>
     <row r="164">
@@ -5260,10 +5260,10 @@
         <v>44013</v>
       </c>
       <c r="B164" t="n">
-        <v>10.058475</v>
+        <v>10.05851</v>
       </c>
       <c r="C164" t="n">
-        <v>10.058475</v>
+        <v>10.05851</v>
       </c>
     </row>
     <row r="165">
@@ -5271,10 +5271,10 @@
         <v>44105</v>
       </c>
       <c r="B165" t="n">
-        <v>10.389341</v>
+        <v>10.389381</v>
       </c>
       <c r="C165" t="n">
-        <v>10.389341</v>
+        <v>10.389381</v>
       </c>
     </row>
     <row r="166">
@@ -5282,10 +5282,10 @@
         <v>44197</v>
       </c>
       <c r="B166" t="n">
-        <v>9.051425999999999</v>
+        <v>9.051456999999999</v>
       </c>
       <c r="C166" t="n">
-        <v>9.051425999999999</v>
+        <v>9.051456999999999</v>
       </c>
     </row>
     <row r="167">
@@ -5293,10 +5293,10 @@
         <v>44287</v>
       </c>
       <c r="B167" t="n">
-        <v>9.840987999999999</v>
+        <v>9.841025</v>
       </c>
       <c r="C167" t="n">
-        <v>9.840987999999999</v>
+        <v>9.841025</v>
       </c>
     </row>
     <row r="168">
@@ -5304,10 +5304,10 @@
         <v>44378</v>
       </c>
       <c r="B168" t="n">
-        <v>10.009574</v>
+        <v>10.009588</v>
       </c>
       <c r="C168" t="n">
-        <v>10.009574</v>
+        <v>10.009588</v>
       </c>
     </row>
     <row r="169">
@@ -5315,10 +5315,10 @@
         <v>44470</v>
       </c>
       <c r="B169" t="n">
-        <v>10.228773</v>
+        <v>10.228796</v>
       </c>
       <c r="C169" t="n">
-        <v>10.228773</v>
+        <v>10.228796</v>
       </c>
     </row>
     <row r="170">
@@ -5326,10 +5326,10 @@
         <v>44562</v>
       </c>
       <c r="B170" t="n">
-        <v>10.472376</v>
+        <v>10.472393</v>
       </c>
       <c r="C170" t="n">
-        <v>10.472376</v>
+        <v>10.472393</v>
       </c>
     </row>
     <row r="171">
@@ -5337,10 +5337,10 @@
         <v>44652</v>
       </c>
       <c r="B171" t="n">
-        <v>10.684715</v>
+        <v>10.684739</v>
       </c>
       <c r="C171" t="n">
-        <v>10.684715</v>
+        <v>10.684739</v>
       </c>
     </row>
     <row r="172">
@@ -5348,10 +5348,10 @@
         <v>44743</v>
       </c>
       <c r="B172" t="n">
-        <v>10.567813</v>
+        <v>10.567838</v>
       </c>
       <c r="C172" t="n">
-        <v>10.567813</v>
+        <v>10.567838</v>
       </c>
     </row>
     <row r="173">
@@ -5359,10 +5359,10 @@
         <v>44835</v>
       </c>
       <c r="B173" t="n">
-        <v>10.736908</v>
+        <v>10.736945</v>
       </c>
       <c r="C173" t="n">
-        <v>10.736908</v>
+        <v>10.736945</v>
       </c>
     </row>
     <row r="174">
@@ -5370,10 +5370,10 @@
         <v>44927</v>
       </c>
       <c r="B174" t="n">
-        <v>10.564065</v>
+        <v>10.564109</v>
       </c>
       <c r="C174" t="n">
-        <v>10.564065</v>
+        <v>10.564109</v>
       </c>
     </row>
     <row r="175">
@@ -5381,10 +5381,10 @@
         <v>45017</v>
       </c>
       <c r="B175" t="n">
-        <v>10.576964</v>
+        <v>10.577002</v>
       </c>
       <c r="C175" t="n">
-        <v>10.576964</v>
+        <v>10.577002</v>
       </c>
     </row>
     <row r="176">
@@ -5392,10 +5392,10 @@
         <v>45108</v>
       </c>
       <c r="B176" t="n">
-        <v>10.747803</v>
+        <v>10.747842</v>
       </c>
       <c r="C176" t="n">
-        <v>10.747803</v>
+        <v>10.747842</v>
       </c>
     </row>
     <row r="177">
@@ -5403,10 +5403,10 @@
         <v>45200</v>
       </c>
       <c r="B177" t="n">
-        <v>11.096103</v>
+        <v>11.096141</v>
       </c>
       <c r="C177" t="n">
-        <v>11.096103</v>
+        <v>11.096141</v>
       </c>
     </row>
     <row r="178">
@@ -5414,10 +5414,10 @@
         <v>45292</v>
       </c>
       <c r="B178" t="n">
-        <v>11.058844</v>
+        <v>11.058904</v>
       </c>
       <c r="C178" t="n">
-        <v>11.058844</v>
+        <v>11.058904</v>
       </c>
     </row>
     <row r="179">
@@ -5425,10 +5425,10 @@
         <v>45383</v>
       </c>
       <c r="B179" t="n">
-        <v>11.0193</v>
+        <v>11.01936</v>
       </c>
       <c r="C179" t="n">
-        <v>11.0193</v>
+        <v>11.01936</v>
       </c>
     </row>
     <row r="180">
@@ -5436,10 +5436,10 @@
         <v>45474</v>
       </c>
       <c r="B180" t="n">
-        <v>11.138746</v>
+        <v>11.138759</v>
       </c>
       <c r="C180" t="n">
-        <v>11.138746</v>
+        <v>11.138759</v>
       </c>
     </row>
     <row r="181">
@@ -5447,10 +5447,10 @@
         <v>45566</v>
       </c>
       <c r="B181" t="n">
-        <v>11.122474</v>
+        <v>11.122486</v>
       </c>
       <c r="C181" t="n">
-        <v>11.122474</v>
+        <v>11.122486</v>
       </c>
     </row>
     <row r="182">
@@ -5458,10 +5458,10 @@
         <v>45658</v>
       </c>
       <c r="B182" t="n">
-        <v>11.105374</v>
+        <v>11.105381</v>
       </c>
       <c r="C182" t="n">
-        <v>11.105374</v>
+        <v>11.105381</v>
       </c>
     </row>
     <row r="183">
@@ -5469,10 +5469,10 @@
         <v>45748</v>
       </c>
       <c r="B183" t="n">
-        <v>11.124175</v>
+        <v>11.124241</v>
       </c>
       <c r="C183" t="n">
-        <v>11.124175</v>
+        <v>11.124241</v>
       </c>
     </row>
     <row r="184">
@@ -5480,10 +5480,10 @@
         <v>45839</v>
       </c>
       <c r="B184" t="n">
-        <v>11.257951</v>
+        <v>11.229451</v>
       </c>
       <c r="C184" t="n">
-        <v>11.257951</v>
+        <v>11.229451</v>
       </c>
     </row>
     <row r="185">
@@ -5491,10 +5491,21 @@
         <v>45931</v>
       </c>
       <c r="B185" t="n">
-        <v>11.323096</v>
+        <v>11.322759</v>
       </c>
       <c r="C185" t="n">
-        <v>11.323096</v>
+        <v>11.322759</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B186" t="n">
+        <v>11.164138</v>
+      </c>
+      <c r="C186" t="n">
+        <v>11.164138</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -28596,7 +28596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3103"/>
+  <dimension ref="A1:C3104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62732,10 +62732,21 @@
         <v>46186</v>
       </c>
       <c r="B3103" t="n">
-        <v>226000</v>
+        <v>227000</v>
       </c>
       <c r="C3103" t="n">
-        <v>226000</v>
+        <v>227000</v>
+      </c>
+    </row>
+    <row r="3104">
+      <c r="A3104" s="1" t="n">
+        <v>46193</v>
+      </c>
+      <c r="B3104" t="n">
+        <v>215000</v>
+      </c>
+      <c r="C3104" t="n">
+        <v>215000</v>
       </c>
     </row>
   </sheetData>
@@ -62749,7 +62760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C809"/>
+  <dimension ref="A1:C810"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71618,10 +71629,10 @@
         <v>46023</v>
       </c>
       <c r="B806" t="n">
-        <v>18132.2</v>
+        <v>18134.6</v>
       </c>
       <c r="C806" t="n">
-        <v>18132.2</v>
+        <v>18134.6</v>
       </c>
     </row>
     <row r="807">
@@ -71629,10 +71640,10 @@
         <v>46054</v>
       </c>
       <c r="B807" t="n">
-        <v>18048.5</v>
+        <v>18051.9</v>
       </c>
       <c r="C807" t="n">
-        <v>18048.5</v>
+        <v>18051.9</v>
       </c>
     </row>
     <row r="808">
@@ -71640,10 +71651,10 @@
         <v>46082</v>
       </c>
       <c r="B808" t="n">
-        <v>18019.6</v>
+        <v>18030.5</v>
       </c>
       <c r="C808" t="n">
-        <v>18019.6</v>
+        <v>18030.5</v>
       </c>
     </row>
     <row r="809">
@@ -71651,10 +71662,21 @@
         <v>46113</v>
       </c>
       <c r="B809" t="n">
-        <v>17932.6</v>
+        <v>17938.8</v>
       </c>
       <c r="C809" t="n">
-        <v>17932.6</v>
+        <v>17938.8</v>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B810" t="n">
+        <v>17983.8</v>
+      </c>
+      <c r="C810" t="n">
+        <v>17983.8</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -14832,7 +14832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C306"/>
+  <dimension ref="A1:C307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18201,10 +18201,21 @@
         <v>46113</v>
       </c>
       <c r="B306" t="n">
-        <v>7618</v>
+        <v>7585</v>
       </c>
       <c r="C306" t="n">
-        <v>7.618</v>
+        <v>7.585</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B307" t="n">
+        <v>7594</v>
+      </c>
+      <c r="C307" t="n">
+        <v>7.594</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -18229,7 +18229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C942"/>
+  <dimension ref="A1:C943"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28594,6 +28594,17 @@
       </c>
       <c r="C942" t="n">
         <v>4.3</v>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B943" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C943" t="n">
+        <v>4.2</v>
       </c>
     </row>
   </sheetData>
@@ -28607,7 +28618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3104"/>
+  <dimension ref="A1:C3105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62754,9 +62765,20 @@
         <v>46193</v>
       </c>
       <c r="B3104" t="n">
+        <v>216000</v>
+      </c>
+      <c r="C3104" t="n">
+        <v>216000</v>
+      </c>
+    </row>
+    <row r="3105">
+      <c r="A3105" s="1" t="n">
+        <v>46200</v>
+      </c>
+      <c r="B3105" t="n">
         <v>215000</v>
       </c>
-      <c r="C3104" t="n">
+      <c r="C3105" t="n">
         <v>215000</v>
       </c>
     </row>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -7101,7 +7101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C701"/>
+  <dimension ref="A1:C702"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14749,10 +14749,10 @@
         <v>45931</v>
       </c>
       <c r="B695" t="n">
-        <v>1317360.61</v>
+        <v>1317360.55</v>
       </c>
       <c r="C695" t="n">
-        <v>1317360.61</v>
+        <v>1317360.55</v>
       </c>
     </row>
     <row r="696">
@@ -14760,10 +14760,10 @@
         <v>45962</v>
       </c>
       <c r="B696" t="n">
-        <v>1316595.89</v>
+        <v>1316595.76</v>
       </c>
       <c r="C696" t="n">
-        <v>1316595.89</v>
+        <v>1316595.76</v>
       </c>
     </row>
     <row r="697">
@@ -14771,10 +14771,10 @@
         <v>45992</v>
       </c>
       <c r="B697" t="n">
-        <v>1324322.54</v>
+        <v>1324322.36</v>
       </c>
       <c r="C697" t="n">
-        <v>1324322.54</v>
+        <v>1324322.36</v>
       </c>
     </row>
     <row r="698">
@@ -14782,10 +14782,10 @@
         <v>46023</v>
       </c>
       <c r="B698" t="n">
-        <v>1325847.84</v>
+        <v>1326134.9</v>
       </c>
       <c r="C698" t="n">
-        <v>1325847.84</v>
+        <v>1326134.9</v>
       </c>
     </row>
     <row r="699">
@@ -14793,10 +14793,10 @@
         <v>46054</v>
       </c>
       <c r="B699" t="n">
-        <v>1326709.14</v>
+        <v>1327271.55</v>
       </c>
       <c r="C699" t="n">
-        <v>1326709.14</v>
+        <v>1327271.55</v>
       </c>
     </row>
     <row r="700">
@@ -14804,10 +14804,10 @@
         <v>46082</v>
       </c>
       <c r="B700" t="n">
-        <v>1337051.75</v>
+        <v>1337959.33</v>
       </c>
       <c r="C700" t="n">
-        <v>1337051.75</v>
+        <v>1337959.33</v>
       </c>
     </row>
     <row r="701">
@@ -14815,10 +14815,21 @@
         <v>46113</v>
       </c>
       <c r="B701" t="n">
-        <v>1348688.3</v>
+        <v>1349505.63</v>
       </c>
       <c r="C701" t="n">
-        <v>1348688.3</v>
+        <v>1349505.63</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B702" t="n">
+        <v>1344207.79</v>
+      </c>
+      <c r="C702" t="n">
+        <v>1344207.79</v>
       </c>
     </row>
   </sheetData>
@@ -28618,7 +28629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3105"/>
+  <dimension ref="A1:C3106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62776,9 +62787,20 @@
         <v>46200</v>
       </c>
       <c r="B3105" t="n">
+        <v>217000</v>
+      </c>
+      <c r="C3105" t="n">
+        <v>217000</v>
+      </c>
+    </row>
+    <row r="3106">
+      <c r="A3106" s="1" t="n">
+        <v>46207</v>
+      </c>
+      <c r="B3106" t="n">
         <v>215000</v>
       </c>
-      <c r="C3105" t="n">
+      <c r="C3106" t="n">
         <v>215000</v>
       </c>
     </row>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -28629,7 +28629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3106"/>
+  <dimension ref="A1:C3107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62798,10 +62798,21 @@
         <v>46207</v>
       </c>
       <c r="B3106" t="n">
-        <v>215000</v>
+        <v>216000</v>
       </c>
       <c r="C3106" t="n">
-        <v>215000</v>
+        <v>216000</v>
+      </c>
+    </row>
+    <row r="3107">
+      <c r="A3107" s="1" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B3107" t="n">
+        <v>208000</v>
+      </c>
+      <c r="C3107" t="n">
+        <v>208000</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -28629,7 +28629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3107"/>
+  <dimension ref="A1:C3108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62798,10 +62798,10 @@
         <v>46207</v>
       </c>
       <c r="B3106" t="n">
-        <v>216000</v>
+        <v>217000</v>
       </c>
       <c r="C3106" t="n">
-        <v>216000</v>
+        <v>217000</v>
       </c>
     </row>
     <row r="3107">
@@ -62809,10 +62809,21 @@
         <v>46214</v>
       </c>
       <c r="B3107" t="n">
-        <v>208000</v>
+        <v>209000</v>
       </c>
       <c r="C3107" t="n">
-        <v>208000</v>
+        <v>209000</v>
+      </c>
+    </row>
+    <row r="3108">
+      <c r="A3108" s="1" t="n">
+        <v>46221</v>
+      </c>
+      <c r="B3108" t="n">
+        <v>187000</v>
+      </c>
+      <c r="C3108" t="n">
+        <v>187000</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -28629,7 +28629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3108"/>
+  <dimension ref="A1:C3109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62820,10 +62820,21 @@
         <v>46221</v>
       </c>
       <c r="B3108" t="n">
-        <v>187000</v>
+        <v>188000</v>
       </c>
       <c r="C3108" t="n">
-        <v>187000</v>
+        <v>188000</v>
+      </c>
+    </row>
+    <row r="3109">
+      <c r="A3109" s="1" t="n">
+        <v>46228</v>
+      </c>
+      <c r="B3109" t="n">
+        <v>197000</v>
+      </c>
+      <c r="C3109" t="n">
+        <v>197000</v>
       </c>
     </row>
   </sheetData>
@@ -62837,7 +62848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C810"/>
+  <dimension ref="A1:C811"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71739,10 +71750,10 @@
         <v>46113</v>
       </c>
       <c r="B809" t="n">
-        <v>17938.8</v>
+        <v>17956.2</v>
       </c>
       <c r="C809" t="n">
-        <v>17938.8</v>
+        <v>17956.2</v>
       </c>
     </row>
     <row r="810">
@@ -71750,10 +71761,21 @@
         <v>46143</v>
       </c>
       <c r="B810" t="n">
-        <v>17983.8</v>
+        <v>17999.8</v>
       </c>
       <c r="C810" t="n">
-        <v>17983.8</v>
+        <v>17999.8</v>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B811" t="n">
+        <v>18056.1</v>
+      </c>
+      <c r="C811" t="n">
+        <v>18056.1</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -14843,7 +14843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C307"/>
+  <dimension ref="A1:C308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18223,10 +18223,21 @@
         <v>46143</v>
       </c>
       <c r="B307" t="n">
-        <v>7594</v>
+        <v>7537</v>
       </c>
       <c r="C307" t="n">
-        <v>7.594</v>
+        <v>7.537</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B308" t="n">
+        <v>7359</v>
+      </c>
+      <c r="C308" t="n">
+        <v>7.359</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -28640,7 +28640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3109"/>
+  <dimension ref="A1:C3110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62831,10 +62831,10 @@
         <v>46221</v>
       </c>
       <c r="B3108" t="n">
-        <v>188000</v>
+        <v>189000</v>
       </c>
       <c r="C3108" t="n">
-        <v>188000</v>
+        <v>189000</v>
       </c>
     </row>
     <row r="3109">
@@ -62842,10 +62842,21 @@
         <v>46228</v>
       </c>
       <c r="B3109" t="n">
-        <v>197000</v>
+        <v>198000</v>
       </c>
       <c r="C3109" t="n">
-        <v>197000</v>
+        <v>198000</v>
+      </c>
+    </row>
+    <row r="3110">
+      <c r="A3110" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B3110" t="n">
+        <v>199000</v>
+      </c>
+      <c r="C3110" t="n">
+        <v>199000</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -18251,7 +18251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C943"/>
+  <dimension ref="A1:C944"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28627,6 +28627,17 @@
       </c>
       <c r="C943" t="n">
         <v>4.2</v>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B944" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="C944" t="n">
+        <v>4.1</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -7101,7 +7101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C702"/>
+  <dimension ref="A1:C703"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14419,10 +14419,10 @@
         <v>45017</v>
       </c>
       <c r="B665" t="n">
-        <v>1232543.71</v>
+        <v>1232544.16</v>
       </c>
       <c r="C665" t="n">
-        <v>1232543.71</v>
+        <v>1232544.16</v>
       </c>
     </row>
     <row r="666">
@@ -14430,10 +14430,10 @@
         <v>45047</v>
       </c>
       <c r="B666" t="n">
-        <v>1241274.52</v>
+        <v>1241274.33</v>
       </c>
       <c r="C666" t="n">
-        <v>1241274.52</v>
+        <v>1241274.33</v>
       </c>
     </row>
     <row r="667">
@@ -14441,10 +14441,10 @@
         <v>45078</v>
       </c>
       <c r="B667" t="n">
-        <v>1247629.97</v>
+        <v>1247630.05</v>
       </c>
       <c r="C667" t="n">
-        <v>1247629.97</v>
+        <v>1247630.05</v>
       </c>
     </row>
     <row r="668">
@@ -14452,10 +14452,10 @@
         <v>45108</v>
       </c>
       <c r="B668" t="n">
-        <v>1255755.94</v>
+        <v>1255749.42</v>
       </c>
       <c r="C668" t="n">
-        <v>1255755.94</v>
+        <v>1255749.42</v>
       </c>
     </row>
     <row r="669">
@@ -14463,10 +14463,10 @@
         <v>45139</v>
       </c>
       <c r="B669" t="n">
-        <v>1271810.03</v>
+        <v>1271808.6</v>
       </c>
       <c r="C669" t="n">
-        <v>1271810.03</v>
+        <v>1271808.6</v>
       </c>
     </row>
     <row r="670">
@@ -14474,10 +14474,10 @@
         <v>45170</v>
       </c>
       <c r="B670" t="n">
-        <v>1277927.44</v>
+        <v>1277927.45</v>
       </c>
       <c r="C670" t="n">
-        <v>1277927.44</v>
+        <v>1277927.45</v>
       </c>
     </row>
     <row r="671">
@@ -14485,10 +14485,10 @@
         <v>45200</v>
       </c>
       <c r="B671" t="n">
-        <v>1282359.38</v>
+        <v>1282360.29</v>
       </c>
       <c r="C671" t="n">
-        <v>1282359.38</v>
+        <v>1282360.29</v>
       </c>
     </row>
     <row r="672">
@@ -14496,10 +14496,10 @@
         <v>45231</v>
       </c>
       <c r="B672" t="n">
-        <v>1301585.93</v>
+        <v>1301584.14</v>
       </c>
       <c r="C672" t="n">
-        <v>1301585.93</v>
+        <v>1301584.14</v>
       </c>
     </row>
     <row r="673">
@@ -14507,10 +14507,10 @@
         <v>45261</v>
       </c>
       <c r="B673" t="n">
-        <v>1298865.89</v>
+        <v>1298865.94</v>
       </c>
       <c r="C673" t="n">
-        <v>1298865.89</v>
+        <v>1298865.94</v>
       </c>
     </row>
     <row r="674">
@@ -14518,10 +14518,10 @@
         <v>45292</v>
       </c>
       <c r="B674" t="n">
-        <v>1308351.47</v>
+        <v>1308360.21</v>
       </c>
       <c r="C674" t="n">
-        <v>1308351.47</v>
+        <v>1308360.21</v>
       </c>
     </row>
     <row r="675">
@@ -14529,10 +14529,10 @@
         <v>45323</v>
       </c>
       <c r="B675" t="n">
-        <v>1319462.37</v>
+        <v>1319466.64</v>
       </c>
       <c r="C675" t="n">
-        <v>1319462.37</v>
+        <v>1319466.64</v>
       </c>
     </row>
     <row r="676">
@@ -14540,10 +14540,10 @@
         <v>45352</v>
       </c>
       <c r="B676" t="n">
-        <v>1320920.6</v>
+        <v>1320920.67</v>
       </c>
       <c r="C676" t="n">
-        <v>1320920.6</v>
+        <v>1320920.67</v>
       </c>
     </row>
     <row r="677">
@@ -14551,10 +14551,10 @@
         <v>45383</v>
       </c>
       <c r="B677" t="n">
-        <v>1322883.53</v>
+        <v>1322889.21</v>
       </c>
       <c r="C677" t="n">
-        <v>1322883.53</v>
+        <v>1322889.21</v>
       </c>
     </row>
     <row r="678">
@@ -14562,10 +14562,10 @@
         <v>45413</v>
       </c>
       <c r="B678" t="n">
-        <v>1331284.5</v>
+        <v>1331285.6</v>
       </c>
       <c r="C678" t="n">
-        <v>1331284.5</v>
+        <v>1331285.6</v>
       </c>
     </row>
     <row r="679">
@@ -14584,10 +14584,10 @@
         <v>45474</v>
       </c>
       <c r="B680" t="n">
-        <v>1337484.66</v>
+        <v>1337484.65</v>
       </c>
       <c r="C680" t="n">
-        <v>1337484.66</v>
+        <v>1337484.65</v>
       </c>
     </row>
     <row r="681">
@@ -14595,10 +14595,10 @@
         <v>45505</v>
       </c>
       <c r="B681" t="n">
-        <v>1340184.49</v>
+        <v>1340184.48</v>
       </c>
       <c r="C681" t="n">
-        <v>1340184.49</v>
+        <v>1340184.48</v>
       </c>
     </row>
     <row r="682">
@@ -14628,10 +14628,10 @@
         <v>45597</v>
       </c>
       <c r="B684" t="n">
-        <v>1342090.49</v>
+        <v>1342090.48</v>
       </c>
       <c r="C684" t="n">
-        <v>1342090.49</v>
+        <v>1342090.48</v>
       </c>
     </row>
     <row r="685">
@@ -14650,10 +14650,10 @@
         <v>45658</v>
       </c>
       <c r="B686" t="n">
-        <v>1301982.23</v>
+        <v>1301935.81</v>
       </c>
       <c r="C686" t="n">
-        <v>1301982.23</v>
+        <v>1301935.81</v>
       </c>
     </row>
     <row r="687">
@@ -14661,10 +14661,10 @@
         <v>45689</v>
       </c>
       <c r="B687" t="n">
-        <v>1304274.47</v>
+        <v>1304181.74</v>
       </c>
       <c r="C687" t="n">
-        <v>1304274.47</v>
+        <v>1304181.74</v>
       </c>
     </row>
     <row r="688">
@@ -14672,10 +14672,10 @@
         <v>45717</v>
       </c>
       <c r="B688" t="n">
-        <v>1292802.55</v>
+        <v>1292802.54</v>
       </c>
       <c r="C688" t="n">
-        <v>1292802.55</v>
+        <v>1292802.54</v>
       </c>
     </row>
     <row r="689">
@@ -14683,10 +14683,10 @@
         <v>45748</v>
       </c>
       <c r="B689" t="n">
-        <v>1299129.25</v>
+        <v>1299412.58</v>
       </c>
       <c r="C689" t="n">
-        <v>1299129.25</v>
+        <v>1299412.58</v>
       </c>
     </row>
     <row r="690">
@@ -14694,10 +14694,10 @@
         <v>45778</v>
       </c>
       <c r="B690" t="n">
-        <v>1299722.4</v>
+        <v>1300224.95</v>
       </c>
       <c r="C690" t="n">
-        <v>1299722.4</v>
+        <v>1300224.95</v>
       </c>
     </row>
     <row r="691">
@@ -14705,10 +14705,10 @@
         <v>45809</v>
       </c>
       <c r="B691" t="n">
-        <v>1301742.19</v>
+        <v>1301742.16</v>
       </c>
       <c r="C691" t="n">
-        <v>1301742.19</v>
+        <v>1301742.16</v>
       </c>
     </row>
     <row r="692">
@@ -14716,10 +14716,10 @@
         <v>45839</v>
       </c>
       <c r="B692" t="n">
-        <v>1310351.97</v>
+        <v>1310281.47</v>
       </c>
       <c r="C692" t="n">
-        <v>1310351.97</v>
+        <v>1310281.47</v>
       </c>
     </row>
     <row r="693">
@@ -14727,10 +14727,10 @@
         <v>45870</v>
       </c>
       <c r="B693" t="n">
-        <v>1308162.07</v>
+        <v>1308311.66</v>
       </c>
       <c r="C693" t="n">
-        <v>1308162.07</v>
+        <v>1308311.66</v>
       </c>
     </row>
     <row r="694">
@@ -14749,10 +14749,10 @@
         <v>45931</v>
       </c>
       <c r="B695" t="n">
-        <v>1317360.55</v>
+        <v>1317077.74</v>
       </c>
       <c r="C695" t="n">
-        <v>1317360.55</v>
+        <v>1317077.74</v>
       </c>
     </row>
     <row r="696">
@@ -14760,10 +14760,10 @@
         <v>45962</v>
       </c>
       <c r="B696" t="n">
-        <v>1316595.76</v>
+        <v>1316336.21</v>
       </c>
       <c r="C696" t="n">
-        <v>1316595.76</v>
+        <v>1316336.21</v>
       </c>
     </row>
     <row r="697">
@@ -14771,10 +14771,10 @@
         <v>45992</v>
       </c>
       <c r="B697" t="n">
-        <v>1324322.36</v>
+        <v>1324322.34</v>
       </c>
       <c r="C697" t="n">
-        <v>1324322.36</v>
+        <v>1324322.34</v>
       </c>
     </row>
     <row r="698">
@@ -14782,10 +14782,10 @@
         <v>46023</v>
       </c>
       <c r="B698" t="n">
-        <v>1326134.9</v>
+        <v>1326083.72</v>
       </c>
       <c r="C698" t="n">
-        <v>1326134.9</v>
+        <v>1326083.72</v>
       </c>
     </row>
     <row r="699">
@@ -14793,10 +14793,10 @@
         <v>46054</v>
       </c>
       <c r="B699" t="n">
-        <v>1327271.55</v>
+        <v>1327206.23</v>
       </c>
       <c r="C699" t="n">
-        <v>1327271.55</v>
+        <v>1327206.23</v>
       </c>
     </row>
     <row r="700">
@@ -14815,10 +14815,10 @@
         <v>46113</v>
       </c>
       <c r="B701" t="n">
-        <v>1349505.63</v>
+        <v>1349631.51</v>
       </c>
       <c r="C701" t="n">
-        <v>1349505.63</v>
+        <v>1349631.51</v>
       </c>
     </row>
     <row r="702">
@@ -14826,10 +14826,21 @@
         <v>46143</v>
       </c>
       <c r="B702" t="n">
-        <v>1344207.79</v>
+        <v>1344328.87</v>
       </c>
       <c r="C702" t="n">
-        <v>1344207.79</v>
+        <v>1344328.87</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B703" t="n">
+        <v>1351069.14</v>
+      </c>
+      <c r="C703" t="n">
+        <v>1351069.14</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -28662,7 +28662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3110"/>
+  <dimension ref="A1:C3111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62875,10 +62875,21 @@
         <v>46235</v>
       </c>
       <c r="B3110" t="n">
-        <v>199000</v>
+        <v>200000</v>
       </c>
       <c r="C3110" t="n">
-        <v>199000</v>
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="3111">
+      <c r="A3111" s="1" t="n">
+        <v>46242</v>
+      </c>
+      <c r="B3111" t="n">
+        <v>209000</v>
+      </c>
+      <c r="C3111" t="n">
+        <v>209000</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -28662,7 +28662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3111"/>
+  <dimension ref="A1:C3112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62886,10 +62886,21 @@
         <v>46242</v>
       </c>
       <c r="B3111" t="n">
-        <v>209000</v>
+        <v>212000</v>
       </c>
       <c r="C3111" t="n">
-        <v>209000</v>
+        <v>212000</v>
+      </c>
+    </row>
+    <row r="3112">
+      <c r="A3112" s="1" t="n">
+        <v>46249</v>
+      </c>
+      <c r="B3112" t="n">
+        <v>206000</v>
+      </c>
+      <c r="C3112" t="n">
+        <v>206000</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C142"/>
+  <dimension ref="A1:C143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1880,10 +1880,10 @@
         <v>45108</v>
       </c>
       <c r="B132" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="C132" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="133">
@@ -1946,10 +1946,10 @@
         <v>45658</v>
       </c>
       <c r="B138" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="C138" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="139">
@@ -1968,10 +1968,10 @@
         <v>45839</v>
       </c>
       <c r="B140" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="C140" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="141">
@@ -1979,10 +1979,10 @@
         <v>45931</v>
       </c>
       <c r="B141" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="C141" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="142">
@@ -1990,10 +1990,21 @@
         <v>46023</v>
       </c>
       <c r="B142" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="C142" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B143" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="C143" t="n">
+        <v>2.85</v>
       </c>
     </row>
   </sheetData>
@@ -2007,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C166"/>
+  <dimension ref="A1:C167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2582,10 +2593,10 @@
         <v>35612</v>
       </c>
       <c r="B52" t="n">
-        <v>5.49</v>
+        <v>5.5</v>
       </c>
       <c r="C52" t="n">
-        <v>5.49</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="53">
@@ -2604,10 +2615,10 @@
         <v>35796</v>
       </c>
       <c r="B54" t="n">
-        <v>5.25</v>
+        <v>5.24</v>
       </c>
       <c r="C54" t="n">
-        <v>5.25</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="55">
@@ -2615,10 +2626,10 @@
         <v>35886</v>
       </c>
       <c r="B55" t="n">
-        <v>5.21</v>
+        <v>5.2</v>
       </c>
       <c r="C55" t="n">
-        <v>5.21</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="56">
@@ -2626,10 +2637,10 @@
         <v>35977</v>
       </c>
       <c r="B56" t="n">
-        <v>5.27</v>
+        <v>5.28</v>
       </c>
       <c r="C56" t="n">
-        <v>5.27</v>
+        <v>5.28</v>
       </c>
     </row>
     <row r="57">
@@ -2637,10 +2648,10 @@
         <v>36069</v>
       </c>
       <c r="B57" t="n">
-        <v>5.06</v>
+        <v>5.08</v>
       </c>
       <c r="C57" t="n">
-        <v>5.06</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="58">
@@ -2648,10 +2659,10 @@
         <v>36161</v>
       </c>
       <c r="B58" t="n">
-        <v>4.92</v>
+        <v>4.89</v>
       </c>
       <c r="C58" t="n">
-        <v>4.92</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="59">
@@ -2659,10 +2670,10 @@
         <v>36251</v>
       </c>
       <c r="B59" t="n">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="C59" t="n">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="60">
@@ -2670,10 +2681,10 @@
         <v>36342</v>
       </c>
       <c r="B60" t="n">
-        <v>4.48</v>
+        <v>4.5</v>
       </c>
       <c r="C60" t="n">
-        <v>4.48</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="61">
@@ -2681,10 +2692,10 @@
         <v>36434</v>
       </c>
       <c r="B61" t="n">
-        <v>4.46</v>
+        <v>4.49</v>
       </c>
       <c r="C61" t="n">
-        <v>4.46</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="62">
@@ -2692,10 +2703,10 @@
         <v>36526</v>
       </c>
       <c r="B62" t="n">
-        <v>4.53</v>
+        <v>4.49</v>
       </c>
       <c r="C62" t="n">
-        <v>4.53</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="63">
@@ -2703,10 +2714,10 @@
         <v>36617</v>
       </c>
       <c r="B63" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="C63" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="64">
@@ -2714,10 +2725,10 @@
         <v>36708</v>
       </c>
       <c r="B64" t="n">
-        <v>4.23</v>
+        <v>4.25</v>
       </c>
       <c r="C64" t="n">
-        <v>4.23</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="65">
@@ -2725,10 +2736,10 @@
         <v>36800</v>
       </c>
       <c r="B65" t="n">
-        <v>4.34</v>
+        <v>4.39</v>
       </c>
       <c r="C65" t="n">
-        <v>4.34</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="66">
@@ -2736,10 +2747,10 @@
         <v>36892</v>
       </c>
       <c r="B66" t="n">
-        <v>4.65</v>
+        <v>4.57</v>
       </c>
       <c r="C66" t="n">
-        <v>4.65</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="67">
@@ -2747,10 +2758,10 @@
         <v>36982</v>
       </c>
       <c r="B67" t="n">
-        <v>5.21</v>
+        <v>5.22</v>
       </c>
       <c r="C67" t="n">
-        <v>5.21</v>
+        <v>5.22</v>
       </c>
     </row>
     <row r="68">
@@ -2758,10 +2769,10 @@
         <v>37073</v>
       </c>
       <c r="B68" t="n">
-        <v>5.52</v>
+        <v>5.55</v>
       </c>
       <c r="C68" t="n">
-        <v>5.52</v>
+        <v>5.55</v>
       </c>
     </row>
     <row r="69">
@@ -2769,10 +2780,10 @@
         <v>37165</v>
       </c>
       <c r="B69" t="n">
-        <v>6.28</v>
+        <v>6.35</v>
       </c>
       <c r="C69" t="n">
-        <v>6.28</v>
+        <v>6.35</v>
       </c>
     </row>
     <row r="70">
@@ -2780,10 +2791,10 @@
         <v>37257</v>
       </c>
       <c r="B70" t="n">
-        <v>7.78</v>
+        <v>7.65</v>
       </c>
       <c r="C70" t="n">
-        <v>7.78</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="71">
@@ -2802,10 +2813,10 @@
         <v>37438</v>
       </c>
       <c r="B72" t="n">
-        <v>6.18</v>
+        <v>6.22</v>
       </c>
       <c r="C72" t="n">
-        <v>6.18</v>
+        <v>6.22</v>
       </c>
     </row>
     <row r="73">
@@ -2813,10 +2824,10 @@
         <v>37530</v>
       </c>
       <c r="B73" t="n">
-        <v>5.48</v>
+        <v>5.54</v>
       </c>
       <c r="C73" t="n">
-        <v>5.48</v>
+        <v>5.54</v>
       </c>
     </row>
     <row r="74">
@@ -2824,10 +2835,10 @@
         <v>37622</v>
       </c>
       <c r="B74" t="n">
-        <v>5.83</v>
+        <v>5.73</v>
       </c>
       <c r="C74" t="n">
-        <v>5.83</v>
+        <v>5.73</v>
       </c>
     </row>
     <row r="75">
@@ -2846,10 +2857,10 @@
         <v>37803</v>
       </c>
       <c r="B76" t="n">
-        <v>5.57</v>
+        <v>5.59</v>
       </c>
       <c r="C76" t="n">
-        <v>5.57</v>
+        <v>5.59</v>
       </c>
     </row>
     <row r="77">
@@ -2857,10 +2868,10 @@
         <v>37895</v>
       </c>
       <c r="B77" t="n">
-        <v>5.95</v>
+        <v>6.01</v>
       </c>
       <c r="C77" t="n">
-        <v>5.95</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="78">
@@ -2868,10 +2879,10 @@
         <v>37987</v>
       </c>
       <c r="B78" t="n">
-        <v>5.47</v>
+        <v>5.4</v>
       </c>
       <c r="C78" t="n">
-        <v>5.47</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="79">
@@ -2890,10 +2901,10 @@
         <v>38169</v>
       </c>
       <c r="B80" t="n">
-        <v>4.47</v>
+        <v>4.49</v>
       </c>
       <c r="C80" t="n">
-        <v>4.47</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="81">
@@ -2901,10 +2912,10 @@
         <v>38261</v>
       </c>
       <c r="B81" t="n">
-        <v>4.65</v>
+        <v>4.68</v>
       </c>
       <c r="C81" t="n">
-        <v>4.65</v>
+        <v>4.68</v>
       </c>
     </row>
     <row r="82">
@@ -2912,10 +2923,10 @@
         <v>38353</v>
       </c>
       <c r="B82" t="n">
-        <v>4.7</v>
+        <v>4.66</v>
       </c>
       <c r="C82" t="n">
-        <v>4.7</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="83">
@@ -2923,10 +2934,10 @@
         <v>38443</v>
       </c>
       <c r="B83" t="n">
-        <v>4.26</v>
+        <v>4.25</v>
       </c>
       <c r="C83" t="n">
-        <v>4.26</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="84">
@@ -2934,10 +2945,10 @@
         <v>38534</v>
       </c>
       <c r="B84" t="n">
-        <v>4.34</v>
+        <v>4.35</v>
       </c>
       <c r="C84" t="n">
-        <v>4.34</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="85">
@@ -2945,10 +2956,10 @@
         <v>38626</v>
       </c>
       <c r="B85" t="n">
-        <v>6.07</v>
+        <v>6.09</v>
       </c>
       <c r="C85" t="n">
-        <v>6.07</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="86">
@@ -2956,10 +2967,10 @@
         <v>38718</v>
       </c>
       <c r="B86" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="C86" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="87">
@@ -2967,10 +2978,10 @@
         <v>38808</v>
       </c>
       <c r="B87" t="n">
-        <v>3.44</v>
+        <v>3.43</v>
       </c>
       <c r="C87" t="n">
-        <v>3.44</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="88">
@@ -2978,10 +2989,10 @@
         <v>38899</v>
       </c>
       <c r="B88" t="n">
-        <v>3.83</v>
+        <v>3.84</v>
       </c>
       <c r="C88" t="n">
-        <v>3.83</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="89">
@@ -2989,10 +3000,10 @@
         <v>38991</v>
       </c>
       <c r="B89" t="n">
-        <v>3.69</v>
+        <v>3.7</v>
       </c>
       <c r="C89" t="n">
-        <v>3.69</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="90">
@@ -3000,10 +3011,10 @@
         <v>39083</v>
       </c>
       <c r="B90" t="n">
-        <v>4.02</v>
+        <v>4.01</v>
       </c>
       <c r="C90" t="n">
-        <v>4.02</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="91">
@@ -3022,10 +3033,10 @@
         <v>39264</v>
       </c>
       <c r="B92" t="n">
-        <v>3.9</v>
+        <v>3.91</v>
       </c>
       <c r="C92" t="n">
-        <v>3.9</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="93">
@@ -3033,10 +3044,10 @@
         <v>39356</v>
       </c>
       <c r="B93" t="n">
-        <v>4.31</v>
+        <v>4.32</v>
       </c>
       <c r="C93" t="n">
-        <v>4.31</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="94">
@@ -3044,10 +3055,10 @@
         <v>39448</v>
       </c>
       <c r="B94" t="n">
-        <v>4.77</v>
+        <v>4.76</v>
       </c>
       <c r="C94" t="n">
-        <v>4.77</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="95">
@@ -3077,10 +3088,10 @@
         <v>39722</v>
       </c>
       <c r="B97" t="n">
-        <v>6.52</v>
+        <v>6.53</v>
       </c>
       <c r="C97" t="n">
-        <v>6.52</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="98">
@@ -3088,10 +3099,10 @@
         <v>39814</v>
       </c>
       <c r="B98" t="n">
-        <v>7.69</v>
+        <v>7.68</v>
       </c>
       <c r="C98" t="n">
-        <v>7.69</v>
+        <v>7.68</v>
       </c>
     </row>
     <row r="99">
@@ -3154,10 +3165,10 @@
         <v>40360</v>
       </c>
       <c r="B104" t="n">
-        <v>8.77</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="C104" t="n">
-        <v>8.77</v>
+        <v>8.779999999999999</v>
       </c>
     </row>
     <row r="105">
@@ -3363,10 +3374,10 @@
         <v>42095</v>
       </c>
       <c r="B123" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="C123" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="124">
@@ -3374,10 +3385,10 @@
         <v>42186</v>
       </c>
       <c r="B124" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="C124" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="125">
@@ -3385,10 +3396,10 @@
         <v>42278</v>
       </c>
       <c r="B125" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="C125" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="126">
@@ -3407,10 +3418,10 @@
         <v>42461</v>
       </c>
       <c r="B127" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="C127" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="128">
@@ -3418,10 +3429,10 @@
         <v>42552</v>
       </c>
       <c r="B128" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="C128" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="129">
@@ -3440,10 +3451,10 @@
         <v>42736</v>
       </c>
       <c r="B130" t="n">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="C130" t="n">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="131">
@@ -3451,10 +3462,10 @@
         <v>42826</v>
       </c>
       <c r="B131" t="n">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="C131" t="n">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="132">
@@ -3462,10 +3473,10 @@
         <v>42917</v>
       </c>
       <c r="B132" t="n">
-        <v>3.58</v>
+        <v>3.59</v>
       </c>
       <c r="C132" t="n">
-        <v>3.58</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="133">
@@ -3473,10 +3484,10 @@
         <v>43009</v>
       </c>
       <c r="B133" t="n">
-        <v>3.69</v>
+        <v>3.7</v>
       </c>
       <c r="C133" t="n">
-        <v>3.69</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="134">
@@ -3484,10 +3495,10 @@
         <v>43101</v>
       </c>
       <c r="B134" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="C134" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="135">
@@ -3506,10 +3517,10 @@
         <v>43282</v>
       </c>
       <c r="B136" t="n">
-        <v>3.65</v>
+        <v>3.69</v>
       </c>
       <c r="C136" t="n">
-        <v>3.65</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="137">
@@ -3517,10 +3528,10 @@
         <v>43374</v>
       </c>
       <c r="B137" t="n">
-        <v>3.66</v>
+        <v>3.67</v>
       </c>
       <c r="C137" t="n">
-        <v>3.66</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="138">
@@ -3528,10 +3539,10 @@
         <v>43466</v>
       </c>
       <c r="B138" t="n">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="C138" t="n">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="139">
@@ -3539,10 +3550,10 @@
         <v>43556</v>
       </c>
       <c r="B139" t="n">
-        <v>3.67</v>
+        <v>3.63</v>
       </c>
       <c r="C139" t="n">
-        <v>3.67</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="140">
@@ -3550,10 +3561,10 @@
         <v>43647</v>
       </c>
       <c r="B140" t="n">
-        <v>3.68</v>
+        <v>3.75</v>
       </c>
       <c r="C140" t="n">
-        <v>3.68</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="141">
@@ -3561,10 +3572,10 @@
         <v>43739</v>
       </c>
       <c r="B141" t="n">
-        <v>3.77</v>
+        <v>3.78</v>
       </c>
       <c r="C141" t="n">
-        <v>3.77</v>
+        <v>3.78</v>
       </c>
     </row>
     <row r="142">
@@ -3572,10 +3583,10 @@
         <v>43831</v>
       </c>
       <c r="B142" t="n">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="C142" t="n">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
     </row>
     <row r="143">
@@ -3583,10 +3594,10 @@
         <v>43922</v>
       </c>
       <c r="B143" t="n">
-        <v>3.84</v>
+        <v>3.78</v>
       </c>
       <c r="C143" t="n">
-        <v>3.84</v>
+        <v>3.78</v>
       </c>
     </row>
     <row r="144">
@@ -3594,10 +3605,10 @@
         <v>44013</v>
       </c>
       <c r="B144" t="n">
-        <v>3.51</v>
+        <v>3.6</v>
       </c>
       <c r="C144" t="n">
-        <v>3.51</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="145">
@@ -3616,10 +3627,10 @@
         <v>44197</v>
       </c>
       <c r="B146" t="n">
-        <v>2.84</v>
+        <v>2.81</v>
       </c>
       <c r="C146" t="n">
-        <v>2.84</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="147">
@@ -3627,10 +3638,10 @@
         <v>44287</v>
       </c>
       <c r="B147" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="C147" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="148">
@@ -3638,10 +3649,10 @@
         <v>44378</v>
       </c>
       <c r="B148" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="C148" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="149">
@@ -3660,10 +3671,10 @@
         <v>44562</v>
       </c>
       <c r="B150" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="C150" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="151">
@@ -3671,10 +3682,10 @@
         <v>44652</v>
       </c>
       <c r="B151" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="C151" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="152">
@@ -3682,10 +3693,10 @@
         <v>44743</v>
       </c>
       <c r="B152" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="C152" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="153">
@@ -3693,10 +3704,10 @@
         <v>44835</v>
       </c>
       <c r="B153" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="C153" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="154">
@@ -3704,10 +3715,10 @@
         <v>44927</v>
       </c>
       <c r="B154" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="C154" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="155">
@@ -3715,10 +3726,10 @@
         <v>45017</v>
       </c>
       <c r="B155" t="n">
-        <v>3.26</v>
+        <v>3.23</v>
       </c>
       <c r="C155" t="n">
-        <v>3.26</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="156">
@@ -3726,10 +3737,10 @@
         <v>45108</v>
       </c>
       <c r="B156" t="n">
-        <v>3.7</v>
+        <v>3.76</v>
       </c>
       <c r="C156" t="n">
-        <v>3.7</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="157">
@@ -3737,10 +3748,10 @@
         <v>45200</v>
       </c>
       <c r="B157" t="n">
-        <v>4.17</v>
+        <v>4.18</v>
       </c>
       <c r="C157" t="n">
-        <v>4.17</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="158">
@@ -3748,10 +3759,10 @@
         <v>45292</v>
       </c>
       <c r="B158" t="n">
-        <v>4.43</v>
+        <v>4.4</v>
       </c>
       <c r="C158" t="n">
-        <v>4.43</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="159">
@@ -3759,10 +3770,10 @@
         <v>45383</v>
       </c>
       <c r="B159" t="n">
-        <v>4.59</v>
+        <v>4.56</v>
       </c>
       <c r="C159" t="n">
-        <v>4.59</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="160">
@@ -3770,10 +3781,10 @@
         <v>45474</v>
       </c>
       <c r="B160" t="n">
-        <v>4.64</v>
+        <v>4.69</v>
       </c>
       <c r="C160" t="n">
-        <v>4.64</v>
+        <v>4.69</v>
       </c>
     </row>
     <row r="161">
@@ -3781,10 +3792,10 @@
         <v>45566</v>
       </c>
       <c r="B161" t="n">
-        <v>4.56</v>
+        <v>4.57</v>
       </c>
       <c r="C161" t="n">
-        <v>4.56</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="162">
@@ -3792,10 +3803,10 @@
         <v>45658</v>
       </c>
       <c r="B162" t="n">
-        <v>4.46</v>
+        <v>4.44</v>
       </c>
       <c r="C162" t="n">
-        <v>4.46</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="163">
@@ -3803,10 +3814,10 @@
         <v>45748</v>
       </c>
       <c r="B163" t="n">
-        <v>4.21</v>
+        <v>4.19</v>
       </c>
       <c r="C163" t="n">
-        <v>4.21</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="164">
@@ -3814,10 +3825,10 @@
         <v>45839</v>
       </c>
       <c r="B164" t="n">
-        <v>4.15</v>
+        <v>4.18</v>
       </c>
       <c r="C164" t="n">
-        <v>4.15</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="165">
@@ -3825,10 +3836,10 @@
         <v>45931</v>
       </c>
       <c r="B165" t="n">
-        <v>4.07</v>
+        <v>4.09</v>
       </c>
       <c r="C165" t="n">
-        <v>4.07</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="166">
@@ -3836,10 +3847,21 @@
         <v>46023</v>
       </c>
       <c r="B166" t="n">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="C166" t="n">
-        <v>3.84</v>
+        <v>3.82</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B167" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="C167" t="n">
+        <v>3.82</v>
       </c>
     </row>
   </sheetData>
@@ -5519,7 +5541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C142"/>
+  <dimension ref="A1:C143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5544,10 +5566,10 @@
         <v>33239</v>
       </c>
       <c r="B2" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="C2" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="3">
@@ -5588,10 +5610,10 @@
         <v>33604</v>
       </c>
       <c r="B6" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="C6" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="7">
@@ -5731,10 +5753,10 @@
         <v>34790</v>
       </c>
       <c r="B19" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="C19" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="20">
@@ -5973,10 +5995,10 @@
         <v>36800</v>
       </c>
       <c r="B41" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="C41" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="42">
@@ -6292,10 +6314,10 @@
         <v>39448</v>
       </c>
       <c r="B70" t="n">
-        <v>3.67</v>
+        <v>3.68</v>
       </c>
       <c r="C70" t="n">
-        <v>3.67</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="71">
@@ -6303,10 +6325,10 @@
         <v>39539</v>
       </c>
       <c r="B71" t="n">
-        <v>4.36</v>
+        <v>4.37</v>
       </c>
       <c r="C71" t="n">
-        <v>4.36</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="72">
@@ -6314,10 +6336,10 @@
         <v>39630</v>
       </c>
       <c r="B72" t="n">
-        <v>5.27</v>
+        <v>5.26</v>
       </c>
       <c r="C72" t="n">
-        <v>5.27</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="73">
@@ -6325,10 +6347,10 @@
         <v>39722</v>
       </c>
       <c r="B73" t="n">
-        <v>6.59</v>
+        <v>6.6</v>
       </c>
       <c r="C73" t="n">
-        <v>6.59</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="74">
@@ -6336,10 +6358,10 @@
         <v>39814</v>
       </c>
       <c r="B74" t="n">
-        <v>8</v>
+        <v>7.99</v>
       </c>
       <c r="C74" t="n">
-        <v>8</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="75">
@@ -6402,10 +6424,10 @@
         <v>40360</v>
       </c>
       <c r="B80" t="n">
-        <v>10.66</v>
+        <v>10.65</v>
       </c>
       <c r="C80" t="n">
-        <v>10.66</v>
+        <v>10.65</v>
       </c>
     </row>
     <row r="81">
@@ -6534,10 +6556,10 @@
         <v>41456</v>
       </c>
       <c r="B92" t="n">
-        <v>8.66</v>
+        <v>8.65</v>
       </c>
       <c r="C92" t="n">
-        <v>8.66</v>
+        <v>8.65</v>
       </c>
     </row>
     <row r="93">
@@ -6600,10 +6622,10 @@
         <v>42005</v>
       </c>
       <c r="B98" t="n">
-        <v>6.23</v>
+        <v>6.22</v>
       </c>
       <c r="C98" t="n">
-        <v>6.23</v>
+        <v>6.22</v>
       </c>
     </row>
     <row r="99">
@@ -6622,10 +6644,10 @@
         <v>42186</v>
       </c>
       <c r="B100" t="n">
-        <v>5.4</v>
+        <v>5.41</v>
       </c>
       <c r="C100" t="n">
-        <v>5.4</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="101">
@@ -6754,10 +6776,10 @@
         <v>43282</v>
       </c>
       <c r="B112" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
       <c r="C112" t="n">
-        <v>2.99</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="113">
@@ -6842,10 +6864,10 @@
         <v>44013</v>
       </c>
       <c r="B120" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="C120" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="121">
@@ -6919,10 +6941,10 @@
         <v>44652</v>
       </c>
       <c r="B127" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="C127" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="128">
@@ -7029,10 +7051,10 @@
         <v>45566</v>
       </c>
       <c r="B137" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="C137" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="138">
@@ -7084,10 +7106,21 @@
         <v>46023</v>
       </c>
       <c r="B142" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="C142" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B143" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1.86</v>
       </c>
     </row>
   </sheetData>
@@ -62914,7 +62947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C811"/>
+  <dimension ref="A1:C812"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71816,10 +71849,10 @@
         <v>46113</v>
       </c>
       <c r="B809" t="n">
-        <v>17956.2</v>
+        <v>17957.1</v>
       </c>
       <c r="C809" t="n">
-        <v>17956.2</v>
+        <v>17957.1</v>
       </c>
     </row>
     <row r="810">
@@ -71827,10 +71860,10 @@
         <v>46143</v>
       </c>
       <c r="B810" t="n">
-        <v>17999.8</v>
+        <v>18000.1</v>
       </c>
       <c r="C810" t="n">
-        <v>17999.8</v>
+        <v>18000.1</v>
       </c>
     </row>
     <row r="811">
@@ -71838,10 +71871,21 @@
         <v>46174</v>
       </c>
       <c r="B811" t="n">
-        <v>18056.1</v>
+        <v>18054.9</v>
       </c>
       <c r="C811" t="n">
-        <v>18056.1</v>
+        <v>18054.9</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B812" t="n">
+        <v>18122.5</v>
+      </c>
+      <c r="C812" t="n">
+        <v>18122.5</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -28695,7 +28695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3112"/>
+  <dimension ref="A1:C3113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62930,10 +62930,21 @@
         <v>46249</v>
       </c>
       <c r="B3112" t="n">
-        <v>206000</v>
+        <v>207000</v>
       </c>
       <c r="C3112" t="n">
-        <v>206000</v>
+        <v>207000</v>
+      </c>
+    </row>
+    <row r="3113">
+      <c r="A3113" s="1" t="n">
+        <v>46256</v>
+      </c>
+      <c r="B3113" t="n">
+        <v>203000</v>
+      </c>
+      <c r="C3113" t="n">
+        <v>203000</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -14887,7 +14887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C308"/>
+  <dimension ref="A1:C309"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18278,10 +18278,21 @@
         <v>46174</v>
       </c>
       <c r="B308" t="n">
-        <v>7359</v>
+        <v>7182</v>
       </c>
       <c r="C308" t="n">
-        <v>7.359</v>
+        <v>7.182</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B309" t="n">
+        <v>7271</v>
+      </c>
+      <c r="C309" t="n">
+        <v>7.271</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -28706,7 +28706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3113"/>
+  <dimension ref="A1:C3114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62952,10 +62952,21 @@
         <v>46256</v>
       </c>
       <c r="B3113" t="n">
-        <v>203000</v>
+        <v>204000</v>
       </c>
       <c r="C3113" t="n">
-        <v>203000</v>
+        <v>204000</v>
+      </c>
+    </row>
+    <row r="3114">
+      <c r="A3114" s="1" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B3114" t="n">
+        <v>206000</v>
+      </c>
+      <c r="C3114" t="n">
+        <v>206000</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -18306,7 +18306,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C944"/>
+  <dimension ref="A1:C945"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28692,6 +28692,17 @@
         <v>4.1</v>
       </c>
       <c r="C944" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B945" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="C945" t="n">
         <v>4.1</v>
       </c>
     </row>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -7134,7 +7134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C703"/>
+  <dimension ref="A1:C704"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14815,10 +14815,10 @@
         <v>46023</v>
       </c>
       <c r="B698" t="n">
-        <v>1326083.72</v>
+        <v>1326040.45</v>
       </c>
       <c r="C698" t="n">
-        <v>1326083.72</v>
+        <v>1326040.45</v>
       </c>
     </row>
     <row r="699">
@@ -14826,10 +14826,10 @@
         <v>46054</v>
       </c>
       <c r="B699" t="n">
-        <v>1327206.23</v>
+        <v>1327120.87</v>
       </c>
       <c r="C699" t="n">
-        <v>1327206.23</v>
+        <v>1327120.87</v>
       </c>
     </row>
     <row r="700">
@@ -14837,10 +14837,10 @@
         <v>46082</v>
       </c>
       <c r="B700" t="n">
-        <v>1337959.33</v>
+        <v>1338182.22</v>
       </c>
       <c r="C700" t="n">
-        <v>1337959.33</v>
+        <v>1338182.22</v>
       </c>
     </row>
     <row r="701">
@@ -14848,10 +14848,10 @@
         <v>46113</v>
       </c>
       <c r="B701" t="n">
-        <v>1349631.51</v>
+        <v>1349906.26</v>
       </c>
       <c r="C701" t="n">
-        <v>1349631.51</v>
+        <v>1349906.26</v>
       </c>
     </row>
     <row r="702">
@@ -14859,10 +14859,10 @@
         <v>46143</v>
       </c>
       <c r="B702" t="n">
-        <v>1344328.87</v>
+        <v>1347697.77</v>
       </c>
       <c r="C702" t="n">
-        <v>1344328.87</v>
+        <v>1347697.77</v>
       </c>
     </row>
     <row r="703">
@@ -14870,10 +14870,21 @@
         <v>46174</v>
       </c>
       <c r="B703" t="n">
-        <v>1351069.14</v>
+        <v>1354418.69</v>
       </c>
       <c r="C703" t="n">
-        <v>1351069.14</v>
+        <v>1354418.69</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B704" t="n">
+        <v>1357221.44</v>
+      </c>
+      <c r="C704" t="n">
+        <v>1357221.44</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_timeseries.xlsx
+++ b/macro_credit_timeseries.xlsx
@@ -28728,7 +28728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3114"/>
+  <dimension ref="A1:C3115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62985,9 +62985,20 @@
         <v>46263</v>
       </c>
       <c r="B3114" t="n">
+        <v>207000</v>
+      </c>
+      <c r="C3114" t="n">
+        <v>207000</v>
+      </c>
+    </row>
+    <row r="3115">
+      <c r="A3115" s="1" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B3115" t="n">
         <v>206000</v>
       </c>
-      <c r="C3114" t="n">
+      <c r="C3115" t="n">
         <v>206000</v>
       </c>
     </row>
